--- a/reports/excel/Vulnerability_Report.xlsx
+++ b/reports/excel/Vulnerability_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="859">
   <si>
     <t>📊 VULNERABILITY REPORT - AUTOMATION EXECUTION SUMMARY</t>
   </si>
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 03:51:22</t>
+    <t>2026-08-20 04:37:21</t>
   </si>
   <si>
     <t>TC-SEC-002</t>
@@ -745,6 +745,9 @@
     <t>Headers: Strict-Transport-Security (HSTS) configured for production</t>
   </si>
   <si>
+    <t>2026-08-20 04:37:22</t>
+  </si>
+  <si>
     <t>TC-SEC-106</t>
   </si>
   <si>
@@ -1340,6 +1343,9 @@
   </si>
   <si>
     <t>Path Traversal: Absolute path to /proc/self/environ</t>
+  </si>
+  <si>
+    <t>0.01s</t>
   </si>
   <si>
     <t>TC-SEC-208</t>
@@ -6073,7 +6079,7 @@
         <v>27</v>
       </c>
       <c r="G106" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H106" s="15" t="s">
         <v>13</v>
@@ -6081,13 +6087,13 @@
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B107" s="18" t="s">
         <v>233</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>25</v>
@@ -6096,10 +6102,10 @@
         <v>26</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H107" s="20" t="s">
         <v>13</v>
@@ -6107,13 +6113,13 @@
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B108" s="13" t="s">
         <v>233</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>25</v>
@@ -6122,10 +6128,10 @@
         <v>26</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H108" s="15" t="s">
         <v>13</v>
@@ -6133,13 +6139,13 @@
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B109" s="18" t="s">
         <v>233</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D109" s="20" t="s">
         <v>25</v>
@@ -6148,10 +6154,10 @@
         <v>26</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H109" s="20" t="s">
         <v>13</v>
@@ -6159,13 +6165,13 @@
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B110" s="13" t="s">
         <v>233</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>25</v>
@@ -6174,10 +6180,10 @@
         <v>26</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H110" s="15" t="s">
         <v>13</v>
@@ -6185,13 +6191,13 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B111" s="18" t="s">
         <v>233</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D111" s="20" t="s">
         <v>25</v>
@@ -6200,10 +6206,10 @@
         <v>26</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H111" s="20" t="s">
         <v>13</v>
@@ -6211,13 +6217,13 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>25</v>
@@ -6226,10 +6232,10 @@
         <v>26</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H112" s="15" t="s">
         <v>13</v>
@@ -6237,13 +6243,13 @@
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D113" s="20" t="s">
         <v>25</v>
@@ -6252,10 +6258,10 @@
         <v>26</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H113" s="20" t="s">
         <v>13</v>
@@ -6263,13 +6269,13 @@
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>25</v>
@@ -6278,10 +6284,10 @@
         <v>26</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H114" s="15" t="s">
         <v>13</v>
@@ -6289,13 +6295,13 @@
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D115" s="20" t="s">
         <v>25</v>
@@ -6304,10 +6310,10 @@
         <v>26</v>
       </c>
       <c r="F115" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H115" s="20" t="s">
         <v>13</v>
@@ -6315,13 +6321,13 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>25</v>
@@ -6330,10 +6336,10 @@
         <v>26</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H116" s="15" t="s">
         <v>13</v>
@@ -6341,13 +6347,13 @@
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D117" s="20" t="s">
         <v>25</v>
@@ -6356,10 +6362,10 @@
         <v>26</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G117" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H117" s="20" t="s">
         <v>13</v>
@@ -6367,13 +6373,13 @@
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D118" s="15" t="s">
         <v>25</v>
@@ -6382,10 +6388,10 @@
         <v>26</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G118" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H118" s="15" t="s">
         <v>13</v>
@@ -6393,13 +6399,13 @@
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B119" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D119" s="20" t="s">
         <v>25</v>
@@ -6408,10 +6414,10 @@
         <v>26</v>
       </c>
       <c r="F119" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H119" s="20" t="s">
         <v>13</v>
@@ -6419,13 +6425,13 @@
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>25</v>
@@ -6434,10 +6440,10 @@
         <v>26</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H120" s="15" t="s">
         <v>13</v>
@@ -6445,13 +6451,13 @@
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D121" s="20" t="s">
         <v>25</v>
@@ -6460,10 +6466,10 @@
         <v>26</v>
       </c>
       <c r="F121" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H121" s="20" t="s">
         <v>13</v>
@@ -6471,13 +6477,13 @@
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>25</v>
@@ -6486,10 +6492,10 @@
         <v>26</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H122" s="15" t="s">
         <v>13</v>
@@ -6497,13 +6503,13 @@
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D123" s="20" t="s">
         <v>25</v>
@@ -6512,10 +6518,10 @@
         <v>26</v>
       </c>
       <c r="F123" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H123" s="20" t="s">
         <v>13</v>
@@ -6523,13 +6529,13 @@
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D124" s="15" t="s">
         <v>25</v>
@@ -6538,10 +6544,10 @@
         <v>26</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H124" s="15" t="s">
         <v>13</v>
@@ -6549,13 +6555,13 @@
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D125" s="20" t="s">
         <v>25</v>
@@ -6564,10 +6570,10 @@
         <v>26</v>
       </c>
       <c r="F125" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H125" s="20" t="s">
         <v>13</v>
@@ -6575,13 +6581,13 @@
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>25</v>
@@ -6590,10 +6596,10 @@
         <v>26</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H126" s="15" t="s">
         <v>13</v>
@@ -6601,13 +6607,13 @@
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D127" s="20" t="s">
         <v>25</v>
@@ -6616,10 +6622,10 @@
         <v>26</v>
       </c>
       <c r="F127" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H127" s="20" t="s">
         <v>13</v>
@@ -6627,13 +6633,13 @@
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>25</v>
@@ -6642,10 +6648,10 @@
         <v>26</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G128" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H128" s="15" t="s">
         <v>13</v>
@@ -6653,13 +6659,13 @@
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D129" s="20" t="s">
         <v>25</v>
@@ -6668,10 +6674,10 @@
         <v>26</v>
       </c>
       <c r="F129" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G129" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H129" s="20" t="s">
         <v>13</v>
@@ -6679,13 +6685,13 @@
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>25</v>
@@ -6694,10 +6700,10 @@
         <v>26</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G130" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H130" s="15" t="s">
         <v>13</v>
@@ -6705,13 +6711,13 @@
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D131" s="20" t="s">
         <v>25</v>
@@ -6720,10 +6726,10 @@
         <v>26</v>
       </c>
       <c r="F131" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G131" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H131" s="20" t="s">
         <v>13</v>
@@ -6731,13 +6737,13 @@
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D132" s="15" t="s">
         <v>25</v>
@@ -6746,10 +6752,10 @@
         <v>26</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G132" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H132" s="15" t="s">
         <v>13</v>
@@ -6757,13 +6763,13 @@
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D133" s="20" t="s">
         <v>25</v>
@@ -6772,10 +6778,10 @@
         <v>26</v>
       </c>
       <c r="F133" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G133" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H133" s="20" t="s">
         <v>13</v>
@@ -6783,13 +6789,13 @@
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>25</v>
@@ -6798,10 +6804,10 @@
         <v>26</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G134" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H134" s="15" t="s">
         <v>13</v>
@@ -6809,13 +6815,13 @@
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D135" s="20" t="s">
         <v>25</v>
@@ -6824,10 +6830,10 @@
         <v>26</v>
       </c>
       <c r="F135" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H135" s="20" t="s">
         <v>13</v>
@@ -6835,13 +6841,13 @@
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>25</v>
@@ -6850,10 +6856,10 @@
         <v>26</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G136" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H136" s="15" t="s">
         <v>13</v>
@@ -6861,13 +6867,13 @@
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D137" s="20" t="s">
         <v>25</v>
@@ -6876,10 +6882,10 @@
         <v>26</v>
       </c>
       <c r="F137" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G137" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H137" s="20" t="s">
         <v>13</v>
@@ -6887,13 +6893,13 @@
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>25</v>
@@ -6902,10 +6908,10 @@
         <v>26</v>
       </c>
       <c r="F138" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G138" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H138" s="15" t="s">
         <v>13</v>
@@ -6913,13 +6919,13 @@
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D139" s="20" t="s">
         <v>25</v>
@@ -6928,10 +6934,10 @@
         <v>26</v>
       </c>
       <c r="F139" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H139" s="20" t="s">
         <v>13</v>
@@ -6939,13 +6945,13 @@
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>25</v>
@@ -6954,10 +6960,10 @@
         <v>26</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H140" s="15" t="s">
         <v>13</v>
@@ -6965,13 +6971,13 @@
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D141" s="20" t="s">
         <v>25</v>
@@ -6980,10 +6986,10 @@
         <v>26</v>
       </c>
       <c r="F141" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H141" s="20" t="s">
         <v>13</v>
@@ -6991,13 +6997,13 @@
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>25</v>
@@ -7006,10 +7012,10 @@
         <v>26</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H142" s="15" t="s">
         <v>13</v>
@@ -7017,13 +7023,13 @@
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D143" s="20" t="s">
         <v>25</v>
@@ -7032,10 +7038,10 @@
         <v>26</v>
       </c>
       <c r="F143" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G143" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H143" s="20" t="s">
         <v>13</v>
@@ -7043,13 +7049,13 @@
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>25</v>
@@ -7058,10 +7064,10 @@
         <v>26</v>
       </c>
       <c r="F144" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G144" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H144" s="15" t="s">
         <v>13</v>
@@ -7069,13 +7075,13 @@
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D145" s="20" t="s">
         <v>25</v>
@@ -7084,10 +7090,10 @@
         <v>26</v>
       </c>
       <c r="F145" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H145" s="20" t="s">
         <v>13</v>
@@ -7095,13 +7101,13 @@
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>25</v>
@@ -7110,10 +7116,10 @@
         <v>26</v>
       </c>
       <c r="F146" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G146" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H146" s="15" t="s">
         <v>13</v>
@@ -7121,13 +7127,13 @@
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D147" s="20" t="s">
         <v>25</v>
@@ -7136,10 +7142,10 @@
         <v>26</v>
       </c>
       <c r="F147" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G147" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H147" s="20" t="s">
         <v>13</v>
@@ -7147,13 +7153,13 @@
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D148" s="15" t="s">
         <v>25</v>
@@ -7162,10 +7168,10 @@
         <v>26</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H148" s="15" t="s">
         <v>13</v>
@@ -7173,13 +7179,13 @@
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D149" s="20" t="s">
         <v>25</v>
@@ -7188,10 +7194,10 @@
         <v>26</v>
       </c>
       <c r="F149" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G149" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H149" s="20" t="s">
         <v>13</v>
@@ -7199,13 +7205,13 @@
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>25</v>
@@ -7214,10 +7220,10 @@
         <v>26</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H150" s="15" t="s">
         <v>13</v>
@@ -7225,13 +7231,13 @@
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D151" s="20" t="s">
         <v>25</v>
@@ -7240,10 +7246,10 @@
         <v>26</v>
       </c>
       <c r="F151" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G151" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H151" s="20" t="s">
         <v>13</v>
@@ -7251,13 +7257,13 @@
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>25</v>
@@ -7266,10 +7272,10 @@
         <v>26</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G152" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H152" s="15" t="s">
         <v>13</v>
@@ -7277,13 +7283,13 @@
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B153" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D153" s="20" t="s">
         <v>25</v>
@@ -7292,10 +7298,10 @@
         <v>26</v>
       </c>
       <c r="F153" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H153" s="20" t="s">
         <v>13</v>
@@ -7303,13 +7309,13 @@
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D154" s="15" t="s">
         <v>25</v>
@@ -7318,10 +7324,10 @@
         <v>26</v>
       </c>
       <c r="F154" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G154" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H154" s="15" t="s">
         <v>13</v>
@@ -7329,13 +7335,13 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B155" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>25</v>
@@ -7344,10 +7350,10 @@
         <v>26</v>
       </c>
       <c r="F155" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G155" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H155" s="20" t="s">
         <v>13</v>
@@ -7355,13 +7361,13 @@
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D156" s="15" t="s">
         <v>25</v>
@@ -7370,10 +7376,10 @@
         <v>26</v>
       </c>
       <c r="F156" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H156" s="15" t="s">
         <v>13</v>
@@ -7381,13 +7387,13 @@
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D157" s="20" t="s">
         <v>25</v>
@@ -7396,10 +7402,10 @@
         <v>26</v>
       </c>
       <c r="F157" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H157" s="20" t="s">
         <v>13</v>
@@ -7407,13 +7413,13 @@
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D158" s="15" t="s">
         <v>25</v>
@@ -7422,10 +7428,10 @@
         <v>26</v>
       </c>
       <c r="F158" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H158" s="15" t="s">
         <v>13</v>
@@ -7433,13 +7439,13 @@
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C159" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D159" s="20" t="s">
         <v>25</v>
@@ -7448,10 +7454,10 @@
         <v>26</v>
       </c>
       <c r="F159" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H159" s="20" t="s">
         <v>13</v>
@@ -7459,13 +7465,13 @@
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D160" s="15" t="s">
         <v>25</v>
@@ -7474,10 +7480,10 @@
         <v>26</v>
       </c>
       <c r="F160" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H160" s="15" t="s">
         <v>13</v>
@@ -7485,13 +7491,13 @@
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B161" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C161" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D161" s="20" t="s">
         <v>25</v>
@@ -7500,10 +7506,10 @@
         <v>26</v>
       </c>
       <c r="F161" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H161" s="20" t="s">
         <v>13</v>
@@ -7511,13 +7517,13 @@
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D162" s="15" t="s">
         <v>25</v>
@@ -7526,10 +7532,10 @@
         <v>26</v>
       </c>
       <c r="F162" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H162" s="15" t="s">
         <v>13</v>
@@ -7537,13 +7543,13 @@
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B163" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C163" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D163" s="20" t="s">
         <v>25</v>
@@ -7552,10 +7558,10 @@
         <v>26</v>
       </c>
       <c r="F163" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G163" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H163" s="20" t="s">
         <v>13</v>
@@ -7563,13 +7569,13 @@
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D164" s="15" t="s">
         <v>25</v>
@@ -7578,10 +7584,10 @@
         <v>26</v>
       </c>
       <c r="F164" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G164" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H164" s="15" t="s">
         <v>13</v>
@@ -7589,13 +7595,13 @@
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B165" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D165" s="20" t="s">
         <v>25</v>
@@ -7604,10 +7610,10 @@
         <v>26</v>
       </c>
       <c r="F165" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G165" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H165" s="20" t="s">
         <v>13</v>
@@ -7615,13 +7621,13 @@
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D166" s="15" t="s">
         <v>25</v>
@@ -7630,10 +7636,10 @@
         <v>26</v>
       </c>
       <c r="F166" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G166" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H166" s="15" t="s">
         <v>13</v>
@@ -7641,13 +7647,13 @@
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>25</v>
@@ -7656,10 +7662,10 @@
         <v>26</v>
       </c>
       <c r="F167" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G167" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H167" s="20" t="s">
         <v>13</v>
@@ -7667,13 +7673,13 @@
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D168" s="15" t="s">
         <v>25</v>
@@ -7682,10 +7688,10 @@
         <v>26</v>
       </c>
       <c r="F168" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G168" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H168" s="15" t="s">
         <v>13</v>
@@ -7693,13 +7699,13 @@
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C169" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D169" s="20" t="s">
         <v>25</v>
@@ -7708,10 +7714,10 @@
         <v>26</v>
       </c>
       <c r="F169" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G169" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H169" s="20" t="s">
         <v>13</v>
@@ -7719,13 +7725,13 @@
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D170" s="15" t="s">
         <v>25</v>
@@ -7734,10 +7740,10 @@
         <v>26</v>
       </c>
       <c r="F170" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G170" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H170" s="15" t="s">
         <v>13</v>
@@ -7745,13 +7751,13 @@
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C171" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D171" s="20" t="s">
         <v>25</v>
@@ -7760,10 +7766,10 @@
         <v>26</v>
       </c>
       <c r="F171" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G171" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H171" s="20" t="s">
         <v>13</v>
@@ -7771,13 +7777,13 @@
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D172" s="15" t="s">
         <v>25</v>
@@ -7786,10 +7792,10 @@
         <v>26</v>
       </c>
       <c r="F172" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H172" s="15" t="s">
         <v>13</v>
@@ -7797,13 +7803,13 @@
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C173" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D173" s="20" t="s">
         <v>25</v>
@@ -7812,10 +7818,10 @@
         <v>26</v>
       </c>
       <c r="F173" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G173" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H173" s="20" t="s">
         <v>13</v>
@@ -7823,13 +7829,13 @@
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D174" s="15" t="s">
         <v>25</v>
@@ -7838,10 +7844,10 @@
         <v>26</v>
       </c>
       <c r="F174" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G174" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H174" s="15" t="s">
         <v>13</v>
@@ -7849,13 +7855,13 @@
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D175" s="20" t="s">
         <v>25</v>
@@ -7864,10 +7870,10 @@
         <v>26</v>
       </c>
       <c r="F175" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G175" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H175" s="20" t="s">
         <v>13</v>
@@ -7875,13 +7881,13 @@
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>25</v>
@@ -7890,10 +7896,10 @@
         <v>26</v>
       </c>
       <c r="F176" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H176" s="15" t="s">
         <v>13</v>
@@ -7901,13 +7907,13 @@
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B177" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D177" s="20" t="s">
         <v>25</v>
@@ -7916,10 +7922,10 @@
         <v>26</v>
       </c>
       <c r="F177" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G177" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H177" s="20" t="s">
         <v>13</v>
@@ -7927,13 +7933,13 @@
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D178" s="15" t="s">
         <v>25</v>
@@ -7942,10 +7948,10 @@
         <v>26</v>
       </c>
       <c r="F178" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G178" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H178" s="15" t="s">
         <v>13</v>
@@ -7953,13 +7959,13 @@
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B179" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C179" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D179" s="20" t="s">
         <v>25</v>
@@ -7968,10 +7974,10 @@
         <v>26</v>
       </c>
       <c r="F179" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G179" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H179" s="20" t="s">
         <v>13</v>
@@ -7979,13 +7985,13 @@
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D180" s="15" t="s">
         <v>25</v>
@@ -7994,10 +8000,10 @@
         <v>26</v>
       </c>
       <c r="F180" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H180" s="15" t="s">
         <v>13</v>
@@ -8005,13 +8011,13 @@
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D181" s="20" t="s">
         <v>25</v>
@@ -8020,10 +8026,10 @@
         <v>26</v>
       </c>
       <c r="F181" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H181" s="20" t="s">
         <v>13</v>
@@ -8031,13 +8037,13 @@
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D182" s="15" t="s">
         <v>25</v>
@@ -8046,10 +8052,10 @@
         <v>26</v>
       </c>
       <c r="F182" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G182" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H182" s="15" t="s">
         <v>13</v>
@@ -8057,13 +8063,13 @@
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B183" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C183" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D183" s="20" t="s">
         <v>25</v>
@@ -8072,10 +8078,10 @@
         <v>26</v>
       </c>
       <c r="F183" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G183" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H183" s="20" t="s">
         <v>13</v>
@@ -8083,13 +8089,13 @@
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D184" s="15" t="s">
         <v>25</v>
@@ -8098,10 +8104,10 @@
         <v>26</v>
       </c>
       <c r="F184" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G184" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H184" s="15" t="s">
         <v>13</v>
@@ -8109,13 +8115,13 @@
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C185" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D185" s="20" t="s">
         <v>25</v>
@@ -8124,10 +8130,10 @@
         <v>26</v>
       </c>
       <c r="F185" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G185" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H185" s="20" t="s">
         <v>13</v>
@@ -8135,13 +8141,13 @@
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D186" s="15" t="s">
         <v>25</v>
@@ -8150,10 +8156,10 @@
         <v>26</v>
       </c>
       <c r="F186" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G186" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H186" s="15" t="s">
         <v>13</v>
@@ -8161,13 +8167,13 @@
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B187" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C187" s="19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D187" s="20" t="s">
         <v>25</v>
@@ -8176,10 +8182,10 @@
         <v>26</v>
       </c>
       <c r="F187" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H187" s="20" t="s">
         <v>13</v>
@@ -8187,13 +8193,13 @@
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D188" s="15" t="s">
         <v>25</v>
@@ -8202,10 +8208,10 @@
         <v>26</v>
       </c>
       <c r="F188" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G188" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H188" s="15" t="s">
         <v>13</v>
@@ -8213,13 +8219,13 @@
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="17" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C189" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D189" s="20" t="s">
         <v>25</v>
@@ -8228,10 +8234,10 @@
         <v>26</v>
       </c>
       <c r="F189" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G189" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H189" s="20" t="s">
         <v>13</v>
@@ -8239,13 +8245,13 @@
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D190" s="15" t="s">
         <v>25</v>
@@ -8254,10 +8260,10 @@
         <v>26</v>
       </c>
       <c r="F190" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G190" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H190" s="15" t="s">
         <v>13</v>
@@ -8265,13 +8271,13 @@
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C191" s="19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D191" s="20" t="s">
         <v>25</v>
@@ -8280,10 +8286,10 @@
         <v>26</v>
       </c>
       <c r="F191" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G191" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H191" s="20" t="s">
         <v>13</v>
@@ -8291,13 +8297,13 @@
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D192" s="15" t="s">
         <v>25</v>
@@ -8306,10 +8312,10 @@
         <v>26</v>
       </c>
       <c r="F192" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G192" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H192" s="15" t="s">
         <v>13</v>
@@ -8317,13 +8323,13 @@
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B193" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C193" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D193" s="20" t="s">
         <v>25</v>
@@ -8332,10 +8338,10 @@
         <v>26</v>
       </c>
       <c r="F193" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G193" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H193" s="20" t="s">
         <v>13</v>
@@ -8343,13 +8349,13 @@
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D194" s="15" t="s">
         <v>25</v>
@@ -8358,10 +8364,10 @@
         <v>26</v>
       </c>
       <c r="F194" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G194" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H194" s="15" t="s">
         <v>13</v>
@@ -8369,13 +8375,13 @@
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C195" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D195" s="20" t="s">
         <v>25</v>
@@ -8384,10 +8390,10 @@
         <v>26</v>
       </c>
       <c r="F195" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G195" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H195" s="20" t="s">
         <v>13</v>
@@ -8395,13 +8401,13 @@
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D196" s="15" t="s">
         <v>25</v>
@@ -8410,10 +8416,10 @@
         <v>26</v>
       </c>
       <c r="F196" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G196" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H196" s="15" t="s">
         <v>13</v>
@@ -8421,13 +8427,13 @@
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="17" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B197" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C197" s="19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D197" s="20" t="s">
         <v>25</v>
@@ -8436,10 +8442,10 @@
         <v>26</v>
       </c>
       <c r="F197" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G197" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H197" s="20" t="s">
         <v>13</v>
@@ -8447,13 +8453,13 @@
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D198" s="15" t="s">
         <v>25</v>
@@ -8462,10 +8468,10 @@
         <v>26</v>
       </c>
       <c r="F198" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G198" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H198" s="15" t="s">
         <v>13</v>
@@ -8473,13 +8479,13 @@
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B199" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C199" s="19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D199" s="20" t="s">
         <v>25</v>
@@ -8488,10 +8494,10 @@
         <v>26</v>
       </c>
       <c r="F199" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G199" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H199" s="20" t="s">
         <v>13</v>
@@ -8499,13 +8505,13 @@
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D200" s="15" t="s">
         <v>25</v>
@@ -8514,10 +8520,10 @@
         <v>26</v>
       </c>
       <c r="F200" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G200" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H200" s="15" t="s">
         <v>13</v>
@@ -8525,13 +8531,13 @@
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B201" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C201" s="19" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D201" s="20" t="s">
         <v>25</v>
@@ -8540,10 +8546,10 @@
         <v>26</v>
       </c>
       <c r="F201" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G201" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H201" s="20" t="s">
         <v>13</v>
@@ -8551,13 +8557,13 @@
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D202" s="15" t="s">
         <v>25</v>
@@ -8566,10 +8572,10 @@
         <v>26</v>
       </c>
       <c r="F202" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G202" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H202" s="15" t="s">
         <v>13</v>
@@ -8577,13 +8583,13 @@
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B203" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C203" s="19" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D203" s="20" t="s">
         <v>25</v>
@@ -8592,10 +8598,10 @@
         <v>26</v>
       </c>
       <c r="F203" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G203" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H203" s="20" t="s">
         <v>13</v>
@@ -8603,13 +8609,13 @@
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B204" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D204" s="15" t="s">
         <v>25</v>
@@ -8618,10 +8624,10 @@
         <v>26</v>
       </c>
       <c r="F204" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G204" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H204" s="15" t="s">
         <v>13</v>
@@ -8629,13 +8635,13 @@
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B205" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C205" s="19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D205" s="20" t="s">
         <v>25</v>
@@ -8644,10 +8650,10 @@
         <v>26</v>
       </c>
       <c r="F205" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G205" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H205" s="20" t="s">
         <v>13</v>
@@ -8655,13 +8661,13 @@
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B206" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D206" s="15" t="s">
         <v>25</v>
@@ -8670,10 +8676,10 @@
         <v>26</v>
       </c>
       <c r="F206" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G206" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H206" s="15" t="s">
         <v>13</v>
@@ -8681,13 +8687,13 @@
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B207" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C207" s="19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D207" s="20" t="s">
         <v>25</v>
@@ -8696,10 +8702,10 @@
         <v>26</v>
       </c>
       <c r="F207" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G207" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H207" s="20" t="s">
         <v>13</v>
@@ -8707,13 +8713,13 @@
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B208" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D208" s="15" t="s">
         <v>25</v>
@@ -8722,24 +8728,24 @@
         <v>26</v>
       </c>
       <c r="F208" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G208" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H208" s="15" t="s">
-        <v>13</v>
+        <v>443</v>
       </c>
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="17" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B209" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C209" s="19" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D209" s="20" t="s">
         <v>25</v>
@@ -8748,10 +8754,10 @@
         <v>26</v>
       </c>
       <c r="F209" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G209" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H209" s="20" t="s">
         <v>13</v>
@@ -8759,13 +8765,13 @@
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B210" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D210" s="15" t="s">
         <v>25</v>
@@ -8774,10 +8780,10 @@
         <v>26</v>
       </c>
       <c r="F210" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G210" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H210" s="15" t="s">
         <v>13</v>
@@ -8785,13 +8791,13 @@
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="17" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B211" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D211" s="20" t="s">
         <v>25</v>
@@ -8800,10 +8806,10 @@
         <v>26</v>
       </c>
       <c r="F211" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G211" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H211" s="20" t="s">
         <v>13</v>
@@ -8811,13 +8817,13 @@
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D212" s="15" t="s">
         <v>25</v>
@@ -8826,10 +8832,10 @@
         <v>26</v>
       </c>
       <c r="F212" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G212" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H212" s="15" t="s">
         <v>13</v>
@@ -8837,13 +8843,13 @@
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="B213" s="18" t="s">
         <v>451</v>
       </c>
-      <c r="B213" s="18" t="s">
-        <v>449</v>
-      </c>
       <c r="C213" s="19" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D213" s="20" t="s">
         <v>25</v>
@@ -8852,10 +8858,10 @@
         <v>26</v>
       </c>
       <c r="F213" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G213" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H213" s="20" t="s">
         <v>13</v>
@@ -8863,13 +8869,13 @@
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D214" s="15" t="s">
         <v>25</v>
@@ -8878,10 +8884,10 @@
         <v>26</v>
       </c>
       <c r="F214" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G214" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H214" s="15" t="s">
         <v>13</v>
@@ -8889,13 +8895,13 @@
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="17" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B215" s="18" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C215" s="19" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D215" s="20" t="s">
         <v>25</v>
@@ -8904,10 +8910,10 @@
         <v>26</v>
       </c>
       <c r="F215" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G215" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H215" s="20" t="s">
         <v>13</v>
@@ -8915,13 +8921,13 @@
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D216" s="15" t="s">
         <v>25</v>
@@ -8930,10 +8936,10 @@
         <v>26</v>
       </c>
       <c r="F216" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G216" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H216" s="15" t="s">
         <v>13</v>
@@ -8941,13 +8947,13 @@
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="17" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B217" s="18" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C217" s="19" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D217" s="20" t="s">
         <v>25</v>
@@ -8956,10 +8962,10 @@
         <v>26</v>
       </c>
       <c r="F217" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G217" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H217" s="20" t="s">
         <v>13</v>
@@ -8967,13 +8973,13 @@
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D218" s="15" t="s">
         <v>25</v>
@@ -8982,10 +8988,10 @@
         <v>26</v>
       </c>
       <c r="F218" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G218" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H218" s="15" t="s">
         <v>13</v>
@@ -8993,13 +8999,13 @@
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="17" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B219" s="18" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>25</v>
@@ -9008,10 +9014,10 @@
         <v>26</v>
       </c>
       <c r="F219" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G219" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H219" s="20" t="s">
         <v>13</v>
@@ -9019,13 +9025,13 @@
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D220" s="15" t="s">
         <v>25</v>
@@ -9034,10 +9040,10 @@
         <v>26</v>
       </c>
       <c r="F220" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G220" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H220" s="15" t="s">
         <v>13</v>
@@ -9045,13 +9051,13 @@
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="17" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B221" s="18" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C221" s="19" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D221" s="20" t="s">
         <v>25</v>
@@ -9060,10 +9066,10 @@
         <v>26</v>
       </c>
       <c r="F221" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G221" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H221" s="20" t="s">
         <v>13</v>
@@ -9071,13 +9077,13 @@
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B222" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D222" s="15" t="s">
         <v>25</v>
@@ -9086,10 +9092,10 @@
         <v>26</v>
       </c>
       <c r="F222" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G222" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H222" s="15" t="s">
         <v>13</v>
@@ -9097,13 +9103,13 @@
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="17" t="s">
+        <v>474</v>
+      </c>
+      <c r="B223" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="B223" s="18" t="s">
-        <v>470</v>
-      </c>
       <c r="C223" s="19" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D223" s="20" t="s">
         <v>25</v>
@@ -9112,10 +9118,10 @@
         <v>26</v>
       </c>
       <c r="F223" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G223" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H223" s="20" t="s">
         <v>13</v>
@@ -9123,13 +9129,13 @@
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D224" s="15" t="s">
         <v>25</v>
@@ -9138,10 +9144,10 @@
         <v>26</v>
       </c>
       <c r="F224" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G224" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H224" s="15" t="s">
         <v>13</v>
@@ -9149,13 +9155,13 @@
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="17" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B225" s="18" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D225" s="20" t="s">
         <v>25</v>
@@ -9164,10 +9170,10 @@
         <v>26</v>
       </c>
       <c r="F225" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G225" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H225" s="20" t="s">
         <v>13</v>
@@ -9175,13 +9181,13 @@
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D226" s="15" t="s">
         <v>25</v>
@@ -9190,10 +9196,10 @@
         <v>26</v>
       </c>
       <c r="F226" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G226" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H226" s="15" t="s">
         <v>13</v>
@@ -9201,13 +9207,13 @@
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="17" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B227" s="18" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C227" s="19" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>25</v>
@@ -9216,10 +9222,10 @@
         <v>26</v>
       </c>
       <c r="F227" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G227" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H227" s="20" t="s">
         <v>13</v>
@@ -9227,13 +9233,13 @@
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D228" s="15" t="s">
         <v>25</v>
@@ -9242,10 +9248,10 @@
         <v>26</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G228" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H228" s="15" t="s">
         <v>13</v>
@@ -9253,13 +9259,13 @@
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="17" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B229" s="18" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C229" s="19" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>25</v>
@@ -9268,10 +9274,10 @@
         <v>26</v>
       </c>
       <c r="F229" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G229" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H229" s="20" t="s">
         <v>13</v>
@@ -9279,13 +9285,13 @@
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B230" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D230" s="15" t="s">
         <v>25</v>
@@ -9294,10 +9300,10 @@
         <v>26</v>
       </c>
       <c r="F230" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G230" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H230" s="15" t="s">
         <v>13</v>
@@ -9305,13 +9311,13 @@
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="17" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B231" s="18" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C231" s="19" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D231" s="20" t="s">
         <v>25</v>
@@ -9320,10 +9326,10 @@
         <v>26</v>
       </c>
       <c r="F231" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G231" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H231" s="20" t="s">
         <v>13</v>
@@ -9331,13 +9337,13 @@
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B232" s="13" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D232" s="15" t="s">
         <v>25</v>
@@ -9346,10 +9352,10 @@
         <v>26</v>
       </c>
       <c r="F232" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G232" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H232" s="15" t="s">
         <v>13</v>
@@ -9357,13 +9363,13 @@
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="B233" s="18" t="s">
         <v>493</v>
       </c>
-      <c r="B233" s="18" t="s">
-        <v>491</v>
-      </c>
       <c r="C233" s="19" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>25</v>
@@ -9372,10 +9378,10 @@
         <v>26</v>
       </c>
       <c r="F233" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G233" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H233" s="20" t="s">
         <v>13</v>
@@ -9383,13 +9389,13 @@
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>25</v>
@@ -9398,10 +9404,10 @@
         <v>26</v>
       </c>
       <c r="F234" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G234" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H234" s="15" t="s">
         <v>13</v>
@@ -9409,13 +9415,13 @@
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="17" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B235" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C235" s="19" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>25</v>
@@ -9424,10 +9430,10 @@
         <v>26</v>
       </c>
       <c r="F235" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G235" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H235" s="20" t="s">
         <v>13</v>
@@ -9435,13 +9441,13 @@
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C236" s="14" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D236" s="15" t="s">
         <v>25</v>
@@ -9450,10 +9456,10 @@
         <v>26</v>
       </c>
       <c r="F236" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G236" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H236" s="15" t="s">
         <v>13</v>
@@ -9461,13 +9467,13 @@
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="17" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B237" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C237" s="19" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>25</v>
@@ -9476,10 +9482,10 @@
         <v>26</v>
       </c>
       <c r="F237" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G237" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H237" s="20" t="s">
         <v>13</v>
@@ -9487,13 +9493,13 @@
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B238" s="13" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>25</v>
@@ -9502,10 +9508,10 @@
         <v>26</v>
       </c>
       <c r="F238" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G238" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H238" s="15" t="s">
         <v>13</v>
@@ -9513,13 +9519,13 @@
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="17" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B239" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C239" s="19" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>25</v>
@@ -9528,10 +9534,10 @@
         <v>26</v>
       </c>
       <c r="F239" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G239" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H239" s="20" t="s">
         <v>13</v>
@@ -9539,13 +9545,13 @@
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B240" s="13" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D240" s="15" t="s">
         <v>25</v>
@@ -9554,10 +9560,10 @@
         <v>26</v>
       </c>
       <c r="F240" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G240" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H240" s="15" t="s">
         <v>13</v>
@@ -9565,13 +9571,13 @@
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B241" s="18" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C241" s="19" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>25</v>
@@ -9580,10 +9586,10 @@
         <v>26</v>
       </c>
       <c r="F241" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G241" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H241" s="20" t="s">
         <v>13</v>
@@ -9591,13 +9597,13 @@
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B242" s="13" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D242" s="15" t="s">
         <v>25</v>
@@ -9606,10 +9612,10 @@
         <v>26</v>
       </c>
       <c r="F242" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G242" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H242" s="15" t="s">
         <v>13</v>
@@ -9617,13 +9623,13 @@
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="B243" s="18" t="s">
         <v>514</v>
       </c>
-      <c r="B243" s="18" t="s">
-        <v>512</v>
-      </c>
       <c r="C243" s="19" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>25</v>
@@ -9632,10 +9638,10 @@
         <v>26</v>
       </c>
       <c r="F243" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G243" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H243" s="20" t="s">
         <v>13</v>
@@ -9643,13 +9649,13 @@
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D244" s="15" t="s">
         <v>25</v>
@@ -9658,10 +9664,10 @@
         <v>26</v>
       </c>
       <c r="F244" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G244" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H244" s="15" t="s">
         <v>13</v>
@@ -9669,13 +9675,13 @@
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="17" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B245" s="18" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C245" s="19" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D245" s="20" t="s">
         <v>25</v>
@@ -9684,10 +9690,10 @@
         <v>26</v>
       </c>
       <c r="F245" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G245" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H245" s="20" t="s">
         <v>13</v>
@@ -9695,13 +9701,13 @@
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D246" s="15" t="s">
         <v>25</v>
@@ -9710,10 +9716,10 @@
         <v>26</v>
       </c>
       <c r="F246" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G246" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H246" s="15" t="s">
         <v>13</v>
@@ -9721,13 +9727,13 @@
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="17" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C247" s="19" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D247" s="20" t="s">
         <v>25</v>
@@ -9736,10 +9742,10 @@
         <v>26</v>
       </c>
       <c r="F247" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G247" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H247" s="20" t="s">
         <v>13</v>
@@ -9747,13 +9753,13 @@
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D248" s="15" t="s">
         <v>25</v>
@@ -9762,10 +9768,10 @@
         <v>26</v>
       </c>
       <c r="F248" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G248" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H248" s="15" t="s">
         <v>13</v>
@@ -9773,13 +9779,13 @@
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="17" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C249" s="19" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D249" s="20" t="s">
         <v>25</v>
@@ -9788,10 +9794,10 @@
         <v>26</v>
       </c>
       <c r="F249" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G249" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H249" s="20" t="s">
         <v>13</v>
@@ -9799,13 +9805,13 @@
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D250" s="15" t="s">
         <v>25</v>
@@ -9814,10 +9820,10 @@
         <v>26</v>
       </c>
       <c r="F250" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G250" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H250" s="15" t="s">
         <v>13</v>
@@ -9825,13 +9831,13 @@
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="17" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C251" s="19" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D251" s="20" t="s">
         <v>25</v>
@@ -9840,10 +9846,10 @@
         <v>26</v>
       </c>
       <c r="F251" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G251" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H251" s="20" t="s">
         <v>13</v>
@@ -9851,13 +9857,13 @@
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B252" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D252" s="15" t="s">
         <v>25</v>
@@ -9866,10 +9872,10 @@
         <v>26</v>
       </c>
       <c r="F252" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G252" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H252" s="15" t="s">
         <v>13</v>
@@ -9877,13 +9883,13 @@
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="B253" s="18" t="s">
         <v>535</v>
       </c>
-      <c r="B253" s="18" t="s">
-        <v>533</v>
-      </c>
       <c r="C253" s="19" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>25</v>
@@ -9892,10 +9898,10 @@
         <v>26</v>
       </c>
       <c r="F253" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G253" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H253" s="20" t="s">
         <v>13</v>
@@ -9903,13 +9909,13 @@
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D254" s="15" t="s">
         <v>25</v>
@@ -9918,10 +9924,10 @@
         <v>26</v>
       </c>
       <c r="F254" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G254" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H254" s="15" t="s">
         <v>13</v>
@@ -9929,13 +9935,13 @@
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="17" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C255" s="19" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D255" s="20" t="s">
         <v>25</v>
@@ -9944,10 +9950,10 @@
         <v>26</v>
       </c>
       <c r="F255" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G255" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H255" s="20" t="s">
         <v>13</v>
@@ -9955,13 +9961,13 @@
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B256" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D256" s="15" t="s">
         <v>25</v>
@@ -9970,10 +9976,10 @@
         <v>26</v>
       </c>
       <c r="F256" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G256" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H256" s="15" t="s">
         <v>13</v>
@@ -9981,13 +9987,13 @@
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="17" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B257" s="18" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C257" s="19" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D257" s="20" t="s">
         <v>25</v>
@@ -9996,10 +10002,10 @@
         <v>26</v>
       </c>
       <c r="F257" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G257" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H257" s="20" t="s">
         <v>13</v>
@@ -10007,13 +10013,13 @@
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B258" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D258" s="15" t="s">
         <v>25</v>
@@ -10022,10 +10028,10 @@
         <v>26</v>
       </c>
       <c r="F258" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G258" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H258" s="15" t="s">
         <v>13</v>
@@ -10033,13 +10039,13 @@
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="17" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B259" s="18" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C259" s="19" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D259" s="20" t="s">
         <v>25</v>
@@ -10048,10 +10054,10 @@
         <v>26</v>
       </c>
       <c r="F259" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G259" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H259" s="20" t="s">
         <v>13</v>
@@ -10059,13 +10065,13 @@
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B260" s="13" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D260" s="15" t="s">
         <v>25</v>
@@ -10074,10 +10080,10 @@
         <v>26</v>
       </c>
       <c r="F260" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G260" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H260" s="15" t="s">
         <v>13</v>
@@ -10085,13 +10091,13 @@
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="17" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B261" s="18" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C261" s="19" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D261" s="20" t="s">
         <v>25</v>
@@ -10100,10 +10106,10 @@
         <v>26</v>
       </c>
       <c r="F261" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G261" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H261" s="20" t="s">
         <v>13</v>
@@ -10111,13 +10117,13 @@
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B262" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D262" s="15" t="s">
         <v>25</v>
@@ -10126,10 +10132,10 @@
         <v>26</v>
       </c>
       <c r="F262" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G262" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H262" s="15" t="s">
         <v>13</v>
@@ -10137,13 +10143,13 @@
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="17" t="s">
+        <v>558</v>
+      </c>
+      <c r="B263" s="18" t="s">
         <v>556</v>
       </c>
-      <c r="B263" s="18" t="s">
-        <v>554</v>
-      </c>
       <c r="C263" s="19" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D263" s="20" t="s">
         <v>25</v>
@@ -10152,10 +10158,10 @@
         <v>26</v>
       </c>
       <c r="F263" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G263" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H263" s="20" t="s">
         <v>13</v>
@@ -10163,13 +10169,13 @@
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B264" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C264" s="14" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D264" s="15" t="s">
         <v>25</v>
@@ -10178,10 +10184,10 @@
         <v>26</v>
       </c>
       <c r="F264" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G264" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H264" s="15" t="s">
         <v>13</v>
@@ -10189,13 +10195,13 @@
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="17" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B265" s="18" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C265" s="19" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D265" s="20" t="s">
         <v>25</v>
@@ -10204,10 +10210,10 @@
         <v>26</v>
       </c>
       <c r="F265" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G265" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H265" s="20" t="s">
         <v>13</v>
@@ -10215,13 +10221,13 @@
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D266" s="15" t="s">
         <v>25</v>
@@ -10230,10 +10236,10 @@
         <v>26</v>
       </c>
       <c r="F266" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G266" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H266" s="15" t="s">
         <v>13</v>
@@ -10241,13 +10247,13 @@
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="17" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B267" s="18" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C267" s="19" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D267" s="20" t="s">
         <v>25</v>
@@ -10256,10 +10262,10 @@
         <v>26</v>
       </c>
       <c r="F267" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G267" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H267" s="20" t="s">
         <v>13</v>
@@ -10267,13 +10273,13 @@
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>25</v>
@@ -10282,10 +10288,10 @@
         <v>26</v>
       </c>
       <c r="F268" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G268" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H268" s="15" t="s">
         <v>13</v>
@@ -10293,13 +10299,13 @@
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="17" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B269" s="18" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C269" s="19" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D269" s="20" t="s">
         <v>25</v>
@@ -10308,10 +10314,10 @@
         <v>26</v>
       </c>
       <c r="F269" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G269" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H269" s="20" t="s">
         <v>13</v>
@@ -10319,13 +10325,13 @@
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D270" s="15" t="s">
         <v>25</v>
@@ -10334,10 +10340,10 @@
         <v>26</v>
       </c>
       <c r="F270" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G270" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H270" s="15" t="s">
         <v>13</v>
@@ -10345,13 +10351,13 @@
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="17" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B271" s="18" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C271" s="19" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D271" s="20" t="s">
         <v>25</v>
@@ -10360,10 +10366,10 @@
         <v>26</v>
       </c>
       <c r="F271" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G271" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H271" s="20" t="s">
         <v>13</v>
@@ -10371,13 +10377,13 @@
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B272" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C272" s="14" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D272" s="15" t="s">
         <v>25</v>
@@ -10386,10 +10392,10 @@
         <v>26</v>
       </c>
       <c r="F272" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G272" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H272" s="15" t="s">
         <v>13</v>
@@ -10397,13 +10403,13 @@
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
+        <v>579</v>
+      </c>
+      <c r="B273" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="B273" s="18" t="s">
-        <v>575</v>
-      </c>
       <c r="C273" s="19" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D273" s="20" t="s">
         <v>25</v>
@@ -10412,10 +10418,10 @@
         <v>26</v>
       </c>
       <c r="F273" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G273" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H273" s="20" t="s">
         <v>13</v>
@@ -10423,13 +10429,13 @@
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B274" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D274" s="15" t="s">
         <v>25</v>
@@ -10438,10 +10444,10 @@
         <v>26</v>
       </c>
       <c r="F274" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G274" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H274" s="15" t="s">
         <v>13</v>
@@ -10449,13 +10455,13 @@
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="17" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B275" s="18" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C275" s="19" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D275" s="20" t="s">
         <v>25</v>
@@ -10464,10 +10470,10 @@
         <v>26</v>
       </c>
       <c r="F275" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G275" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H275" s="20" t="s">
         <v>13</v>
@@ -10475,13 +10481,13 @@
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D276" s="15" t="s">
         <v>25</v>
@@ -10490,10 +10496,10 @@
         <v>26</v>
       </c>
       <c r="F276" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G276" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H276" s="15" t="s">
         <v>13</v>
@@ -10501,13 +10507,13 @@
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="17" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B277" s="18" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C277" s="19" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D277" s="20" t="s">
         <v>25</v>
@@ -10516,10 +10522,10 @@
         <v>26</v>
       </c>
       <c r="F277" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G277" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H277" s="20" t="s">
         <v>13</v>
@@ -10527,13 +10533,13 @@
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B278" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D278" s="15" t="s">
         <v>25</v>
@@ -10542,10 +10548,10 @@
         <v>26</v>
       </c>
       <c r="F278" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G278" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H278" s="15" t="s">
         <v>13</v>
@@ -10553,13 +10559,13 @@
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B279" s="18" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C279" s="19" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D279" s="20" t="s">
         <v>25</v>
@@ -10568,10 +10574,10 @@
         <v>26</v>
       </c>
       <c r="F279" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G279" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H279" s="20" t="s">
         <v>13</v>
@@ -10579,13 +10585,13 @@
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="D280" s="15" t="s">
         <v>25</v>
@@ -10594,10 +10600,10 @@
         <v>26</v>
       </c>
       <c r="F280" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G280" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H280" s="15" t="s">
         <v>13</v>
@@ -10605,13 +10611,13 @@
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="17" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B281" s="18" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C281" s="19" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D281" s="20" t="s">
         <v>25</v>
@@ -10620,10 +10626,10 @@
         <v>26</v>
       </c>
       <c r="F281" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G281" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H281" s="20" t="s">
         <v>13</v>
@@ -10631,13 +10637,13 @@
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B282" s="13" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C282" s="14" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D282" s="15" t="s">
         <v>25</v>
@@ -10646,10 +10652,10 @@
         <v>26</v>
       </c>
       <c r="F282" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G282" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H282" s="15" t="s">
         <v>13</v>
@@ -10657,13 +10663,13 @@
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="B283" s="18" t="s">
         <v>598</v>
       </c>
-      <c r="B283" s="18" t="s">
-        <v>596</v>
-      </c>
       <c r="C283" s="19" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D283" s="20" t="s">
         <v>25</v>
@@ -10672,10 +10678,10 @@
         <v>26</v>
       </c>
       <c r="F283" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G283" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H283" s="20" t="s">
         <v>13</v>
@@ -10683,13 +10689,13 @@
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D284" s="15" t="s">
         <v>25</v>
@@ -10698,10 +10704,10 @@
         <v>26</v>
       </c>
       <c r="F284" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G284" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H284" s="15" t="s">
         <v>13</v>
@@ -10709,13 +10715,13 @@
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="17" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B285" s="18" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C285" s="19" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D285" s="20" t="s">
         <v>25</v>
@@ -10724,10 +10730,10 @@
         <v>26</v>
       </c>
       <c r="F285" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G285" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H285" s="20" t="s">
         <v>13</v>
@@ -10735,13 +10741,13 @@
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B286" s="13" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D286" s="15" t="s">
         <v>25</v>
@@ -10750,10 +10756,10 @@
         <v>26</v>
       </c>
       <c r="F286" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G286" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H286" s="15" t="s">
         <v>13</v>
@@ -10761,13 +10767,13 @@
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="17" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B287" s="18" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C287" s="19" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D287" s="20" t="s">
         <v>25</v>
@@ -10776,10 +10782,10 @@
         <v>26</v>
       </c>
       <c r="F287" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G287" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H287" s="20" t="s">
         <v>13</v>
@@ -10787,13 +10793,13 @@
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B288" s="13" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D288" s="15" t="s">
         <v>25</v>
@@ -10802,10 +10808,10 @@
         <v>26</v>
       </c>
       <c r="F288" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G288" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H288" s="15" t="s">
         <v>13</v>
@@ -10813,13 +10819,13 @@
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="17" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B289" s="18" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C289" s="19" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D289" s="20" t="s">
         <v>25</v>
@@ -10828,10 +10834,10 @@
         <v>26</v>
       </c>
       <c r="F289" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G289" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H289" s="20" t="s">
         <v>13</v>
@@ -10839,13 +10845,13 @@
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B290" s="13" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D290" s="15" t="s">
         <v>25</v>
@@ -10854,10 +10860,10 @@
         <v>26</v>
       </c>
       <c r="F290" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G290" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H290" s="15" t="s">
         <v>13</v>
@@ -10865,13 +10871,13 @@
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="17" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B291" s="18" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C291" s="19" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D291" s="20" t="s">
         <v>25</v>
@@ -10880,10 +10886,10 @@
         <v>26</v>
       </c>
       <c r="F291" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G291" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H291" s="20" t="s">
         <v>13</v>
@@ -10891,13 +10897,13 @@
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B292" s="13" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C292" s="14" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D292" s="15" t="s">
         <v>25</v>
@@ -10906,10 +10912,10 @@
         <v>26</v>
       </c>
       <c r="F292" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G292" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H292" s="15" t="s">
         <v>13</v>
@@ -10917,13 +10923,13 @@
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="17" t="s">
+        <v>621</v>
+      </c>
+      <c r="B293" s="18" t="s">
         <v>619</v>
       </c>
-      <c r="B293" s="18" t="s">
-        <v>617</v>
-      </c>
       <c r="C293" s="19" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D293" s="20" t="s">
         <v>25</v>
@@ -10932,10 +10938,10 @@
         <v>26</v>
       </c>
       <c r="F293" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G293" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H293" s="20" t="s">
         <v>13</v>
@@ -10943,13 +10949,13 @@
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D294" s="15" t="s">
         <v>25</v>
@@ -10958,10 +10964,10 @@
         <v>26</v>
       </c>
       <c r="F294" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G294" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H294" s="15" t="s">
         <v>13</v>
@@ -10969,13 +10975,13 @@
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="17" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B295" s="18" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C295" s="19" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D295" s="20" t="s">
         <v>25</v>
@@ -10984,10 +10990,10 @@
         <v>26</v>
       </c>
       <c r="F295" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G295" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H295" s="20" t="s">
         <v>13</v>
@@ -10995,13 +11001,13 @@
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D296" s="15" t="s">
         <v>25</v>
@@ -11010,10 +11016,10 @@
         <v>26</v>
       </c>
       <c r="F296" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G296" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H296" s="15" t="s">
         <v>13</v>
@@ -11021,13 +11027,13 @@
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="17" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C297" s="19" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D297" s="20" t="s">
         <v>25</v>
@@ -11036,10 +11042,10 @@
         <v>26</v>
       </c>
       <c r="F297" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G297" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H297" s="20" t="s">
         <v>13</v>
@@ -11047,13 +11053,13 @@
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B298" s="13" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D298" s="15" t="s">
         <v>25</v>
@@ -11062,10 +11068,10 @@
         <v>26</v>
       </c>
       <c r="F298" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G298" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H298" s="15" t="s">
         <v>13</v>
@@ -11073,13 +11079,13 @@
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B299" s="18" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C299" s="19" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D299" s="20" t="s">
         <v>25</v>
@@ -11088,10 +11094,10 @@
         <v>26</v>
       </c>
       <c r="F299" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G299" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H299" s="20" t="s">
         <v>13</v>
@@ -11099,13 +11105,13 @@
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C300" s="14" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D300" s="15" t="s">
         <v>25</v>
@@ -11114,10 +11120,10 @@
         <v>26</v>
       </c>
       <c r="F300" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G300" s="15" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H300" s="15" t="s">
         <v>13</v>
@@ -11125,13 +11131,13 @@
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="17" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B301" s="18" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C301" s="19" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D301" s="20" t="s">
         <v>25</v>
@@ -11140,10 +11146,10 @@
         <v>26</v>
       </c>
       <c r="F301" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="G301" s="20" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="H301" s="20" t="s">
         <v>13</v>
@@ -11172,33 +11178,33 @@
         <v>16</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -11221,19 +11227,19 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11241,16 +11247,16 @@
         <v>27</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11258,16 +11264,16 @@
         <v>27</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>655</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>656</v>
+      </c>
+      <c r="D3" s="27" t="s">
         <v>653</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>654</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11275,16 +11281,16 @@
         <v>27</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11292,16 +11298,16 @@
         <v>27</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11309,16 +11315,16 @@
         <v>27</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11326,16 +11332,16 @@
         <v>27</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11343,16 +11349,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11360,16 +11366,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11377,16 +11383,16 @@
         <v>27</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11394,16 +11400,16 @@
         <v>27</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11411,16 +11417,16 @@
         <v>27</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11428,16 +11434,16 @@
         <v>27</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11445,16 +11451,16 @@
         <v>27</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11462,16 +11468,16 @@
         <v>27</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11479,16 +11485,16 @@
         <v>27</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11496,16 +11502,16 @@
         <v>27</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11513,16 +11519,16 @@
         <v>27</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11530,16 +11536,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11547,16 +11553,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11564,16 +11570,16 @@
         <v>27</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11581,16 +11587,16 @@
         <v>27</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11598,16 +11604,16 @@
         <v>27</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11615,16 +11621,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11632,16 +11638,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11649,16 +11655,16 @@
         <v>27</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11666,16 +11672,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11683,16 +11689,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C28" s="24" t="s">
+        <v>707</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>653</v>
+      </c>
+      <c r="E28" s="24" t="s">
         <v>705</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>651</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11700,16 +11706,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11717,16 +11723,16 @@
         <v>27</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11734,16 +11740,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11751,16 +11757,16 @@
         <v>27</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11768,16 +11774,16 @@
         <v>27</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11785,16 +11791,16 @@
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11802,16 +11808,16 @@
         <v>27</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11819,16 +11825,16 @@
         <v>27</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11836,16 +11842,16 @@
         <v>27</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11853,16 +11859,16 @@
         <v>27</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11870,16 +11876,16 @@
         <v>27</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11887,16 +11893,16 @@
         <v>27</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11904,16 +11910,16 @@
         <v>27</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11921,16 +11927,16 @@
         <v>27</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11938,16 +11944,16 @@
         <v>27</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11955,16 +11961,16 @@
         <v>27</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11972,16 +11978,16 @@
         <v>27</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11989,16 +11995,16 @@
         <v>27</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12006,16 +12012,16 @@
         <v>27</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12023,16 +12029,16 @@
         <v>27</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12040,16 +12046,16 @@
         <v>27</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12057,16 +12063,16 @@
         <v>27</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12074,866 +12080,866 @@
         <v>27</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C53" s="26" t="s">
+        <v>758</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>653</v>
+      </c>
+      <c r="E53" s="26" t="s">
         <v>756</v>
-      </c>
-      <c r="D53" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E53" s="26" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C63" s="26" t="s">
+        <v>779</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>653</v>
+      </c>
+      <c r="E63" s="26" t="s">
         <v>777</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E63" s="26" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E72" s="24" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C73" s="26" t="s">
+        <v>800</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>653</v>
+      </c>
+      <c r="E73" s="26" t="s">
         <v>798</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E73" s="26" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B82" s="24" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E82" s="24" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C83" s="26" t="s">
+        <v>821</v>
+      </c>
+      <c r="D83" s="27" t="s">
+        <v>653</v>
+      </c>
+      <c r="E83" s="26" t="s">
         <v>819</v>
-      </c>
-      <c r="D83" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E83" s="26" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B84" s="24" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E84" s="24" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B86" s="24" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B88" s="24" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B90" s="24" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B92" s="24" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E92" s="24" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B93" s="26" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C93" s="26" t="s">
+        <v>842</v>
+      </c>
+      <c r="D93" s="27" t="s">
+        <v>653</v>
+      </c>
+      <c r="E93" s="26" t="s">
         <v>840</v>
-      </c>
-      <c r="D93" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E93" s="26" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E94" s="24" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B95" s="26" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B96" s="24" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B98" s="24" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="24" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B100" s="24" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E100" s="24" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>27</v>
+        <v>243</v>
       </c>
       <c r="B101" s="26" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>

--- a/reports/excel/Vulnerability_Report.xlsx
+++ b/reports/excel/Vulnerability_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="857">
   <si>
     <t>📊 VULNERABILITY REPORT - AUTOMATION EXECUTION SUMMARY</t>
   </si>
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 04:37:21</t>
+    <t>2026-08-20 03:51:22</t>
   </si>
   <si>
     <t>TC-SEC-002</t>
@@ -745,9 +745,6 @@
     <t>Headers: Strict-Transport-Security (HSTS) configured for production</t>
   </si>
   <si>
-    <t>2026-08-20 04:37:22</t>
-  </si>
-  <si>
     <t>TC-SEC-106</t>
   </si>
   <si>
@@ -1343,9 +1340,6 @@
   </si>
   <si>
     <t>Path Traversal: Absolute path to /proc/self/environ</t>
-  </si>
-  <si>
-    <t>0.01s</t>
   </si>
   <si>
     <t>TC-SEC-208</t>
@@ -6079,7 +6073,7 @@
         <v>27</v>
       </c>
       <c r="G106" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H106" s="15" t="s">
         <v>13</v>
@@ -6087,13 +6081,13 @@
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B107" s="18" t="s">
         <v>233</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>25</v>
@@ -6102,10 +6096,10 @@
         <v>26</v>
       </c>
       <c r="F107" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G107" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H107" s="20" t="s">
         <v>13</v>
@@ -6113,13 +6107,13 @@
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B108" s="13" t="s">
         <v>233</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>25</v>
@@ -6128,10 +6122,10 @@
         <v>26</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H108" s="15" t="s">
         <v>13</v>
@@ -6139,13 +6133,13 @@
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B109" s="18" t="s">
         <v>233</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D109" s="20" t="s">
         <v>25</v>
@@ -6154,10 +6148,10 @@
         <v>26</v>
       </c>
       <c r="F109" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H109" s="20" t="s">
         <v>13</v>
@@ -6165,13 +6159,13 @@
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B110" s="13" t="s">
         <v>233</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>25</v>
@@ -6180,10 +6174,10 @@
         <v>26</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H110" s="15" t="s">
         <v>13</v>
@@ -6191,13 +6185,13 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B111" s="18" t="s">
         <v>233</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D111" s="20" t="s">
         <v>25</v>
@@ -6206,10 +6200,10 @@
         <v>26</v>
       </c>
       <c r="F111" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G111" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H111" s="20" t="s">
         <v>13</v>
@@ -6217,14 +6211,14 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B112" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="C112" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="C112" s="14" t="s">
-        <v>256</v>
-      </c>
       <c r="D112" s="15" t="s">
         <v>25</v>
       </c>
@@ -6232,10 +6226,10 @@
         <v>26</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H112" s="15" t="s">
         <v>13</v>
@@ -6243,14 +6237,14 @@
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C113" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="B113" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>258</v>
-      </c>
       <c r="D113" s="20" t="s">
         <v>25</v>
       </c>
@@ -6258,10 +6252,10 @@
         <v>26</v>
       </c>
       <c r="F113" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G113" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H113" s="20" t="s">
         <v>13</v>
@@ -6269,14 +6263,14 @@
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="B114" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C114" s="14" t="s">
-        <v>260</v>
-      </c>
       <c r="D114" s="15" t="s">
         <v>25</v>
       </c>
@@ -6284,10 +6278,10 @@
         <v>26</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H114" s="15" t="s">
         <v>13</v>
@@ -6295,14 +6289,14 @@
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="B115" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C115" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="B115" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>262</v>
-      </c>
       <c r="D115" s="20" t="s">
         <v>25</v>
       </c>
@@ -6310,10 +6304,10 @@
         <v>26</v>
       </c>
       <c r="F115" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G115" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H115" s="20" t="s">
         <v>13</v>
@@ -6321,14 +6315,14 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C116" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="B116" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C116" s="14" t="s">
-        <v>264</v>
-      </c>
       <c r="D116" s="15" t="s">
         <v>25</v>
       </c>
@@ -6336,10 +6330,10 @@
         <v>26</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H116" s="15" t="s">
         <v>13</v>
@@ -6347,14 +6341,14 @@
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="B117" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C117" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="B117" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C117" s="19" t="s">
-        <v>266</v>
-      </c>
       <c r="D117" s="20" t="s">
         <v>25</v>
       </c>
@@ -6362,10 +6356,10 @@
         <v>26</v>
       </c>
       <c r="F117" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G117" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H117" s="20" t="s">
         <v>13</v>
@@ -6373,14 +6367,14 @@
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B118" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C118" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="B118" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C118" s="14" t="s">
-        <v>268</v>
-      </c>
       <c r="D118" s="15" t="s">
         <v>25</v>
       </c>
@@ -6388,10 +6382,10 @@
         <v>26</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G118" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H118" s="15" t="s">
         <v>13</v>
@@ -6399,14 +6393,14 @@
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="B119" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C119" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="B119" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C119" s="19" t="s">
-        <v>270</v>
-      </c>
       <c r="D119" s="20" t="s">
         <v>25</v>
       </c>
@@ -6414,10 +6408,10 @@
         <v>26</v>
       </c>
       <c r="F119" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G119" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H119" s="20" t="s">
         <v>13</v>
@@ -6425,14 +6419,14 @@
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C120" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="B120" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C120" s="14" t="s">
-        <v>272</v>
-      </c>
       <c r="D120" s="15" t="s">
         <v>25</v>
       </c>
@@ -6440,10 +6434,10 @@
         <v>26</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H120" s="15" t="s">
         <v>13</v>
@@ -6451,14 +6445,14 @@
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="B121" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C121" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="B121" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C121" s="19" t="s">
-        <v>274</v>
-      </c>
       <c r="D121" s="20" t="s">
         <v>25</v>
       </c>
@@ -6466,10 +6460,10 @@
         <v>26</v>
       </c>
       <c r="F121" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G121" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H121" s="20" t="s">
         <v>13</v>
@@ -6477,14 +6471,14 @@
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B122" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="C122" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="C122" s="14" t="s">
-        <v>277</v>
-      </c>
       <c r="D122" s="15" t="s">
         <v>25</v>
       </c>
@@ -6492,10 +6486,10 @@
         <v>26</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H122" s="15" t="s">
         <v>13</v>
@@ -6503,14 +6497,14 @@
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="B123" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C123" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="B123" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C123" s="19" t="s">
-        <v>279</v>
-      </c>
       <c r="D123" s="20" t="s">
         <v>25</v>
       </c>
@@ -6518,10 +6512,10 @@
         <v>26</v>
       </c>
       <c r="F123" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G123" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H123" s="20" t="s">
         <v>13</v>
@@ -6529,14 +6523,14 @@
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C124" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="B124" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C124" s="14" t="s">
-        <v>281</v>
-      </c>
       <c r="D124" s="15" t="s">
         <v>25</v>
       </c>
@@ -6544,10 +6538,10 @@
         <v>26</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H124" s="15" t="s">
         <v>13</v>
@@ -6555,14 +6549,14 @@
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="B125" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C125" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="B125" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C125" s="19" t="s">
-        <v>283</v>
-      </c>
       <c r="D125" s="20" t="s">
         <v>25</v>
       </c>
@@ -6570,10 +6564,10 @@
         <v>26</v>
       </c>
       <c r="F125" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H125" s="20" t="s">
         <v>13</v>
@@ -6581,14 +6575,14 @@
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B126" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C126" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="B126" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C126" s="14" t="s">
-        <v>285</v>
-      </c>
       <c r="D126" s="15" t="s">
         <v>25</v>
       </c>
@@ -6596,10 +6590,10 @@
         <v>26</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H126" s="15" t="s">
         <v>13</v>
@@ -6607,14 +6601,14 @@
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="B127" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C127" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="B127" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C127" s="19" t="s">
-        <v>287</v>
-      </c>
       <c r="D127" s="20" t="s">
         <v>25</v>
       </c>
@@ -6622,10 +6616,10 @@
         <v>26</v>
       </c>
       <c r="F127" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G127" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H127" s="20" t="s">
         <v>13</v>
@@ -6633,14 +6627,14 @@
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="B128" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C128" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="B128" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C128" s="14" t="s">
-        <v>289</v>
-      </c>
       <c r="D128" s="15" t="s">
         <v>25</v>
       </c>
@@ -6648,10 +6642,10 @@
         <v>26</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G128" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H128" s="15" t="s">
         <v>13</v>
@@ -6659,14 +6653,14 @@
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="B129" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C129" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="B129" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C129" s="19" t="s">
-        <v>291</v>
-      </c>
       <c r="D129" s="20" t="s">
         <v>25</v>
       </c>
@@ -6674,10 +6668,10 @@
         <v>26</v>
       </c>
       <c r="F129" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G129" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H129" s="20" t="s">
         <v>13</v>
@@ -6685,14 +6679,14 @@
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B130" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C130" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="B130" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C130" s="14" t="s">
-        <v>293</v>
-      </c>
       <c r="D130" s="15" t="s">
         <v>25</v>
       </c>
@@ -6700,10 +6694,10 @@
         <v>26</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G130" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H130" s="15" t="s">
         <v>13</v>
@@ -6711,14 +6705,14 @@
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="B131" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C131" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="B131" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C131" s="19" t="s">
-        <v>295</v>
-      </c>
       <c r="D131" s="20" t="s">
         <v>25</v>
       </c>
@@ -6726,10 +6720,10 @@
         <v>26</v>
       </c>
       <c r="F131" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G131" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H131" s="20" t="s">
         <v>13</v>
@@ -6737,14 +6731,14 @@
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B132" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="C132" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C132" s="14" t="s">
-        <v>298</v>
-      </c>
       <c r="D132" s="15" t="s">
         <v>25</v>
       </c>
@@ -6752,10 +6746,10 @@
         <v>26</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G132" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H132" s="15" t="s">
         <v>13</v>
@@ -6763,14 +6757,14 @@
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B133" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C133" s="19" t="s">
         <v>299</v>
       </c>
-      <c r="B133" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C133" s="19" t="s">
-        <v>300</v>
-      </c>
       <c r="D133" s="20" t="s">
         <v>25</v>
       </c>
@@ -6778,10 +6772,10 @@
         <v>26</v>
       </c>
       <c r="F133" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G133" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H133" s="20" t="s">
         <v>13</v>
@@ -6789,14 +6783,14 @@
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="B134" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C134" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="B134" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C134" s="14" t="s">
-        <v>302</v>
-      </c>
       <c r="D134" s="15" t="s">
         <v>25</v>
       </c>
@@ -6804,10 +6798,10 @@
         <v>26</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G134" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H134" s="15" t="s">
         <v>13</v>
@@ -6815,14 +6809,14 @@
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="B135" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C135" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="B135" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C135" s="19" t="s">
-        <v>304</v>
-      </c>
       <c r="D135" s="20" t="s">
         <v>25</v>
       </c>
@@ -6830,10 +6824,10 @@
         <v>26</v>
       </c>
       <c r="F135" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H135" s="20" t="s">
         <v>13</v>
@@ -6841,14 +6835,14 @@
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C136" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="B136" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C136" s="14" t="s">
-        <v>306</v>
-      </c>
       <c r="D136" s="15" t="s">
         <v>25</v>
       </c>
@@ -6856,10 +6850,10 @@
         <v>26</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G136" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H136" s="15" t="s">
         <v>13</v>
@@ -6867,14 +6861,14 @@
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="B137" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C137" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="B137" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C137" s="19" t="s">
-        <v>308</v>
-      </c>
       <c r="D137" s="20" t="s">
         <v>25</v>
       </c>
@@ -6882,10 +6876,10 @@
         <v>26</v>
       </c>
       <c r="F137" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G137" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H137" s="20" t="s">
         <v>13</v>
@@ -6893,14 +6887,14 @@
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C138" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="B138" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C138" s="14" t="s">
-        <v>310</v>
-      </c>
       <c r="D138" s="15" t="s">
         <v>25</v>
       </c>
@@ -6908,10 +6902,10 @@
         <v>26</v>
       </c>
       <c r="F138" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G138" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H138" s="15" t="s">
         <v>13</v>
@@ -6919,14 +6913,14 @@
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B139" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C139" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="B139" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C139" s="19" t="s">
-        <v>312</v>
-      </c>
       <c r="D139" s="20" t="s">
         <v>25</v>
       </c>
@@ -6934,10 +6928,10 @@
         <v>26</v>
       </c>
       <c r="F139" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G139" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H139" s="20" t="s">
         <v>13</v>
@@ -6945,14 +6939,14 @@
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C140" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="B140" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C140" s="14" t="s">
-        <v>314</v>
-      </c>
       <c r="D140" s="15" t="s">
         <v>25</v>
       </c>
@@ -6960,10 +6954,10 @@
         <v>26</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H140" s="15" t="s">
         <v>13</v>
@@ -6971,14 +6965,14 @@
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="B141" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C141" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="B141" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C141" s="19" t="s">
-        <v>316</v>
-      </c>
       <c r="D141" s="20" t="s">
         <v>25</v>
       </c>
@@ -6986,10 +6980,10 @@
         <v>26</v>
       </c>
       <c r="F141" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G141" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H141" s="20" t="s">
         <v>13</v>
@@ -6997,14 +6991,14 @@
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B142" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="B142" s="13" t="s">
+      <c r="C142" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C142" s="14" t="s">
-        <v>319</v>
-      </c>
       <c r="D142" s="15" t="s">
         <v>25</v>
       </c>
@@ -7012,10 +7006,10 @@
         <v>26</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H142" s="15" t="s">
         <v>13</v>
@@ -7023,14 +7017,14 @@
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C143" s="19" t="s">
         <v>320</v>
       </c>
-      <c r="B143" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C143" s="19" t="s">
-        <v>321</v>
-      </c>
       <c r="D143" s="20" t="s">
         <v>25</v>
       </c>
@@ -7038,10 +7032,10 @@
         <v>26</v>
       </c>
       <c r="F143" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G143" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H143" s="20" t="s">
         <v>13</v>
@@ -7049,14 +7043,14 @@
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C144" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="B144" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="C144" s="14" t="s">
-        <v>323</v>
-      </c>
       <c r="D144" s="15" t="s">
         <v>25</v>
       </c>
@@ -7064,10 +7058,10 @@
         <v>26</v>
       </c>
       <c r="F144" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G144" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H144" s="15" t="s">
         <v>13</v>
@@ -7075,14 +7069,14 @@
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="B145" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C145" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="B145" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C145" s="19" t="s">
-        <v>325</v>
-      </c>
       <c r="D145" s="20" t="s">
         <v>25</v>
       </c>
@@ -7090,10 +7084,10 @@
         <v>26</v>
       </c>
       <c r="F145" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G145" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H145" s="20" t="s">
         <v>13</v>
@@ -7101,14 +7095,14 @@
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B146" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C146" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="B146" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="C146" s="14" t="s">
-        <v>327</v>
-      </c>
       <c r="D146" s="15" t="s">
         <v>25</v>
       </c>
@@ -7116,10 +7110,10 @@
         <v>26</v>
       </c>
       <c r="F146" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G146" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H146" s="15" t="s">
         <v>13</v>
@@ -7127,14 +7121,14 @@
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="B147" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C147" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="B147" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C147" s="19" t="s">
-        <v>329</v>
-      </c>
       <c r="D147" s="20" t="s">
         <v>25</v>
       </c>
@@ -7142,10 +7136,10 @@
         <v>26</v>
       </c>
       <c r="F147" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G147" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H147" s="20" t="s">
         <v>13</v>
@@ -7153,14 +7147,14 @@
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C148" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="B148" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="C148" s="14" t="s">
-        <v>331</v>
-      </c>
       <c r="D148" s="15" t="s">
         <v>25</v>
       </c>
@@ -7168,10 +7162,10 @@
         <v>26</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H148" s="15" t="s">
         <v>13</v>
@@ -7179,14 +7173,14 @@
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B149" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C149" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="B149" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C149" s="19" t="s">
-        <v>333</v>
-      </c>
       <c r="D149" s="20" t="s">
         <v>25</v>
       </c>
@@ -7194,10 +7188,10 @@
         <v>26</v>
       </c>
       <c r="F149" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G149" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H149" s="20" t="s">
         <v>13</v>
@@ -7205,14 +7199,14 @@
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B150" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C150" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="B150" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="C150" s="14" t="s">
-        <v>335</v>
-      </c>
       <c r="D150" s="15" t="s">
         <v>25</v>
       </c>
@@ -7220,10 +7214,10 @@
         <v>26</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H150" s="15" t="s">
         <v>13</v>
@@ -7231,14 +7225,14 @@
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C151" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="B151" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C151" s="19" t="s">
-        <v>337</v>
-      </c>
       <c r="D151" s="20" t="s">
         <v>25</v>
       </c>
@@ -7246,10 +7240,10 @@
         <v>26</v>
       </c>
       <c r="F151" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G151" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H151" s="20" t="s">
         <v>13</v>
@@ -7257,14 +7251,14 @@
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B152" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="B152" s="13" t="s">
+      <c r="C152" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="C152" s="14" t="s">
-        <v>340</v>
-      </c>
       <c r="D152" s="15" t="s">
         <v>25</v>
       </c>
@@ -7272,10 +7266,10 @@
         <v>26</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G152" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H152" s="15" t="s">
         <v>13</v>
@@ -7283,14 +7277,14 @@
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="B153" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C153" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="B153" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C153" s="19" t="s">
-        <v>342</v>
-      </c>
       <c r="D153" s="20" t="s">
         <v>25</v>
       </c>
@@ -7298,10 +7292,10 @@
         <v>26</v>
       </c>
       <c r="F153" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G153" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H153" s="20" t="s">
         <v>13</v>
@@ -7309,14 +7303,14 @@
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C154" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="B154" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C154" s="14" t="s">
-        <v>344</v>
-      </c>
       <c r="D154" s="15" t="s">
         <v>25</v>
       </c>
@@ -7324,10 +7318,10 @@
         <v>26</v>
       </c>
       <c r="F154" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G154" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H154" s="15" t="s">
         <v>13</v>
@@ -7335,14 +7329,14 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="B155" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C155" s="19" t="s">
         <v>345</v>
       </c>
-      <c r="B155" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C155" s="19" t="s">
-        <v>346</v>
-      </c>
       <c r="D155" s="20" t="s">
         <v>25</v>
       </c>
@@ -7350,10 +7344,10 @@
         <v>26</v>
       </c>
       <c r="F155" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G155" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H155" s="20" t="s">
         <v>13</v>
@@ -7361,14 +7355,14 @@
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B156" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C156" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="B156" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C156" s="14" t="s">
-        <v>348</v>
-      </c>
       <c r="D156" s="15" t="s">
         <v>25</v>
       </c>
@@ -7376,10 +7370,10 @@
         <v>26</v>
       </c>
       <c r="F156" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H156" s="15" t="s">
         <v>13</v>
@@ -7387,14 +7381,14 @@
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="B157" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C157" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="B157" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C157" s="19" t="s">
-        <v>350</v>
-      </c>
       <c r="D157" s="20" t="s">
         <v>25</v>
       </c>
@@ -7402,10 +7396,10 @@
         <v>26</v>
       </c>
       <c r="F157" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G157" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H157" s="20" t="s">
         <v>13</v>
@@ -7413,14 +7407,14 @@
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C158" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B158" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C158" s="14" t="s">
-        <v>352</v>
-      </c>
       <c r="D158" s="15" t="s">
         <v>25</v>
       </c>
@@ -7428,10 +7422,10 @@
         <v>26</v>
       </c>
       <c r="F158" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H158" s="15" t="s">
         <v>13</v>
@@ -7439,14 +7433,14 @@
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C159" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="B159" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C159" s="19" t="s">
-        <v>354</v>
-      </c>
       <c r="D159" s="20" t="s">
         <v>25</v>
       </c>
@@ -7454,10 +7448,10 @@
         <v>26</v>
       </c>
       <c r="F159" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G159" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H159" s="20" t="s">
         <v>13</v>
@@ -7465,14 +7459,14 @@
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C160" s="14" t="s">
         <v>355</v>
       </c>
-      <c r="B160" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C160" s="14" t="s">
-        <v>356</v>
-      </c>
       <c r="D160" s="15" t="s">
         <v>25</v>
       </c>
@@ -7480,10 +7474,10 @@
         <v>26</v>
       </c>
       <c r="F160" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H160" s="15" t="s">
         <v>13</v>
@@ -7491,13 +7485,13 @@
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B161" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="B161" s="18" t="s">
-        <v>339</v>
-      </c>
       <c r="C161" s="19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D161" s="20" t="s">
         <v>25</v>
@@ -7506,10 +7500,10 @@
         <v>26</v>
       </c>
       <c r="F161" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G161" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H161" s="20" t="s">
         <v>13</v>
@@ -7517,14 +7511,14 @@
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B162" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="C162" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="C162" s="14" t="s">
-        <v>359</v>
-      </c>
       <c r="D162" s="15" t="s">
         <v>25</v>
       </c>
@@ -7532,10 +7526,10 @@
         <v>26</v>
       </c>
       <c r="F162" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H162" s="15" t="s">
         <v>13</v>
@@ -7543,13 +7537,13 @@
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B163" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C163" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D163" s="20" t="s">
         <v>25</v>
@@ -7558,10 +7552,10 @@
         <v>26</v>
       </c>
       <c r="F163" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G163" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H163" s="20" t="s">
         <v>13</v>
@@ -7569,13 +7563,13 @@
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D164" s="15" t="s">
         <v>25</v>
@@ -7584,10 +7578,10 @@
         <v>26</v>
       </c>
       <c r="F164" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G164" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H164" s="15" t="s">
         <v>13</v>
@@ -7595,13 +7589,13 @@
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B165" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D165" s="20" t="s">
         <v>25</v>
@@ -7610,10 +7604,10 @@
         <v>26</v>
       </c>
       <c r="F165" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G165" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H165" s="20" t="s">
         <v>13</v>
@@ -7621,13 +7615,13 @@
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D166" s="15" t="s">
         <v>25</v>
@@ -7636,10 +7630,10 @@
         <v>26</v>
       </c>
       <c r="F166" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G166" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H166" s="15" t="s">
         <v>13</v>
@@ -7647,13 +7641,13 @@
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>25</v>
@@ -7662,10 +7656,10 @@
         <v>26</v>
       </c>
       <c r="F167" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G167" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H167" s="20" t="s">
         <v>13</v>
@@ -7673,14 +7667,14 @@
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B168" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="C168" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B168" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="C168" s="14" t="s">
-        <v>366</v>
-      </c>
       <c r="D168" s="15" t="s">
         <v>25</v>
       </c>
@@ -7688,10 +7682,10 @@
         <v>26</v>
       </c>
       <c r="F168" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G168" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H168" s="15" t="s">
         <v>13</v>
@@ -7699,14 +7693,14 @@
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="B169" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="C169" s="19" t="s">
         <v>367</v>
       </c>
-      <c r="B169" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="C169" s="19" t="s">
-        <v>368</v>
-      </c>
       <c r="D169" s="20" t="s">
         <v>25</v>
       </c>
@@ -7714,10 +7708,10 @@
         <v>26</v>
       </c>
       <c r="F169" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G169" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H169" s="20" t="s">
         <v>13</v>
@@ -7725,14 +7719,14 @@
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B170" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="C170" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B170" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="C170" s="14" t="s">
-        <v>370</v>
-      </c>
       <c r="D170" s="15" t="s">
         <v>25</v>
       </c>
@@ -7740,10 +7734,10 @@
         <v>26</v>
       </c>
       <c r="F170" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G170" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H170" s="15" t="s">
         <v>13</v>
@@ -7751,13 +7745,13 @@
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C171" s="19" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D171" s="20" t="s">
         <v>25</v>
@@ -7766,10 +7760,10 @@
         <v>26</v>
       </c>
       <c r="F171" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G171" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H171" s="20" t="s">
         <v>13</v>
@@ -7777,14 +7771,14 @@
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B172" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C172" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="C172" s="14" t="s">
-        <v>373</v>
-      </c>
       <c r="D172" s="15" t="s">
         <v>25</v>
       </c>
@@ -7792,10 +7786,10 @@
         <v>26</v>
       </c>
       <c r="F172" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H172" s="15" t="s">
         <v>13</v>
@@ -7803,13 +7797,13 @@
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C173" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D173" s="20" t="s">
         <v>25</v>
@@ -7818,10 +7812,10 @@
         <v>26</v>
       </c>
       <c r="F173" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G173" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H173" s="20" t="s">
         <v>13</v>
@@ -7829,13 +7823,13 @@
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D174" s="15" t="s">
         <v>25</v>
@@ -7844,10 +7838,10 @@
         <v>26</v>
       </c>
       <c r="F174" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G174" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H174" s="15" t="s">
         <v>13</v>
@@ -7855,13 +7849,13 @@
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D175" s="20" t="s">
         <v>25</v>
@@ -7870,10 +7864,10 @@
         <v>26</v>
       </c>
       <c r="F175" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G175" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H175" s="20" t="s">
         <v>13</v>
@@ -7881,13 +7875,13 @@
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>25</v>
@@ -7896,10 +7890,10 @@
         <v>26</v>
       </c>
       <c r="F176" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H176" s="15" t="s">
         <v>13</v>
@@ -7907,13 +7901,13 @@
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B177" s="18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D177" s="20" t="s">
         <v>25</v>
@@ -7922,10 +7916,10 @@
         <v>26</v>
       </c>
       <c r="F177" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G177" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H177" s="20" t="s">
         <v>13</v>
@@ -7933,14 +7927,14 @@
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B178" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C178" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="B178" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="C178" s="14" t="s">
-        <v>380</v>
-      </c>
       <c r="D178" s="15" t="s">
         <v>25</v>
       </c>
@@ -7948,10 +7942,10 @@
         <v>26</v>
       </c>
       <c r="F178" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G178" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H178" s="15" t="s">
         <v>13</v>
@@ -7959,14 +7953,14 @@
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="B179" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C179" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="B179" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="C179" s="19" t="s">
-        <v>382</v>
-      </c>
       <c r="D179" s="20" t="s">
         <v>25</v>
       </c>
@@ -7974,10 +7968,10 @@
         <v>26</v>
       </c>
       <c r="F179" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G179" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H179" s="20" t="s">
         <v>13</v>
@@ -7985,14 +7979,14 @@
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B180" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C180" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="B180" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="C180" s="14" t="s">
-        <v>384</v>
-      </c>
       <c r="D180" s="15" t="s">
         <v>25</v>
       </c>
@@ -8000,10 +7994,10 @@
         <v>26</v>
       </c>
       <c r="F180" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H180" s="15" t="s">
         <v>13</v>
@@ -8011,13 +8005,13 @@
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D181" s="20" t="s">
         <v>25</v>
@@ -8026,10 +8020,10 @@
         <v>26</v>
       </c>
       <c r="F181" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G181" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H181" s="20" t="s">
         <v>13</v>
@@ -8037,14 +8031,14 @@
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="B182" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="B182" s="13" t="s">
+      <c r="C182" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="C182" s="14" t="s">
-        <v>388</v>
-      </c>
       <c r="D182" s="15" t="s">
         <v>25</v>
       </c>
@@ -8052,10 +8046,10 @@
         <v>26</v>
       </c>
       <c r="F182" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G182" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H182" s="15" t="s">
         <v>13</v>
@@ -8063,14 +8057,14 @@
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="B183" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C183" s="19" t="s">
         <v>389</v>
       </c>
-      <c r="B183" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C183" s="19" t="s">
-        <v>390</v>
-      </c>
       <c r="D183" s="20" t="s">
         <v>25</v>
       </c>
@@ -8078,10 +8072,10 @@
         <v>26</v>
       </c>
       <c r="F183" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G183" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H183" s="20" t="s">
         <v>13</v>
@@ -8089,14 +8083,14 @@
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B184" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C184" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="B184" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C184" s="14" t="s">
-        <v>392</v>
-      </c>
       <c r="D184" s="15" t="s">
         <v>25</v>
       </c>
@@ -8104,10 +8098,10 @@
         <v>26</v>
       </c>
       <c r="F184" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G184" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H184" s="15" t="s">
         <v>13</v>
@@ -8115,14 +8109,14 @@
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="B185" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C185" s="19" t="s">
         <v>393</v>
       </c>
-      <c r="B185" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C185" s="19" t="s">
-        <v>394</v>
-      </c>
       <c r="D185" s="20" t="s">
         <v>25</v>
       </c>
@@ -8130,10 +8124,10 @@
         <v>26</v>
       </c>
       <c r="F185" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G185" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H185" s="20" t="s">
         <v>13</v>
@@ -8141,14 +8135,14 @@
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B186" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C186" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="B186" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C186" s="14" t="s">
-        <v>396</v>
-      </c>
       <c r="D186" s="15" t="s">
         <v>25</v>
       </c>
@@ -8156,10 +8150,10 @@
         <v>26</v>
       </c>
       <c r="F186" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G186" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H186" s="15" t="s">
         <v>13</v>
@@ -8167,14 +8161,14 @@
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="B187" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C187" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="B187" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C187" s="19" t="s">
-        <v>398</v>
-      </c>
       <c r="D187" s="20" t="s">
         <v>25</v>
       </c>
@@ -8182,10 +8176,10 @@
         <v>26</v>
       </c>
       <c r="F187" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G187" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H187" s="20" t="s">
         <v>13</v>
@@ -8193,14 +8187,14 @@
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B188" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C188" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="B188" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C188" s="14" t="s">
-        <v>400</v>
-      </c>
       <c r="D188" s="15" t="s">
         <v>25</v>
       </c>
@@ -8208,10 +8202,10 @@
         <v>26</v>
       </c>
       <c r="F188" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G188" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H188" s="15" t="s">
         <v>13</v>
@@ -8219,14 +8213,14 @@
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="B189" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C189" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="B189" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C189" s="19" t="s">
-        <v>402</v>
-      </c>
       <c r="D189" s="20" t="s">
         <v>25</v>
       </c>
@@ -8234,10 +8228,10 @@
         <v>26</v>
       </c>
       <c r="F189" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G189" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H189" s="20" t="s">
         <v>13</v>
@@ -8245,14 +8239,14 @@
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="B190" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C190" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="B190" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C190" s="14" t="s">
-        <v>404</v>
-      </c>
       <c r="D190" s="15" t="s">
         <v>25</v>
       </c>
@@ -8260,10 +8254,10 @@
         <v>26</v>
       </c>
       <c r="F190" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G190" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H190" s="15" t="s">
         <v>13</v>
@@ -8271,14 +8265,14 @@
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="B191" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C191" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="B191" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C191" s="19" t="s">
-        <v>406</v>
-      </c>
       <c r="D191" s="20" t="s">
         <v>25</v>
       </c>
@@ -8286,10 +8280,10 @@
         <v>26</v>
       </c>
       <c r="F191" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G191" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H191" s="20" t="s">
         <v>13</v>
@@ -8297,14 +8291,14 @@
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="B192" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="B192" s="13" t="s">
+      <c r="C192" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="C192" s="14" t="s">
-        <v>409</v>
-      </c>
       <c r="D192" s="15" t="s">
         <v>25</v>
       </c>
@@ -8312,10 +8306,10 @@
         <v>26</v>
       </c>
       <c r="F192" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G192" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H192" s="15" t="s">
         <v>13</v>
@@ -8323,14 +8317,14 @@
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B193" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C193" s="19" t="s">
         <v>410</v>
       </c>
-      <c r="B193" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C193" s="19" t="s">
-        <v>411</v>
-      </c>
       <c r="D193" s="20" t="s">
         <v>25</v>
       </c>
@@ -8338,10 +8332,10 @@
         <v>26</v>
       </c>
       <c r="F193" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G193" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H193" s="20" t="s">
         <v>13</v>
@@ -8349,14 +8343,14 @@
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B194" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="C194" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="B194" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="C194" s="14" t="s">
-        <v>413</v>
-      </c>
       <c r="D194" s="15" t="s">
         <v>25</v>
       </c>
@@ -8364,10 +8358,10 @@
         <v>26</v>
       </c>
       <c r="F194" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G194" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H194" s="15" t="s">
         <v>13</v>
@@ -8375,14 +8369,14 @@
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="B195" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C195" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="B195" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C195" s="19" t="s">
-        <v>415</v>
-      </c>
       <c r="D195" s="20" t="s">
         <v>25</v>
       </c>
@@ -8390,10 +8384,10 @@
         <v>26</v>
       </c>
       <c r="F195" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G195" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H195" s="20" t="s">
         <v>13</v>
@@ -8401,14 +8395,14 @@
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B196" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="C196" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="B196" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="C196" s="14" t="s">
-        <v>417</v>
-      </c>
       <c r="D196" s="15" t="s">
         <v>25</v>
       </c>
@@ -8416,10 +8410,10 @@
         <v>26</v>
       </c>
       <c r="F196" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G196" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H196" s="15" t="s">
         <v>13</v>
@@ -8427,14 +8421,14 @@
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="B197" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C197" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="B197" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C197" s="19" t="s">
-        <v>419</v>
-      </c>
       <c r="D197" s="20" t="s">
         <v>25</v>
       </c>
@@ -8442,10 +8436,10 @@
         <v>26</v>
       </c>
       <c r="F197" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G197" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H197" s="20" t="s">
         <v>13</v>
@@ -8453,14 +8447,14 @@
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B198" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="C198" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="B198" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="C198" s="14" t="s">
-        <v>421</v>
-      </c>
       <c r="D198" s="15" t="s">
         <v>25</v>
       </c>
@@ -8468,10 +8462,10 @@
         <v>26</v>
       </c>
       <c r="F198" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G198" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H198" s="15" t="s">
         <v>13</v>
@@ -8479,14 +8473,14 @@
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="B199" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C199" s="19" t="s">
         <v>422</v>
       </c>
-      <c r="B199" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C199" s="19" t="s">
-        <v>423</v>
-      </c>
       <c r="D199" s="20" t="s">
         <v>25</v>
       </c>
@@ -8494,10 +8488,10 @@
         <v>26</v>
       </c>
       <c r="F199" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G199" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H199" s="20" t="s">
         <v>13</v>
@@ -8505,14 +8499,14 @@
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="B200" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="C200" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="B200" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="C200" s="14" t="s">
-        <v>425</v>
-      </c>
       <c r="D200" s="15" t="s">
         <v>25</v>
       </c>
@@ -8520,10 +8514,10 @@
         <v>26</v>
       </c>
       <c r="F200" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G200" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H200" s="15" t="s">
         <v>13</v>
@@ -8531,14 +8525,14 @@
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="B201" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C201" s="19" t="s">
         <v>426</v>
       </c>
-      <c r="B201" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C201" s="19" t="s">
-        <v>427</v>
-      </c>
       <c r="D201" s="20" t="s">
         <v>25</v>
       </c>
@@ -8546,10 +8540,10 @@
         <v>26</v>
       </c>
       <c r="F201" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G201" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H201" s="20" t="s">
         <v>13</v>
@@ -8557,14 +8551,14 @@
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="B202" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="B202" s="13" t="s">
+      <c r="C202" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="C202" s="14" t="s">
-        <v>430</v>
-      </c>
       <c r="D202" s="15" t="s">
         <v>25</v>
       </c>
@@ -8572,10 +8566,10 @@
         <v>26</v>
       </c>
       <c r="F202" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G202" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H202" s="15" t="s">
         <v>13</v>
@@ -8583,14 +8577,14 @@
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="B203" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C203" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="B203" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="C203" s="19" t="s">
-        <v>432</v>
-      </c>
       <c r="D203" s="20" t="s">
         <v>25</v>
       </c>
@@ -8598,10 +8592,10 @@
         <v>26</v>
       </c>
       <c r="F203" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G203" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H203" s="20" t="s">
         <v>13</v>
@@ -8609,14 +8603,14 @@
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B204" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="C204" s="14" t="s">
         <v>433</v>
       </c>
-      <c r="B204" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="C204" s="14" t="s">
-        <v>434</v>
-      </c>
       <c r="D204" s="15" t="s">
         <v>25</v>
       </c>
@@ -8624,10 +8618,10 @@
         <v>26</v>
       </c>
       <c r="F204" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G204" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H204" s="15" t="s">
         <v>13</v>
@@ -8635,14 +8629,14 @@
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="B205" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C205" s="19" t="s">
         <v>435</v>
       </c>
-      <c r="B205" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="C205" s="19" t="s">
-        <v>436</v>
-      </c>
       <c r="D205" s="20" t="s">
         <v>25</v>
       </c>
@@ -8650,10 +8644,10 @@
         <v>26</v>
       </c>
       <c r="F205" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G205" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H205" s="20" t="s">
         <v>13</v>
@@ -8661,14 +8655,14 @@
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="B206" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="C206" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="B206" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="C206" s="14" t="s">
-        <v>438</v>
-      </c>
       <c r="D206" s="15" t="s">
         <v>25</v>
       </c>
@@ -8676,10 +8670,10 @@
         <v>26</v>
       </c>
       <c r="F206" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G206" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H206" s="15" t="s">
         <v>13</v>
@@ -8687,14 +8681,14 @@
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="B207" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C207" s="19" t="s">
         <v>439</v>
       </c>
-      <c r="B207" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="C207" s="19" t="s">
-        <v>440</v>
-      </c>
       <c r="D207" s="20" t="s">
         <v>25</v>
       </c>
@@ -8702,10 +8696,10 @@
         <v>26</v>
       </c>
       <c r="F207" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G207" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H207" s="20" t="s">
         <v>13</v>
@@ -8713,14 +8707,14 @@
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="B208" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="C208" s="14" t="s">
         <v>441</v>
       </c>
-      <c r="B208" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="C208" s="14" t="s">
-        <v>442</v>
-      </c>
       <c r="D208" s="15" t="s">
         <v>25</v>
       </c>
@@ -8728,24 +8722,24 @@
         <v>26</v>
       </c>
       <c r="F208" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G208" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H208" s="15" t="s">
-        <v>443</v>
+        <v>13</v>
       </c>
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="17" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B209" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C209" s="19" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D209" s="20" t="s">
         <v>25</v>
@@ -8754,10 +8748,10 @@
         <v>26</v>
       </c>
       <c r="F209" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G209" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H209" s="20" t="s">
         <v>13</v>
@@ -8765,13 +8759,13 @@
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B210" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D210" s="15" t="s">
         <v>25</v>
@@ -8780,10 +8774,10 @@
         <v>26</v>
       </c>
       <c r="F210" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G210" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H210" s="15" t="s">
         <v>13</v>
@@ -8791,13 +8785,13 @@
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="17" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B211" s="18" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D211" s="20" t="s">
         <v>25</v>
@@ -8806,10 +8800,10 @@
         <v>26</v>
       </c>
       <c r="F211" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G211" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H211" s="20" t="s">
         <v>13</v>
@@ -8817,14 +8811,14 @@
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="B212" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="C212" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="B212" s="13" t="s">
-        <v>451</v>
-      </c>
-      <c r="C212" s="14" t="s">
-        <v>452</v>
-      </c>
       <c r="D212" s="15" t="s">
         <v>25</v>
       </c>
@@ -8832,10 +8826,10 @@
         <v>26</v>
       </c>
       <c r="F212" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G212" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H212" s="15" t="s">
         <v>13</v>
@@ -8843,13 +8837,13 @@
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="17" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B213" s="18" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C213" s="19" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D213" s="20" t="s">
         <v>25</v>
@@ -8858,10 +8852,10 @@
         <v>26</v>
       </c>
       <c r="F213" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G213" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H213" s="20" t="s">
         <v>13</v>
@@ -8869,13 +8863,13 @@
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D214" s="15" t="s">
         <v>25</v>
@@ -8884,10 +8878,10 @@
         <v>26</v>
       </c>
       <c r="F214" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G214" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H214" s="15" t="s">
         <v>13</v>
@@ -8895,13 +8889,13 @@
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="17" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B215" s="18" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C215" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D215" s="20" t="s">
         <v>25</v>
@@ -8910,10 +8904,10 @@
         <v>26</v>
       </c>
       <c r="F215" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G215" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H215" s="20" t="s">
         <v>13</v>
@@ -8921,13 +8915,13 @@
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D216" s="15" t="s">
         <v>25</v>
@@ -8936,10 +8930,10 @@
         <v>26</v>
       </c>
       <c r="F216" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G216" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H216" s="15" t="s">
         <v>13</v>
@@ -8947,13 +8941,13 @@
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="17" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B217" s="18" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C217" s="19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D217" s="20" t="s">
         <v>25</v>
@@ -8962,10 +8956,10 @@
         <v>26</v>
       </c>
       <c r="F217" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G217" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H217" s="20" t="s">
         <v>13</v>
@@ -8973,13 +8967,13 @@
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D218" s="15" t="s">
         <v>25</v>
@@ -8988,10 +8982,10 @@
         <v>26</v>
       </c>
       <c r="F218" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G218" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H218" s="15" t="s">
         <v>13</v>
@@ -8999,13 +8993,13 @@
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="17" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B219" s="18" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>25</v>
@@ -9014,10 +9008,10 @@
         <v>26</v>
       </c>
       <c r="F219" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G219" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H219" s="20" t="s">
         <v>13</v>
@@ -9025,13 +9019,13 @@
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D220" s="15" t="s">
         <v>25</v>
@@ -9040,10 +9034,10 @@
         <v>26</v>
       </c>
       <c r="F220" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G220" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H220" s="15" t="s">
         <v>13</v>
@@ -9051,13 +9045,13 @@
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="17" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B221" s="18" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C221" s="19" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D221" s="20" t="s">
         <v>25</v>
@@ -9066,10 +9060,10 @@
         <v>26</v>
       </c>
       <c r="F221" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G221" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H221" s="20" t="s">
         <v>13</v>
@@ -9077,14 +9071,14 @@
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B222" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="C222" s="14" t="s">
         <v>471</v>
       </c>
-      <c r="B222" s="13" t="s">
-        <v>472</v>
-      </c>
-      <c r="C222" s="14" t="s">
-        <v>473</v>
-      </c>
       <c r="D222" s="15" t="s">
         <v>25</v>
       </c>
@@ -9092,10 +9086,10 @@
         <v>26</v>
       </c>
       <c r="F222" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G222" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H222" s="15" t="s">
         <v>13</v>
@@ -9103,13 +9097,13 @@
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="17" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B223" s="18" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C223" s="19" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D223" s="20" t="s">
         <v>25</v>
@@ -9118,10 +9112,10 @@
         <v>26</v>
       </c>
       <c r="F223" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G223" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H223" s="20" t="s">
         <v>13</v>
@@ -9129,13 +9123,13 @@
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D224" s="15" t="s">
         <v>25</v>
@@ -9144,10 +9138,10 @@
         <v>26</v>
       </c>
       <c r="F224" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G224" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H224" s="15" t="s">
         <v>13</v>
@@ -9155,13 +9149,13 @@
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="17" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B225" s="18" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D225" s="20" t="s">
         <v>25</v>
@@ -9170,10 +9164,10 @@
         <v>26</v>
       </c>
       <c r="F225" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G225" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H225" s="20" t="s">
         <v>13</v>
@@ -9181,13 +9175,13 @@
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D226" s="15" t="s">
         <v>25</v>
@@ -9196,10 +9190,10 @@
         <v>26</v>
       </c>
       <c r="F226" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G226" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H226" s="15" t="s">
         <v>13</v>
@@ -9207,13 +9201,13 @@
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="17" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B227" s="18" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C227" s="19" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>25</v>
@@ -9222,10 +9216,10 @@
         <v>26</v>
       </c>
       <c r="F227" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G227" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H227" s="20" t="s">
         <v>13</v>
@@ -9233,13 +9227,13 @@
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D228" s="15" t="s">
         <v>25</v>
@@ -9248,10 +9242,10 @@
         <v>26</v>
       </c>
       <c r="F228" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G228" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H228" s="15" t="s">
         <v>13</v>
@@ -9259,13 +9253,13 @@
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="17" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B229" s="18" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C229" s="19" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>25</v>
@@ -9274,10 +9268,10 @@
         <v>26</v>
       </c>
       <c r="F229" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G229" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H229" s="20" t="s">
         <v>13</v>
@@ -9285,13 +9279,13 @@
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B230" s="13" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D230" s="15" t="s">
         <v>25</v>
@@ -9300,10 +9294,10 @@
         <v>26</v>
       </c>
       <c r="F230" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G230" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H230" s="15" t="s">
         <v>13</v>
@@ -9311,13 +9305,13 @@
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="17" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B231" s="18" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C231" s="19" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D231" s="20" t="s">
         <v>25</v>
@@ -9326,10 +9320,10 @@
         <v>26</v>
       </c>
       <c r="F231" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G231" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H231" s="20" t="s">
         <v>13</v>
@@ -9337,14 +9331,14 @@
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="B232" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="C232" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="B232" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="C232" s="14" t="s">
-        <v>494</v>
-      </c>
       <c r="D232" s="15" t="s">
         <v>25</v>
       </c>
@@ -9352,10 +9346,10 @@
         <v>26</v>
       </c>
       <c r="F232" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G232" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H232" s="15" t="s">
         <v>13</v>
@@ -9363,13 +9357,13 @@
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="17" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C233" s="19" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>25</v>
@@ -9378,10 +9372,10 @@
         <v>26</v>
       </c>
       <c r="F233" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G233" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H233" s="20" t="s">
         <v>13</v>
@@ -9389,13 +9383,13 @@
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>25</v>
@@ -9404,10 +9398,10 @@
         <v>26</v>
       </c>
       <c r="F234" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G234" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H234" s="15" t="s">
         <v>13</v>
@@ -9415,13 +9409,13 @@
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="17" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B235" s="18" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C235" s="19" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>25</v>
@@ -9430,10 +9424,10 @@
         <v>26</v>
       </c>
       <c r="F235" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G235" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H235" s="20" t="s">
         <v>13</v>
@@ -9441,13 +9435,13 @@
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C236" s="14" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D236" s="15" t="s">
         <v>25</v>
@@ -9456,10 +9450,10 @@
         <v>26</v>
       </c>
       <c r="F236" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G236" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H236" s="15" t="s">
         <v>13</v>
@@ -9467,13 +9461,13 @@
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="17" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B237" s="18" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C237" s="19" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>25</v>
@@ -9482,10 +9476,10 @@
         <v>26</v>
       </c>
       <c r="F237" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G237" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H237" s="20" t="s">
         <v>13</v>
@@ -9493,13 +9487,13 @@
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B238" s="13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>25</v>
@@ -9508,10 +9502,10 @@
         <v>26</v>
       </c>
       <c r="F238" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G238" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H238" s="15" t="s">
         <v>13</v>
@@ -9519,13 +9513,13 @@
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="17" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B239" s="18" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C239" s="19" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>25</v>
@@ -9534,10 +9528,10 @@
         <v>26</v>
       </c>
       <c r="F239" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G239" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H239" s="20" t="s">
         <v>13</v>
@@ -9545,13 +9539,13 @@
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B240" s="13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D240" s="15" t="s">
         <v>25</v>
@@ -9560,10 +9554,10 @@
         <v>26</v>
       </c>
       <c r="F240" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G240" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H240" s="15" t="s">
         <v>13</v>
@@ -9571,13 +9565,13 @@
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B241" s="18" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C241" s="19" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>25</v>
@@ -9586,10 +9580,10 @@
         <v>26</v>
       </c>
       <c r="F241" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G241" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H241" s="20" t="s">
         <v>13</v>
@@ -9597,14 +9591,14 @@
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="B242" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="C242" s="14" t="s">
         <v>513</v>
       </c>
-      <c r="B242" s="13" t="s">
-        <v>514</v>
-      </c>
-      <c r="C242" s="14" t="s">
-        <v>515</v>
-      </c>
       <c r="D242" s="15" t="s">
         <v>25</v>
       </c>
@@ -9612,10 +9606,10 @@
         <v>26</v>
       </c>
       <c r="F242" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G242" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H242" s="15" t="s">
         <v>13</v>
@@ -9623,13 +9617,13 @@
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B243" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C243" s="19" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>25</v>
@@ -9638,10 +9632,10 @@
         <v>26</v>
       </c>
       <c r="F243" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G243" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H243" s="20" t="s">
         <v>13</v>
@@ -9649,13 +9643,13 @@
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D244" s="15" t="s">
         <v>25</v>
@@ -9664,10 +9658,10 @@
         <v>26</v>
       </c>
       <c r="F244" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G244" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H244" s="15" t="s">
         <v>13</v>
@@ -9675,13 +9669,13 @@
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="17" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B245" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C245" s="19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D245" s="20" t="s">
         <v>25</v>
@@ -9690,10 +9684,10 @@
         <v>26</v>
       </c>
       <c r="F245" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G245" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H245" s="20" t="s">
         <v>13</v>
@@ -9701,13 +9695,13 @@
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D246" s="15" t="s">
         <v>25</v>
@@ -9716,10 +9710,10 @@
         <v>26</v>
       </c>
       <c r="F246" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G246" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H246" s="15" t="s">
         <v>13</v>
@@ -9727,13 +9721,13 @@
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="17" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C247" s="19" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D247" s="20" t="s">
         <v>25</v>
@@ -9742,10 +9736,10 @@
         <v>26</v>
       </c>
       <c r="F247" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G247" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H247" s="20" t="s">
         <v>13</v>
@@ -9753,13 +9747,13 @@
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D248" s="15" t="s">
         <v>25</v>
@@ -9768,10 +9762,10 @@
         <v>26</v>
       </c>
       <c r="F248" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G248" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H248" s="15" t="s">
         <v>13</v>
@@ -9779,13 +9773,13 @@
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="17" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C249" s="19" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D249" s="20" t="s">
         <v>25</v>
@@ -9794,10 +9788,10 @@
         <v>26</v>
       </c>
       <c r="F249" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G249" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H249" s="20" t="s">
         <v>13</v>
@@ -9805,13 +9799,13 @@
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D250" s="15" t="s">
         <v>25</v>
@@ -9820,10 +9814,10 @@
         <v>26</v>
       </c>
       <c r="F250" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G250" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H250" s="15" t="s">
         <v>13</v>
@@ -9831,13 +9825,13 @@
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="17" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C251" s="19" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D251" s="20" t="s">
         <v>25</v>
@@ -9846,10 +9840,10 @@
         <v>26</v>
       </c>
       <c r="F251" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G251" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H251" s="20" t="s">
         <v>13</v>
@@ -9857,14 +9851,14 @@
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="B252" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="C252" s="14" t="s">
         <v>534</v>
       </c>
-      <c r="B252" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="C252" s="14" t="s">
-        <v>536</v>
-      </c>
       <c r="D252" s="15" t="s">
         <v>25</v>
       </c>
@@ -9872,10 +9866,10 @@
         <v>26</v>
       </c>
       <c r="F252" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G252" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H252" s="15" t="s">
         <v>13</v>
@@ -9883,13 +9877,13 @@
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C253" s="19" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>25</v>
@@ -9898,10 +9892,10 @@
         <v>26</v>
       </c>
       <c r="F253" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G253" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H253" s="20" t="s">
         <v>13</v>
@@ -9909,13 +9903,13 @@
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D254" s="15" t="s">
         <v>25</v>
@@ -9924,10 +9918,10 @@
         <v>26</v>
       </c>
       <c r="F254" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G254" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H254" s="15" t="s">
         <v>13</v>
@@ -9935,13 +9929,13 @@
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="17" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C255" s="19" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D255" s="20" t="s">
         <v>25</v>
@@ -9950,10 +9944,10 @@
         <v>26</v>
       </c>
       <c r="F255" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G255" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H255" s="20" t="s">
         <v>13</v>
@@ -9961,13 +9955,13 @@
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B256" s="13" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D256" s="15" t="s">
         <v>25</v>
@@ -9976,10 +9970,10 @@
         <v>26</v>
       </c>
       <c r="F256" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G256" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H256" s="15" t="s">
         <v>13</v>
@@ -9987,13 +9981,13 @@
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="17" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B257" s="18" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C257" s="19" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D257" s="20" t="s">
         <v>25</v>
@@ -10002,10 +9996,10 @@
         <v>26</v>
       </c>
       <c r="F257" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G257" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H257" s="20" t="s">
         <v>13</v>
@@ -10013,13 +10007,13 @@
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B258" s="13" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D258" s="15" t="s">
         <v>25</v>
@@ -10028,10 +10022,10 @@
         <v>26</v>
       </c>
       <c r="F258" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G258" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H258" s="15" t="s">
         <v>13</v>
@@ -10039,13 +10033,13 @@
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="17" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B259" s="18" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C259" s="19" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D259" s="20" t="s">
         <v>25</v>
@@ -10054,10 +10048,10 @@
         <v>26</v>
       </c>
       <c r="F259" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G259" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H259" s="20" t="s">
         <v>13</v>
@@ -10065,13 +10059,13 @@
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B260" s="13" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D260" s="15" t="s">
         <v>25</v>
@@ -10080,10 +10074,10 @@
         <v>26</v>
       </c>
       <c r="F260" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G260" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H260" s="15" t="s">
         <v>13</v>
@@ -10091,13 +10085,13 @@
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="17" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B261" s="18" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C261" s="19" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="D261" s="20" t="s">
         <v>25</v>
@@ -10106,10 +10100,10 @@
         <v>26</v>
       </c>
       <c r="F261" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G261" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H261" s="20" t="s">
         <v>13</v>
@@ -10117,14 +10111,14 @@
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="B262" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="C262" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="B262" s="13" t="s">
-        <v>556</v>
-      </c>
-      <c r="C262" s="14" t="s">
-        <v>557</v>
-      </c>
       <c r="D262" s="15" t="s">
         <v>25</v>
       </c>
@@ -10132,10 +10126,10 @@
         <v>26</v>
       </c>
       <c r="F262" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G262" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H262" s="15" t="s">
         <v>13</v>
@@ -10143,13 +10137,13 @@
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="17" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B263" s="18" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C263" s="19" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D263" s="20" t="s">
         <v>25</v>
@@ -10158,10 +10152,10 @@
         <v>26</v>
       </c>
       <c r="F263" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G263" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H263" s="20" t="s">
         <v>13</v>
@@ -10169,13 +10163,13 @@
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B264" s="13" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C264" s="14" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D264" s="15" t="s">
         <v>25</v>
@@ -10184,10 +10178,10 @@
         <v>26</v>
       </c>
       <c r="F264" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G264" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H264" s="15" t="s">
         <v>13</v>
@@ -10195,13 +10189,13 @@
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="17" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B265" s="18" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C265" s="19" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D265" s="20" t="s">
         <v>25</v>
@@ -10210,10 +10204,10 @@
         <v>26</v>
       </c>
       <c r="F265" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G265" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H265" s="20" t="s">
         <v>13</v>
@@ -10221,13 +10215,13 @@
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D266" s="15" t="s">
         <v>25</v>
@@ -10236,10 +10230,10 @@
         <v>26</v>
       </c>
       <c r="F266" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G266" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H266" s="15" t="s">
         <v>13</v>
@@ -10247,13 +10241,13 @@
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="17" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B267" s="18" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C267" s="19" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D267" s="20" t="s">
         <v>25</v>
@@ -10262,10 +10256,10 @@
         <v>26</v>
       </c>
       <c r="F267" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G267" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H267" s="20" t="s">
         <v>13</v>
@@ -10273,13 +10267,13 @@
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>25</v>
@@ -10288,10 +10282,10 @@
         <v>26</v>
       </c>
       <c r="F268" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G268" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H268" s="15" t="s">
         <v>13</v>
@@ -10299,13 +10293,13 @@
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="17" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B269" s="18" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C269" s="19" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D269" s="20" t="s">
         <v>25</v>
@@ -10314,10 +10308,10 @@
         <v>26</v>
       </c>
       <c r="F269" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G269" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H269" s="20" t="s">
         <v>13</v>
@@ -10325,13 +10319,13 @@
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="D270" s="15" t="s">
         <v>25</v>
@@ -10340,10 +10334,10 @@
         <v>26</v>
       </c>
       <c r="F270" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G270" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H270" s="15" t="s">
         <v>13</v>
@@ -10351,13 +10345,13 @@
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="17" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B271" s="18" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C271" s="19" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D271" s="20" t="s">
         <v>25</v>
@@ -10366,10 +10360,10 @@
         <v>26</v>
       </c>
       <c r="F271" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G271" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H271" s="20" t="s">
         <v>13</v>
@@ -10377,14 +10371,14 @@
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="B272" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="C272" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="B272" s="13" t="s">
-        <v>577</v>
-      </c>
-      <c r="C272" s="14" t="s">
-        <v>578</v>
-      </c>
       <c r="D272" s="15" t="s">
         <v>25</v>
       </c>
@@ -10392,10 +10386,10 @@
         <v>26</v>
       </c>
       <c r="F272" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G272" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H272" s="15" t="s">
         <v>13</v>
@@ -10403,13 +10397,13 @@
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B273" s="18" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C273" s="19" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D273" s="20" t="s">
         <v>25</v>
@@ -10418,10 +10412,10 @@
         <v>26</v>
       </c>
       <c r="F273" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G273" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H273" s="20" t="s">
         <v>13</v>
@@ -10429,13 +10423,13 @@
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B274" s="13" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D274" s="15" t="s">
         <v>25</v>
@@ -10444,10 +10438,10 @@
         <v>26</v>
       </c>
       <c r="F274" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G274" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H274" s="15" t="s">
         <v>13</v>
@@ -10455,13 +10449,13 @@
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="17" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B275" s="18" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C275" s="19" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D275" s="20" t="s">
         <v>25</v>
@@ -10470,10 +10464,10 @@
         <v>26</v>
       </c>
       <c r="F275" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G275" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H275" s="20" t="s">
         <v>13</v>
@@ -10481,13 +10475,13 @@
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D276" s="15" t="s">
         <v>25</v>
@@ -10496,10 +10490,10 @@
         <v>26</v>
       </c>
       <c r="F276" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G276" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H276" s="15" t="s">
         <v>13</v>
@@ -10507,13 +10501,13 @@
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="17" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B277" s="18" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C277" s="19" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D277" s="20" t="s">
         <v>25</v>
@@ -10522,10 +10516,10 @@
         <v>26</v>
       </c>
       <c r="F277" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G277" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H277" s="20" t="s">
         <v>13</v>
@@ -10533,13 +10527,13 @@
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B278" s="13" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D278" s="15" t="s">
         <v>25</v>
@@ -10548,10 +10542,10 @@
         <v>26</v>
       </c>
       <c r="F278" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G278" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H278" s="15" t="s">
         <v>13</v>
@@ -10559,13 +10553,13 @@
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B279" s="18" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C279" s="19" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D279" s="20" t="s">
         <v>25</v>
@@ -10574,10 +10568,10 @@
         <v>26</v>
       </c>
       <c r="F279" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G279" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H279" s="20" t="s">
         <v>13</v>
@@ -10585,13 +10579,13 @@
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D280" s="15" t="s">
         <v>25</v>
@@ -10600,10 +10594,10 @@
         <v>26</v>
       </c>
       <c r="F280" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G280" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H280" s="15" t="s">
         <v>13</v>
@@ -10611,13 +10605,13 @@
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="17" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B281" s="18" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C281" s="19" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D281" s="20" t="s">
         <v>25</v>
@@ -10626,10 +10620,10 @@
         <v>26</v>
       </c>
       <c r="F281" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G281" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H281" s="20" t="s">
         <v>13</v>
@@ -10637,14 +10631,14 @@
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="B282" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="C282" s="14" t="s">
         <v>597</v>
       </c>
-      <c r="B282" s="13" t="s">
-        <v>598</v>
-      </c>
-      <c r="C282" s="14" t="s">
-        <v>599</v>
-      </c>
       <c r="D282" s="15" t="s">
         <v>25</v>
       </c>
@@ -10652,10 +10646,10 @@
         <v>26</v>
       </c>
       <c r="F282" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G282" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H282" s="15" t="s">
         <v>13</v>
@@ -10663,13 +10657,13 @@
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B283" s="18" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C283" s="19" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D283" s="20" t="s">
         <v>25</v>
@@ -10678,10 +10672,10 @@
         <v>26</v>
       </c>
       <c r="F283" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G283" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H283" s="20" t="s">
         <v>13</v>
@@ -10689,13 +10683,13 @@
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D284" s="15" t="s">
         <v>25</v>
@@ -10704,10 +10698,10 @@
         <v>26</v>
       </c>
       <c r="F284" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G284" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H284" s="15" t="s">
         <v>13</v>
@@ -10715,13 +10709,13 @@
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="17" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B285" s="18" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C285" s="19" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D285" s="20" t="s">
         <v>25</v>
@@ -10730,10 +10724,10 @@
         <v>26</v>
       </c>
       <c r="F285" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G285" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H285" s="20" t="s">
         <v>13</v>
@@ -10741,13 +10735,13 @@
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B286" s="13" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D286" s="15" t="s">
         <v>25</v>
@@ -10756,10 +10750,10 @@
         <v>26</v>
       </c>
       <c r="F286" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G286" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H286" s="15" t="s">
         <v>13</v>
@@ -10767,13 +10761,13 @@
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="17" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B287" s="18" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C287" s="19" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D287" s="20" t="s">
         <v>25</v>
@@ -10782,10 +10776,10 @@
         <v>26</v>
       </c>
       <c r="F287" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G287" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H287" s="20" t="s">
         <v>13</v>
@@ -10793,13 +10787,13 @@
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B288" s="13" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D288" s="15" t="s">
         <v>25</v>
@@ -10808,10 +10802,10 @@
         <v>26</v>
       </c>
       <c r="F288" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G288" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H288" s="15" t="s">
         <v>13</v>
@@ -10819,13 +10813,13 @@
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="17" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B289" s="18" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C289" s="19" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D289" s="20" t="s">
         <v>25</v>
@@ -10834,10 +10828,10 @@
         <v>26</v>
       </c>
       <c r="F289" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G289" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H289" s="20" t="s">
         <v>13</v>
@@ -10845,13 +10839,13 @@
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B290" s="13" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D290" s="15" t="s">
         <v>25</v>
@@ -10860,10 +10854,10 @@
         <v>26</v>
       </c>
       <c r="F290" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G290" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H290" s="15" t="s">
         <v>13</v>
@@ -10871,13 +10865,13 @@
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="17" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B291" s="18" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C291" s="19" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D291" s="20" t="s">
         <v>25</v>
@@ -10886,10 +10880,10 @@
         <v>26</v>
       </c>
       <c r="F291" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G291" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H291" s="20" t="s">
         <v>13</v>
@@ -10897,14 +10891,14 @@
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="B292" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="C292" s="14" t="s">
         <v>618</v>
       </c>
-      <c r="B292" s="13" t="s">
-        <v>619</v>
-      </c>
-      <c r="C292" s="14" t="s">
-        <v>620</v>
-      </c>
       <c r="D292" s="15" t="s">
         <v>25</v>
       </c>
@@ -10912,10 +10906,10 @@
         <v>26</v>
       </c>
       <c r="F292" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G292" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H292" s="15" t="s">
         <v>13</v>
@@ -10923,13 +10917,13 @@
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="17" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B293" s="18" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C293" s="19" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D293" s="20" t="s">
         <v>25</v>
@@ -10938,10 +10932,10 @@
         <v>26</v>
       </c>
       <c r="F293" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G293" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H293" s="20" t="s">
         <v>13</v>
@@ -10949,13 +10943,13 @@
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D294" s="15" t="s">
         <v>25</v>
@@ -10964,10 +10958,10 @@
         <v>26</v>
       </c>
       <c r="F294" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G294" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H294" s="15" t="s">
         <v>13</v>
@@ -10975,13 +10969,13 @@
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="17" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B295" s="18" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C295" s="19" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D295" s="20" t="s">
         <v>25</v>
@@ -10990,10 +10984,10 @@
         <v>26</v>
       </c>
       <c r="F295" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G295" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H295" s="20" t="s">
         <v>13</v>
@@ -11001,13 +10995,13 @@
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D296" s="15" t="s">
         <v>25</v>
@@ -11016,10 +11010,10 @@
         <v>26</v>
       </c>
       <c r="F296" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G296" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H296" s="15" t="s">
         <v>13</v>
@@ -11027,13 +11021,13 @@
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="17" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C297" s="19" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D297" s="20" t="s">
         <v>25</v>
@@ -11042,10 +11036,10 @@
         <v>26</v>
       </c>
       <c r="F297" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G297" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H297" s="20" t="s">
         <v>13</v>
@@ -11053,13 +11047,13 @@
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B298" s="13" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D298" s="15" t="s">
         <v>25</v>
@@ -11068,10 +11062,10 @@
         <v>26</v>
       </c>
       <c r="F298" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G298" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H298" s="15" t="s">
         <v>13</v>
@@ -11079,13 +11073,13 @@
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B299" s="18" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C299" s="19" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D299" s="20" t="s">
         <v>25</v>
@@ -11094,10 +11088,10 @@
         <v>26</v>
       </c>
       <c r="F299" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G299" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H299" s="20" t="s">
         <v>13</v>
@@ -11105,13 +11099,13 @@
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C300" s="14" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D300" s="15" t="s">
         <v>25</v>
@@ -11120,10 +11114,10 @@
         <v>26</v>
       </c>
       <c r="F300" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G300" s="15" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H300" s="15" t="s">
         <v>13</v>
@@ -11131,13 +11125,13 @@
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="17" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B301" s="18" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C301" s="19" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D301" s="20" t="s">
         <v>25</v>
@@ -11146,10 +11140,10 @@
         <v>26</v>
       </c>
       <c r="F301" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="G301" s="20" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="H301" s="20" t="s">
         <v>13</v>
@@ -11178,33 +11172,33 @@
         <v>16</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
+        <v>640</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>641</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>642</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="D2" s="22" t="s">
         <v>643</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="E2" s="22" t="s">
         <v>644</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>645</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -11227,19 +11221,19 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="23" t="s">
+        <v>646</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>647</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>648</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>649</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11247,16 +11241,16 @@
         <v>27</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>649</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>650</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>651</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="E2" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>653</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11264,16 +11258,16 @@
         <v>27</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11281,16 +11275,16 @@
         <v>27</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11298,16 +11292,16 @@
         <v>27</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11315,16 +11309,16 @@
         <v>27</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11332,16 +11326,16 @@
         <v>27</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11349,16 +11343,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11366,16 +11360,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11383,16 +11377,16 @@
         <v>27</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11400,16 +11394,16 @@
         <v>27</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11417,16 +11411,16 @@
         <v>27</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11434,16 +11428,16 @@
         <v>27</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11451,16 +11445,16 @@
         <v>27</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11468,16 +11462,16 @@
         <v>27</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11485,16 +11479,16 @@
         <v>27</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11502,16 +11496,16 @@
         <v>27</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11519,16 +11513,16 @@
         <v>27</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11536,16 +11530,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11553,16 +11547,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11570,16 +11564,16 @@
         <v>27</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11587,16 +11581,16 @@
         <v>27</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11604,16 +11598,16 @@
         <v>27</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11621,16 +11615,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11638,16 +11632,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11655,16 +11649,16 @@
         <v>27</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11672,16 +11666,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="26" t="s">
+        <v>701</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>702</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E27" s="26" t="s">
         <v>703</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>704</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>653</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11689,16 +11683,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11706,16 +11700,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11723,16 +11717,16 @@
         <v>27</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11740,16 +11734,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11757,16 +11751,16 @@
         <v>27</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11774,16 +11768,16 @@
         <v>27</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11791,16 +11785,16 @@
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11808,16 +11802,16 @@
         <v>27</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11825,16 +11819,16 @@
         <v>27</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11842,16 +11836,16 @@
         <v>27</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11859,16 +11853,16 @@
         <v>27</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11876,16 +11870,16 @@
         <v>27</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11893,16 +11887,16 @@
         <v>27</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11910,16 +11904,16 @@
         <v>27</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11927,16 +11921,16 @@
         <v>27</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11944,16 +11938,16 @@
         <v>27</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11961,16 +11955,16 @@
         <v>27</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11978,16 +11972,16 @@
         <v>27</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11995,16 +11989,16 @@
         <v>27</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12012,16 +12006,16 @@
         <v>27</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12029,16 +12023,16 @@
         <v>27</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12046,16 +12040,16 @@
         <v>27</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12063,16 +12057,16 @@
         <v>27</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12080,866 +12074,866 @@
         <v>27</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B52" s="24" t="s">
+        <v>752</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>753</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E52" s="24" t="s">
         <v>754</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>755</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>653</v>
-      </c>
-      <c r="E52" s="24" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B62" s="24" t="s">
+        <v>773</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>774</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E62" s="24" t="s">
         <v>775</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>776</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>653</v>
-      </c>
-      <c r="E62" s="24" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B72" s="24" t="s">
+        <v>794</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>795</v>
+      </c>
+      <c r="D72" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E72" s="24" t="s">
         <v>796</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>797</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>653</v>
-      </c>
-      <c r="E72" s="24" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B82" s="24" t="s">
+        <v>815</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>816</v>
+      </c>
+      <c r="D82" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E82" s="24" t="s">
         <v>817</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>818</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>653</v>
-      </c>
-      <c r="E82" s="24" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B84" s="24" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E84" s="24" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B86" s="24" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B88" s="24" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B90" s="24" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B92" s="24" t="s">
+        <v>836</v>
+      </c>
+      <c r="C92" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="D92" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E92" s="24" t="s">
         <v>838</v>
-      </c>
-      <c r="C92" s="24" t="s">
-        <v>839</v>
-      </c>
-      <c r="D92" s="25" t="s">
-        <v>653</v>
-      </c>
-      <c r="E92" s="24" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B93" s="26" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E94" s="24" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B95" s="26" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B96" s="24" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B98" s="24" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="24" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B100" s="24" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E100" s="24" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>243</v>
+        <v>27</v>
       </c>
       <c r="B101" s="26" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>

--- a/reports/excel/Vulnerability_Report.xlsx
+++ b/reports/excel/Vulnerability_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="858">
   <si>
     <t>📊 VULNERABILITY REPORT - AUTOMATION EXECUTION SUMMARY</t>
   </si>
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 03:51:22</t>
+    <t>2026-08-20 04:41:24</t>
   </si>
   <si>
     <t>TC-SEC-002</t>
@@ -182,6 +182,9 @@
   </si>
   <si>
     <t>SQLi Test: Search Query with payload "1; DROP TABLE users;--"</t>
+  </si>
+  <si>
+    <t>0.01s</t>
   </si>
   <si>
     <t>TC-SEC-016</t>
@@ -3736,18 +3739,18 @@
         <v>27</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>25</v>
@@ -3767,13 +3770,13 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>25</v>
@@ -3793,13 +3796,13 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>25</v>
@@ -3819,13 +3822,13 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>25</v>
@@ -3845,13 +3848,13 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>25</v>
@@ -3871,13 +3874,13 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>25</v>
@@ -3897,13 +3900,13 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>25</v>
@@ -3923,13 +3926,13 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>25</v>
@@ -3949,13 +3952,13 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>25</v>
@@ -3975,13 +3978,13 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>25</v>
@@ -4001,13 +4004,13 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>25</v>
@@ -4027,13 +4030,13 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>25</v>
@@ -4053,13 +4056,13 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>25</v>
@@ -4079,13 +4082,13 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>25</v>
@@ -4105,13 +4108,13 @@
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>25</v>
@@ -4131,13 +4134,13 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>25</v>
@@ -4157,13 +4160,13 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>25</v>
@@ -4183,13 +4186,13 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>25</v>
@@ -4209,13 +4212,13 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>25</v>
@@ -4235,13 +4238,13 @@
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>25</v>
@@ -4261,13 +4264,13 @@
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>25</v>
@@ -4287,13 +4290,13 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>25</v>
@@ -4313,13 +4316,13 @@
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>25</v>
@@ -4339,13 +4342,13 @@
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>25</v>
@@ -4365,13 +4368,13 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>25</v>
@@ -4391,13 +4394,13 @@
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>25</v>
@@ -4417,13 +4420,13 @@
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>25</v>
@@ -4443,13 +4446,13 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>25</v>
@@ -4469,13 +4472,13 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>25</v>
@@ -4495,13 +4498,13 @@
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>25</v>
@@ -4521,13 +4524,13 @@
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>25</v>
@@ -4547,13 +4550,13 @@
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>25</v>
@@ -4573,13 +4576,13 @@
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>25</v>
@@ -4599,13 +4602,13 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>25</v>
@@ -4625,13 +4628,13 @@
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>25</v>
@@ -4651,13 +4654,13 @@
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>25</v>
@@ -4677,13 +4680,13 @@
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>25</v>
@@ -4703,13 +4706,13 @@
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>25</v>
@@ -4729,13 +4732,13 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>25</v>
@@ -4755,13 +4758,13 @@
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>25</v>
@@ -4781,13 +4784,13 @@
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D57" s="20" t="s">
         <v>25</v>
@@ -4807,13 +4810,13 @@
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D58" s="15" t="s">
         <v>25</v>
@@ -4833,13 +4836,13 @@
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D59" s="20" t="s">
         <v>25</v>
@@ -4859,13 +4862,13 @@
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D60" s="15" t="s">
         <v>25</v>
@@ -4885,13 +4888,13 @@
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D61" s="20" t="s">
         <v>25</v>
@@ -4911,13 +4914,13 @@
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>25</v>
@@ -4937,13 +4940,13 @@
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D63" s="20" t="s">
         <v>25</v>
@@ -4963,13 +4966,13 @@
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>25</v>
@@ -4989,13 +4992,13 @@
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D65" s="20" t="s">
         <v>25</v>
@@ -5015,13 +5018,13 @@
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>25</v>
@@ -5041,13 +5044,13 @@
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D67" s="20" t="s">
         <v>25</v>
@@ -5067,13 +5070,13 @@
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>25</v>
@@ -5093,13 +5096,13 @@
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D69" s="20" t="s">
         <v>25</v>
@@ -5119,13 +5122,13 @@
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D70" s="15" t="s">
         <v>25</v>
@@ -5145,13 +5148,13 @@
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D71" s="20" t="s">
         <v>25</v>
@@ -5171,13 +5174,13 @@
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D72" s="15" t="s">
         <v>25</v>
@@ -5197,13 +5200,13 @@
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D73" s="20" t="s">
         <v>25</v>
@@ -5223,13 +5226,13 @@
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>25</v>
@@ -5249,13 +5252,13 @@
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D75" s="20" t="s">
         <v>25</v>
@@ -5275,13 +5278,13 @@
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>25</v>
@@ -5301,13 +5304,13 @@
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D77" s="20" t="s">
         <v>25</v>
@@ -5327,13 +5330,13 @@
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>25</v>
@@ -5353,13 +5356,13 @@
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D79" s="20" t="s">
         <v>25</v>
@@ -5379,13 +5382,13 @@
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>25</v>
@@ -5405,13 +5408,13 @@
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D81" s="20" t="s">
         <v>25</v>
@@ -5431,13 +5434,13 @@
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D82" s="15" t="s">
         <v>25</v>
@@ -5457,13 +5460,13 @@
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D83" s="20" t="s">
         <v>25</v>
@@ -5483,13 +5486,13 @@
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>25</v>
@@ -5509,13 +5512,13 @@
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D85" s="20" t="s">
         <v>25</v>
@@ -5535,13 +5538,13 @@
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>25</v>
@@ -5561,13 +5564,13 @@
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D87" s="20" t="s">
         <v>25</v>
@@ -5587,13 +5590,13 @@
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>25</v>
@@ -5613,13 +5616,13 @@
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D89" s="20" t="s">
         <v>25</v>
@@ -5639,13 +5642,13 @@
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>25</v>
@@ -5665,13 +5668,13 @@
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D91" s="20" t="s">
         <v>25</v>
@@ -5691,13 +5694,13 @@
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>25</v>
@@ -5717,13 +5720,13 @@
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>25</v>
@@ -5743,13 +5746,13 @@
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>25</v>
@@ -5769,13 +5772,13 @@
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D95" s="20" t="s">
         <v>25</v>
@@ -5795,13 +5798,13 @@
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>25</v>
@@ -5821,13 +5824,13 @@
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D97" s="20" t="s">
         <v>25</v>
@@ -5847,13 +5850,13 @@
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>25</v>
@@ -5873,13 +5876,13 @@
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D99" s="20" t="s">
         <v>25</v>
@@ -5899,13 +5902,13 @@
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>25</v>
@@ -5925,13 +5928,13 @@
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D101" s="20" t="s">
         <v>25</v>
@@ -5951,13 +5954,13 @@
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>25</v>
@@ -5977,13 +5980,13 @@
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D103" s="20" t="s">
         <v>25</v>
@@ -6003,13 +6006,13 @@
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D104" s="15" t="s">
         <v>25</v>
@@ -6029,13 +6032,13 @@
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D105" s="20" t="s">
         <v>25</v>
@@ -6055,13 +6058,13 @@
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>25</v>
@@ -6081,13 +6084,13 @@
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>25</v>
@@ -6107,13 +6110,13 @@
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>25</v>
@@ -6133,13 +6136,13 @@
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D109" s="20" t="s">
         <v>25</v>
@@ -6159,13 +6162,13 @@
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>25</v>
@@ -6185,13 +6188,13 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D111" s="20" t="s">
         <v>25</v>
@@ -6211,13 +6214,13 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>25</v>
@@ -6237,13 +6240,13 @@
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D113" s="20" t="s">
         <v>25</v>
@@ -6263,13 +6266,13 @@
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>25</v>
@@ -6289,13 +6292,13 @@
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D115" s="20" t="s">
         <v>25</v>
@@ -6315,13 +6318,13 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>25</v>
@@ -6341,13 +6344,13 @@
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D117" s="20" t="s">
         <v>25</v>
@@ -6367,13 +6370,13 @@
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D118" s="15" t="s">
         <v>25</v>
@@ -6393,13 +6396,13 @@
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B119" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D119" s="20" t="s">
         <v>25</v>
@@ -6419,13 +6422,13 @@
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>25</v>
@@ -6445,13 +6448,13 @@
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D121" s="20" t="s">
         <v>25</v>
@@ -6471,13 +6474,13 @@
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>25</v>
@@ -6497,13 +6500,13 @@
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D123" s="20" t="s">
         <v>25</v>
@@ -6523,13 +6526,13 @@
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D124" s="15" t="s">
         <v>25</v>
@@ -6549,13 +6552,13 @@
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D125" s="20" t="s">
         <v>25</v>
@@ -6575,13 +6578,13 @@
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>25</v>
@@ -6601,13 +6604,13 @@
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D127" s="20" t="s">
         <v>25</v>
@@ -6627,13 +6630,13 @@
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>25</v>
@@ -6653,13 +6656,13 @@
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D129" s="20" t="s">
         <v>25</v>
@@ -6679,13 +6682,13 @@
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>25</v>
@@ -6705,13 +6708,13 @@
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D131" s="20" t="s">
         <v>25</v>
@@ -6731,13 +6734,13 @@
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D132" s="15" t="s">
         <v>25</v>
@@ -6757,13 +6760,13 @@
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D133" s="20" t="s">
         <v>25</v>
@@ -6783,13 +6786,13 @@
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>25</v>
@@ -6809,13 +6812,13 @@
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D135" s="20" t="s">
         <v>25</v>
@@ -6835,13 +6838,13 @@
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>25</v>
@@ -6861,13 +6864,13 @@
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D137" s="20" t="s">
         <v>25</v>
@@ -6887,13 +6890,13 @@
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>25</v>
@@ -6913,13 +6916,13 @@
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D139" s="20" t="s">
         <v>25</v>
@@ -6939,13 +6942,13 @@
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>25</v>
@@ -6965,13 +6968,13 @@
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D141" s="20" t="s">
         <v>25</v>
@@ -6991,13 +6994,13 @@
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>25</v>
@@ -7017,13 +7020,13 @@
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D143" s="20" t="s">
         <v>25</v>
@@ -7043,13 +7046,13 @@
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>25</v>
@@ -7069,13 +7072,13 @@
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D145" s="20" t="s">
         <v>25</v>
@@ -7095,13 +7098,13 @@
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>25</v>
@@ -7121,13 +7124,13 @@
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D147" s="20" t="s">
         <v>25</v>
@@ -7147,13 +7150,13 @@
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D148" s="15" t="s">
         <v>25</v>
@@ -7173,13 +7176,13 @@
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D149" s="20" t="s">
         <v>25</v>
@@ -7199,13 +7202,13 @@
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>25</v>
@@ -7225,13 +7228,13 @@
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D151" s="20" t="s">
         <v>25</v>
@@ -7251,13 +7254,13 @@
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>25</v>
@@ -7277,13 +7280,13 @@
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B153" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D153" s="20" t="s">
         <v>25</v>
@@ -7303,13 +7306,13 @@
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D154" s="15" t="s">
         <v>25</v>
@@ -7329,13 +7332,13 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B155" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>25</v>
@@ -7355,13 +7358,13 @@
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D156" s="15" t="s">
         <v>25</v>
@@ -7381,13 +7384,13 @@
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D157" s="20" t="s">
         <v>25</v>
@@ -7407,13 +7410,13 @@
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D158" s="15" t="s">
         <v>25</v>
@@ -7433,13 +7436,13 @@
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C159" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D159" s="20" t="s">
         <v>25</v>
@@ -7459,13 +7462,13 @@
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D160" s="15" t="s">
         <v>25</v>
@@ -7485,13 +7488,13 @@
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B161" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C161" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D161" s="20" t="s">
         <v>25</v>
@@ -7511,13 +7514,13 @@
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D162" s="15" t="s">
         <v>25</v>
@@ -7537,13 +7540,13 @@
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B163" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C163" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D163" s="20" t="s">
         <v>25</v>
@@ -7563,13 +7566,13 @@
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D164" s="15" t="s">
         <v>25</v>
@@ -7589,13 +7592,13 @@
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B165" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D165" s="20" t="s">
         <v>25</v>
@@ -7615,13 +7618,13 @@
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D166" s="15" t="s">
         <v>25</v>
@@ -7641,13 +7644,13 @@
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>25</v>
@@ -7667,13 +7670,13 @@
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D168" s="15" t="s">
         <v>25</v>
@@ -7693,13 +7696,13 @@
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C169" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D169" s="20" t="s">
         <v>25</v>
@@ -7719,13 +7722,13 @@
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D170" s="15" t="s">
         <v>25</v>
@@ -7745,13 +7748,13 @@
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C171" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D171" s="20" t="s">
         <v>25</v>
@@ -7771,13 +7774,13 @@
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D172" s="15" t="s">
         <v>25</v>
@@ -7797,13 +7800,13 @@
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C173" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D173" s="20" t="s">
         <v>25</v>
@@ -7823,13 +7826,13 @@
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D174" s="15" t="s">
         <v>25</v>
@@ -7849,13 +7852,13 @@
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D175" s="20" t="s">
         <v>25</v>
@@ -7875,13 +7878,13 @@
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>25</v>
@@ -7901,13 +7904,13 @@
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="17" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B177" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D177" s="20" t="s">
         <v>25</v>
@@ -7927,13 +7930,13 @@
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D178" s="15" t="s">
         <v>25</v>
@@ -7953,13 +7956,13 @@
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B179" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C179" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D179" s="20" t="s">
         <v>25</v>
@@ -7979,13 +7982,13 @@
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D180" s="15" t="s">
         <v>25</v>
@@ -8005,13 +8008,13 @@
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D181" s="20" t="s">
         <v>25</v>
@@ -8031,13 +8034,13 @@
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D182" s="15" t="s">
         <v>25</v>
@@ -8057,13 +8060,13 @@
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B183" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C183" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D183" s="20" t="s">
         <v>25</v>
@@ -8083,13 +8086,13 @@
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D184" s="15" t="s">
         <v>25</v>
@@ -8109,13 +8112,13 @@
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C185" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D185" s="20" t="s">
         <v>25</v>
@@ -8135,13 +8138,13 @@
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D186" s="15" t="s">
         <v>25</v>
@@ -8161,13 +8164,13 @@
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B187" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C187" s="19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D187" s="20" t="s">
         <v>25</v>
@@ -8187,13 +8190,13 @@
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D188" s="15" t="s">
         <v>25</v>
@@ -8213,13 +8216,13 @@
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="17" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C189" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D189" s="20" t="s">
         <v>25</v>
@@ -8239,13 +8242,13 @@
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D190" s="15" t="s">
         <v>25</v>
@@ -8265,13 +8268,13 @@
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="17" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C191" s="19" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D191" s="20" t="s">
         <v>25</v>
@@ -8291,13 +8294,13 @@
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D192" s="15" t="s">
         <v>25</v>
@@ -8317,13 +8320,13 @@
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="17" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B193" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C193" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D193" s="20" t="s">
         <v>25</v>
@@ -8343,13 +8346,13 @@
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D194" s="15" t="s">
         <v>25</v>
@@ -8369,13 +8372,13 @@
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C195" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D195" s="20" t="s">
         <v>25</v>
@@ -8395,13 +8398,13 @@
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D196" s="15" t="s">
         <v>25</v>
@@ -8421,13 +8424,13 @@
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="17" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B197" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C197" s="19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D197" s="20" t="s">
         <v>25</v>
@@ -8447,13 +8450,13 @@
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D198" s="15" t="s">
         <v>25</v>
@@ -8473,13 +8476,13 @@
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B199" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C199" s="19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D199" s="20" t="s">
         <v>25</v>
@@ -8499,13 +8502,13 @@
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D200" s="15" t="s">
         <v>25</v>
@@ -8525,13 +8528,13 @@
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B201" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C201" s="19" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D201" s="20" t="s">
         <v>25</v>
@@ -8551,13 +8554,13 @@
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D202" s="15" t="s">
         <v>25</v>
@@ -8577,13 +8580,13 @@
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="17" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B203" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C203" s="19" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D203" s="20" t="s">
         <v>25</v>
@@ -8603,13 +8606,13 @@
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B204" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D204" s="15" t="s">
         <v>25</v>
@@ -8629,13 +8632,13 @@
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B205" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C205" s="19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D205" s="20" t="s">
         <v>25</v>
@@ -8655,13 +8658,13 @@
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B206" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D206" s="15" t="s">
         <v>25</v>
@@ -8681,13 +8684,13 @@
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B207" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C207" s="19" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D207" s="20" t="s">
         <v>25</v>
@@ -8707,13 +8710,13 @@
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B208" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D208" s="15" t="s">
         <v>25</v>
@@ -8733,13 +8736,13 @@
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="17" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B209" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C209" s="19" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D209" s="20" t="s">
         <v>25</v>
@@ -8759,13 +8762,13 @@
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B210" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D210" s="15" t="s">
         <v>25</v>
@@ -8785,13 +8788,13 @@
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B211" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D211" s="20" t="s">
         <v>25</v>
@@ -8811,13 +8814,13 @@
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D212" s="15" t="s">
         <v>25</v>
@@ -8837,13 +8840,13 @@
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="17" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B213" s="18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C213" s="19" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D213" s="20" t="s">
         <v>25</v>
@@ -8863,13 +8866,13 @@
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D214" s="15" t="s">
         <v>25</v>
@@ -8889,13 +8892,13 @@
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B215" s="18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C215" s="19" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D215" s="20" t="s">
         <v>25</v>
@@ -8915,13 +8918,13 @@
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D216" s="15" t="s">
         <v>25</v>
@@ -8941,13 +8944,13 @@
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="17" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B217" s="18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C217" s="19" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D217" s="20" t="s">
         <v>25</v>
@@ -8967,13 +8970,13 @@
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D218" s="15" t="s">
         <v>25</v>
@@ -8993,13 +8996,13 @@
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B219" s="18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>25</v>
@@ -9019,13 +9022,13 @@
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D220" s="15" t="s">
         <v>25</v>
@@ -9045,13 +9048,13 @@
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="17" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B221" s="18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C221" s="19" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D221" s="20" t="s">
         <v>25</v>
@@ -9071,13 +9074,13 @@
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B222" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D222" s="15" t="s">
         <v>25</v>
@@ -9097,13 +9100,13 @@
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="17" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B223" s="18" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C223" s="19" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D223" s="20" t="s">
         <v>25</v>
@@ -9123,13 +9126,13 @@
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D224" s="15" t="s">
         <v>25</v>
@@ -9149,13 +9152,13 @@
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B225" s="18" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D225" s="20" t="s">
         <v>25</v>
@@ -9175,13 +9178,13 @@
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D226" s="15" t="s">
         <v>25</v>
@@ -9201,13 +9204,13 @@
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="17" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B227" s="18" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C227" s="19" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>25</v>
@@ -9227,13 +9230,13 @@
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D228" s="15" t="s">
         <v>25</v>
@@ -9253,13 +9256,13 @@
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="17" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B229" s="18" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C229" s="19" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>25</v>
@@ -9279,13 +9282,13 @@
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B230" s="13" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D230" s="15" t="s">
         <v>25</v>
@@ -9305,13 +9308,13 @@
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B231" s="18" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C231" s="19" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D231" s="20" t="s">
         <v>25</v>
@@ -9331,13 +9334,13 @@
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B232" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D232" s="15" t="s">
         <v>25</v>
@@ -9357,13 +9360,13 @@
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="17" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C233" s="19" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>25</v>
@@ -9383,13 +9386,13 @@
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>25</v>
@@ -9409,13 +9412,13 @@
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="17" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B235" s="18" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C235" s="19" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>25</v>
@@ -9435,13 +9438,13 @@
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C236" s="14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D236" s="15" t="s">
         <v>25</v>
@@ -9461,13 +9464,13 @@
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="17" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B237" s="18" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C237" s="19" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>25</v>
@@ -9487,13 +9490,13 @@
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B238" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>25</v>
@@ -9513,13 +9516,13 @@
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="17" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B239" s="18" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C239" s="19" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>25</v>
@@ -9539,13 +9542,13 @@
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B240" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D240" s="15" t="s">
         <v>25</v>
@@ -9565,13 +9568,13 @@
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B241" s="18" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C241" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>25</v>
@@ -9591,13 +9594,13 @@
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B242" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D242" s="15" t="s">
         <v>25</v>
@@ -9617,13 +9620,13 @@
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B243" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C243" s="19" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>25</v>
@@ -9643,13 +9646,13 @@
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D244" s="15" t="s">
         <v>25</v>
@@ -9669,13 +9672,13 @@
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="17" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B245" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C245" s="19" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D245" s="20" t="s">
         <v>25</v>
@@ -9695,13 +9698,13 @@
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D246" s="15" t="s">
         <v>25</v>
@@ -9721,13 +9724,13 @@
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="17" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C247" s="19" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D247" s="20" t="s">
         <v>25</v>
@@ -9747,13 +9750,13 @@
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D248" s="15" t="s">
         <v>25</v>
@@ -9773,13 +9776,13 @@
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="17" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C249" s="19" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D249" s="20" t="s">
         <v>25</v>
@@ -9799,13 +9802,13 @@
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D250" s="15" t="s">
         <v>25</v>
@@ -9825,13 +9828,13 @@
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="17" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C251" s="19" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D251" s="20" t="s">
         <v>25</v>
@@ -9851,13 +9854,13 @@
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B252" s="13" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D252" s="15" t="s">
         <v>25</v>
@@ -9877,13 +9880,13 @@
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C253" s="19" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>25</v>
@@ -9903,13 +9906,13 @@
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D254" s="15" t="s">
         <v>25</v>
@@ -9929,13 +9932,13 @@
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="17" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C255" s="19" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D255" s="20" t="s">
         <v>25</v>
@@ -9955,13 +9958,13 @@
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B256" s="13" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D256" s="15" t="s">
         <v>25</v>
@@ -9981,13 +9984,13 @@
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="17" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B257" s="18" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C257" s="19" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D257" s="20" t="s">
         <v>25</v>
@@ -10007,13 +10010,13 @@
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B258" s="13" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D258" s="15" t="s">
         <v>25</v>
@@ -10033,13 +10036,13 @@
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="17" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B259" s="18" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C259" s="19" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D259" s="20" t="s">
         <v>25</v>
@@ -10059,13 +10062,13 @@
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B260" s="13" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D260" s="15" t="s">
         <v>25</v>
@@ -10085,13 +10088,13 @@
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="17" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B261" s="18" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C261" s="19" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D261" s="20" t="s">
         <v>25</v>
@@ -10111,13 +10114,13 @@
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B262" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D262" s="15" t="s">
         <v>25</v>
@@ -10137,13 +10140,13 @@
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="17" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B263" s="18" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C263" s="19" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D263" s="20" t="s">
         <v>25</v>
@@ -10163,13 +10166,13 @@
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B264" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C264" s="14" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D264" s="15" t="s">
         <v>25</v>
@@ -10189,13 +10192,13 @@
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="17" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B265" s="18" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C265" s="19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D265" s="20" t="s">
         <v>25</v>
@@ -10215,13 +10218,13 @@
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D266" s="15" t="s">
         <v>25</v>
@@ -10241,13 +10244,13 @@
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="17" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B267" s="18" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C267" s="19" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D267" s="20" t="s">
         <v>25</v>
@@ -10267,13 +10270,13 @@
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>25</v>
@@ -10293,13 +10296,13 @@
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="17" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B269" s="18" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C269" s="19" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D269" s="20" t="s">
         <v>25</v>
@@ -10319,13 +10322,13 @@
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D270" s="15" t="s">
         <v>25</v>
@@ -10345,13 +10348,13 @@
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="17" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B271" s="18" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C271" s="19" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D271" s="20" t="s">
         <v>25</v>
@@ -10371,13 +10374,13 @@
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B272" s="13" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C272" s="14" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D272" s="15" t="s">
         <v>25</v>
@@ -10397,13 +10400,13 @@
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B273" s="18" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C273" s="19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D273" s="20" t="s">
         <v>25</v>
@@ -10423,13 +10426,13 @@
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B274" s="13" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D274" s="15" t="s">
         <v>25</v>
@@ -10449,13 +10452,13 @@
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="17" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B275" s="18" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C275" s="19" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D275" s="20" t="s">
         <v>25</v>
@@ -10475,13 +10478,13 @@
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D276" s="15" t="s">
         <v>25</v>
@@ -10501,13 +10504,13 @@
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="17" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B277" s="18" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C277" s="19" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D277" s="20" t="s">
         <v>25</v>
@@ -10527,13 +10530,13 @@
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B278" s="13" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D278" s="15" t="s">
         <v>25</v>
@@ -10553,13 +10556,13 @@
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B279" s="18" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C279" s="19" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D279" s="20" t="s">
         <v>25</v>
@@ -10579,13 +10582,13 @@
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D280" s="15" t="s">
         <v>25</v>
@@ -10605,13 +10608,13 @@
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="17" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B281" s="18" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C281" s="19" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D281" s="20" t="s">
         <v>25</v>
@@ -10631,13 +10634,13 @@
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B282" s="13" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C282" s="14" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D282" s="15" t="s">
         <v>25</v>
@@ -10657,13 +10660,13 @@
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B283" s="18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C283" s="19" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D283" s="20" t="s">
         <v>25</v>
@@ -10683,13 +10686,13 @@
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D284" s="15" t="s">
         <v>25</v>
@@ -10709,13 +10712,13 @@
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="17" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B285" s="18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C285" s="19" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D285" s="20" t="s">
         <v>25</v>
@@ -10735,13 +10738,13 @@
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B286" s="13" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D286" s="15" t="s">
         <v>25</v>
@@ -10761,13 +10764,13 @@
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="17" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B287" s="18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C287" s="19" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D287" s="20" t="s">
         <v>25</v>
@@ -10787,13 +10790,13 @@
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B288" s="13" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D288" s="15" t="s">
         <v>25</v>
@@ -10813,13 +10816,13 @@
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="17" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B289" s="18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C289" s="19" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D289" s="20" t="s">
         <v>25</v>
@@ -10839,13 +10842,13 @@
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B290" s="13" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D290" s="15" t="s">
         <v>25</v>
@@ -10865,13 +10868,13 @@
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="17" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B291" s="18" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C291" s="19" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D291" s="20" t="s">
         <v>25</v>
@@ -10891,13 +10894,13 @@
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B292" s="13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C292" s="14" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D292" s="15" t="s">
         <v>25</v>
@@ -10917,13 +10920,13 @@
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="17" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B293" s="18" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C293" s="19" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D293" s="20" t="s">
         <v>25</v>
@@ -10943,13 +10946,13 @@
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D294" s="15" t="s">
         <v>25</v>
@@ -10969,13 +10972,13 @@
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="17" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B295" s="18" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C295" s="19" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D295" s="20" t="s">
         <v>25</v>
@@ -10995,13 +10998,13 @@
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D296" s="15" t="s">
         <v>25</v>
@@ -11021,13 +11024,13 @@
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="17" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C297" s="19" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D297" s="20" t="s">
         <v>25</v>
@@ -11047,13 +11050,13 @@
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B298" s="13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D298" s="15" t="s">
         <v>25</v>
@@ -11073,13 +11076,13 @@
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B299" s="18" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C299" s="19" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D299" s="20" t="s">
         <v>25</v>
@@ -11099,13 +11102,13 @@
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C300" s="14" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D300" s="15" t="s">
         <v>25</v>
@@ -11125,13 +11128,13 @@
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="17" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B301" s="18" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C301" s="19" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D301" s="20" t="s">
         <v>25</v>
@@ -11172,33 +11175,33 @@
         <v>16</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -11221,19 +11224,19 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11241,16 +11244,16 @@
         <v>27</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11258,16 +11261,16 @@
         <v>27</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>654</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>655</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>652</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>653</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>654</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11275,16 +11278,16 @@
         <v>27</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11292,16 +11295,16 @@
         <v>27</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11309,16 +11312,16 @@
         <v>27</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11326,16 +11329,16 @@
         <v>27</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11343,16 +11346,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11360,16 +11363,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11377,16 +11380,16 @@
         <v>27</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11394,16 +11397,16 @@
         <v>27</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11411,16 +11414,16 @@
         <v>27</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11428,16 +11431,16 @@
         <v>27</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11445,16 +11448,16 @@
         <v>27</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11462,16 +11465,16 @@
         <v>27</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11479,16 +11482,16 @@
         <v>27</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11496,16 +11499,16 @@
         <v>27</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11513,16 +11516,16 @@
         <v>27</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11530,16 +11533,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11547,16 +11550,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11564,16 +11567,16 @@
         <v>27</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11581,16 +11584,16 @@
         <v>27</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11598,16 +11601,16 @@
         <v>27</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11615,16 +11618,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11632,16 +11635,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11649,16 +11652,16 @@
         <v>27</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11666,16 +11669,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11683,16 +11686,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="24" t="s">
+        <v>705</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>706</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>652</v>
+      </c>
+      <c r="E28" s="24" t="s">
         <v>704</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>705</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>651</v>
-      </c>
-      <c r="E28" s="24" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11700,16 +11703,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11717,16 +11720,16 @@
         <v>27</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11734,16 +11737,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11751,16 +11754,16 @@
         <v>27</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11768,16 +11771,16 @@
         <v>27</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11785,16 +11788,16 @@
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11802,16 +11805,16 @@
         <v>27</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11819,16 +11822,16 @@
         <v>27</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11836,16 +11839,16 @@
         <v>27</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11853,16 +11856,16 @@
         <v>27</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11870,16 +11873,16 @@
         <v>27</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11887,16 +11890,16 @@
         <v>27</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11904,16 +11907,16 @@
         <v>27</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11921,16 +11924,16 @@
         <v>27</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11938,16 +11941,16 @@
         <v>27</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11955,16 +11958,16 @@
         <v>27</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11972,16 +11975,16 @@
         <v>27</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11989,16 +11992,16 @@
         <v>27</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12006,16 +12009,16 @@
         <v>27</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12023,16 +12026,16 @@
         <v>27</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12040,16 +12043,16 @@
         <v>27</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12057,16 +12060,16 @@
         <v>27</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12074,16 +12077,16 @@
         <v>27</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12091,16 +12094,16 @@
         <v>27</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12108,16 +12111,16 @@
         <v>27</v>
       </c>
       <c r="B53" s="26" t="s">
+        <v>756</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>757</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>652</v>
+      </c>
+      <c r="E53" s="26" t="s">
         <v>755</v>
-      </c>
-      <c r="C53" s="26" t="s">
-        <v>756</v>
-      </c>
-      <c r="D53" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E53" s="26" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12125,16 +12128,16 @@
         <v>27</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12142,16 +12145,16 @@
         <v>27</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12159,16 +12162,16 @@
         <v>27</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12176,16 +12179,16 @@
         <v>27</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12193,16 +12196,16 @@
         <v>27</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12210,16 +12213,16 @@
         <v>27</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12227,16 +12230,16 @@
         <v>27</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12244,16 +12247,16 @@
         <v>27</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12261,16 +12264,16 @@
         <v>27</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12278,16 +12281,16 @@
         <v>27</v>
       </c>
       <c r="B63" s="26" t="s">
+        <v>777</v>
+      </c>
+      <c r="C63" s="26" t="s">
+        <v>778</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>652</v>
+      </c>
+      <c r="E63" s="26" t="s">
         <v>776</v>
-      </c>
-      <c r="C63" s="26" t="s">
-        <v>777</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E63" s="26" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12295,16 +12298,16 @@
         <v>27</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12312,16 +12315,16 @@
         <v>27</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12329,16 +12332,16 @@
         <v>27</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12346,16 +12349,16 @@
         <v>27</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12363,16 +12366,16 @@
         <v>27</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12380,16 +12383,16 @@
         <v>27</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12397,16 +12400,16 @@
         <v>27</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12414,16 +12417,16 @@
         <v>27</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12431,16 +12434,16 @@
         <v>27</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E72" s="24" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12448,16 +12451,16 @@
         <v>27</v>
       </c>
       <c r="B73" s="26" t="s">
+        <v>798</v>
+      </c>
+      <c r="C73" s="26" t="s">
+        <v>799</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>652</v>
+      </c>
+      <c r="E73" s="26" t="s">
         <v>797</v>
-      </c>
-      <c r="C73" s="26" t="s">
-        <v>798</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E73" s="26" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12465,16 +12468,16 @@
         <v>27</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12482,16 +12485,16 @@
         <v>27</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12499,16 +12502,16 @@
         <v>27</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12516,16 +12519,16 @@
         <v>27</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12533,16 +12536,16 @@
         <v>27</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12550,16 +12553,16 @@
         <v>27</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12567,16 +12570,16 @@
         <v>27</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12584,16 +12587,16 @@
         <v>27</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12601,16 +12604,16 @@
         <v>27</v>
       </c>
       <c r="B82" s="24" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E82" s="24" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12618,16 +12621,16 @@
         <v>27</v>
       </c>
       <c r="B83" s="26" t="s">
+        <v>819</v>
+      </c>
+      <c r="C83" s="26" t="s">
+        <v>820</v>
+      </c>
+      <c r="D83" s="27" t="s">
+        <v>652</v>
+      </c>
+      <c r="E83" s="26" t="s">
         <v>818</v>
-      </c>
-      <c r="C83" s="26" t="s">
-        <v>819</v>
-      </c>
-      <c r="D83" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E83" s="26" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12635,16 +12638,16 @@
         <v>27</v>
       </c>
       <c r="B84" s="24" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E84" s="24" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12652,16 +12655,16 @@
         <v>27</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12669,16 +12672,16 @@
         <v>27</v>
       </c>
       <c r="B86" s="24" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12686,16 +12689,16 @@
         <v>27</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12703,16 +12706,16 @@
         <v>27</v>
       </c>
       <c r="B88" s="24" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12720,16 +12723,16 @@
         <v>27</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12737,16 +12740,16 @@
         <v>27</v>
       </c>
       <c r="B90" s="24" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12754,16 +12757,16 @@
         <v>27</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12771,16 +12774,16 @@
         <v>27</v>
       </c>
       <c r="B92" s="24" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C92" s="24" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D92" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E92" s="24" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12788,16 +12791,16 @@
         <v>27</v>
       </c>
       <c r="B93" s="26" t="s">
+        <v>840</v>
+      </c>
+      <c r="C93" s="26" t="s">
+        <v>841</v>
+      </c>
+      <c r="D93" s="27" t="s">
+        <v>652</v>
+      </c>
+      <c r="E93" s="26" t="s">
         <v>839</v>
-      </c>
-      <c r="C93" s="26" t="s">
-        <v>840</v>
-      </c>
-      <c r="D93" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="E93" s="26" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12805,16 +12808,16 @@
         <v>27</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C94" s="24" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D94" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E94" s="24" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12822,16 +12825,16 @@
         <v>27</v>
       </c>
       <c r="B95" s="26" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12839,16 +12842,16 @@
         <v>27</v>
       </c>
       <c r="B96" s="24" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C96" s="24" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D96" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12856,16 +12859,16 @@
         <v>27</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12873,16 +12876,16 @@
         <v>27</v>
       </c>
       <c r="B98" s="24" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C98" s="24" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D98" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12890,16 +12893,16 @@
         <v>27</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12907,16 +12910,16 @@
         <v>27</v>
       </c>
       <c r="B100" s="24" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C100" s="24" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D100" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E100" s="24" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12924,16 +12927,16 @@
         <v>27</v>
       </c>
       <c r="B101" s="26" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
   </sheetData>

--- a/reports/excel/Vulnerability_Report.xlsx
+++ b/reports/excel/Vulnerability_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2937" uniqueCount="857">
   <si>
     <t>📊 VULNERABILITY REPORT - AUTOMATION EXECUTION SUMMARY</t>
   </si>
@@ -97,7 +97,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 04:41:24</t>
+    <t>2026-08-20 03:51:22</t>
   </si>
   <si>
     <t>TC-SEC-002</t>
@@ -182,9 +182,6 @@
   </si>
   <si>
     <t>SQLi Test: Search Query with payload "1; DROP TABLE users;--"</t>
-  </si>
-  <si>
-    <t>0.01s</t>
   </si>
   <si>
     <t>TC-SEC-016</t>
@@ -3739,18 +3736,18 @@
         <v>27</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>25</v>
@@ -3770,13 +3767,13 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>25</v>
@@ -3796,13 +3793,13 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>25</v>
@@ -3822,13 +3819,13 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>25</v>
@@ -3848,13 +3845,13 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>25</v>
@@ -3874,13 +3871,13 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>25</v>
@@ -3900,13 +3897,13 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>25</v>
@@ -3926,13 +3923,13 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>25</v>
@@ -3952,13 +3949,13 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>25</v>
@@ -3978,13 +3975,13 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>25</v>
@@ -4004,13 +4001,13 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="C27" s="19" t="s">
         <v>78</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>79</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>25</v>
@@ -4030,13 +4027,13 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="14" t="s">
         <v>80</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>81</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>25</v>
@@ -4056,13 +4053,13 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>82</v>
-      </c>
-      <c r="B29" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>83</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>25</v>
@@ -4082,13 +4079,13 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>85</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>25</v>
@@ -4108,13 +4105,13 @@
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>86</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>87</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>25</v>
@@ -4134,13 +4131,13 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>88</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>89</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>25</v>
@@ -4160,13 +4157,13 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>90</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="19" t="s">
-        <v>91</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>25</v>
@@ -4186,13 +4183,13 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>92</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>93</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>25</v>
@@ -4212,13 +4209,13 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>94</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>95</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>25</v>
@@ -4238,13 +4235,13 @@
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>96</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>97</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>25</v>
@@ -4264,13 +4261,13 @@
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>98</v>
-      </c>
-      <c r="B37" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>99</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>25</v>
@@ -4290,13 +4287,13 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>100</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>101</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>25</v>
@@ -4316,13 +4313,13 @@
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>102</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>103</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>25</v>
@@ -4342,13 +4339,13 @@
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="14" t="s">
         <v>104</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>105</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>25</v>
@@ -4368,13 +4365,13 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>106</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>107</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>25</v>
@@ -4394,13 +4391,13 @@
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="14" t="s">
         <v>108</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>109</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>25</v>
@@ -4420,13 +4417,13 @@
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="19" t="s">
         <v>110</v>
-      </c>
-      <c r="B43" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>111</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>25</v>
@@ -4446,13 +4443,13 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" s="14" t="s">
         <v>112</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>113</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>25</v>
@@ -4472,13 +4469,13 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>114</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>115</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>25</v>
@@ -4498,13 +4495,13 @@
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>25</v>
@@ -4524,13 +4521,13 @@
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="19" t="s">
         <v>118</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>119</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>25</v>
@@ -4550,13 +4547,13 @@
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="14" t="s">
         <v>120</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>121</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>25</v>
@@ -4576,13 +4573,13 @@
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>122</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>123</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>25</v>
@@ -4602,13 +4599,13 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="14" t="s">
         <v>124</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>125</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>25</v>
@@ -4628,13 +4625,13 @@
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C51" s="19" t="s">
         <v>126</v>
-      </c>
-      <c r="B51" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>127</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>25</v>
@@ -4654,13 +4651,13 @@
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>129</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>130</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>25</v>
@@ -4680,13 +4677,13 @@
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="19" t="s">
         <v>131</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>132</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>25</v>
@@ -4706,13 +4703,13 @@
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C54" s="14" t="s">
         <v>133</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>134</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>25</v>
@@ -4732,13 +4729,13 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="19" t="s">
         <v>135</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>136</v>
       </c>
       <c r="D55" s="20" t="s">
         <v>25</v>
@@ -4758,13 +4755,13 @@
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="14" t="s">
         <v>137</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>138</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>25</v>
@@ -4784,13 +4781,13 @@
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="19" t="s">
         <v>139</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>140</v>
       </c>
       <c r="D57" s="20" t="s">
         <v>25</v>
@@ -4810,13 +4807,13 @@
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="14" t="s">
         <v>141</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>142</v>
       </c>
       <c r="D58" s="15" t="s">
         <v>25</v>
@@ -4836,13 +4833,13 @@
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="19" t="s">
         <v>143</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>144</v>
       </c>
       <c r="D59" s="20" t="s">
         <v>25</v>
@@ -4862,13 +4859,13 @@
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="14" t="s">
         <v>145</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>146</v>
       </c>
       <c r="D60" s="15" t="s">
         <v>25</v>
@@ -4888,13 +4885,13 @@
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="19" t="s">
         <v>147</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>148</v>
       </c>
       <c r="D61" s="20" t="s">
         <v>25</v>
@@ -4914,13 +4911,13 @@
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B62" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="C62" s="14" t="s">
         <v>150</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>151</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>25</v>
@@ -4940,13 +4937,13 @@
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="19" t="s">
         <v>152</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>153</v>
       </c>
       <c r="D63" s="20" t="s">
         <v>25</v>
@@ -4966,13 +4963,13 @@
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C64" s="14" t="s">
         <v>154</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>155</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>25</v>
@@ -4992,13 +4989,13 @@
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="19" t="s">
         <v>156</v>
-      </c>
-      <c r="B65" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>157</v>
       </c>
       <c r="D65" s="20" t="s">
         <v>25</v>
@@ -5018,13 +5015,13 @@
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" s="14" t="s">
         <v>158</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>159</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>25</v>
@@ -5044,13 +5041,13 @@
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C67" s="19" t="s">
         <v>160</v>
-      </c>
-      <c r="B67" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>161</v>
       </c>
       <c r="D67" s="20" t="s">
         <v>25</v>
@@ -5070,13 +5067,13 @@
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C68" s="14" t="s">
         <v>162</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>163</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>25</v>
@@ -5096,13 +5093,13 @@
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C69" s="19" t="s">
         <v>164</v>
-      </c>
-      <c r="B69" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C69" s="19" t="s">
-        <v>165</v>
       </c>
       <c r="D69" s="20" t="s">
         <v>25</v>
@@ -5122,13 +5119,13 @@
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C70" s="14" t="s">
         <v>166</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>167</v>
       </c>
       <c r="D70" s="15" t="s">
         <v>25</v>
@@ -5148,13 +5145,13 @@
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C71" s="19" t="s">
         <v>168</v>
-      </c>
-      <c r="B71" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>169</v>
       </c>
       <c r="D71" s="20" t="s">
         <v>25</v>
@@ -5174,13 +5171,13 @@
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B72" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="C72" s="14" t="s">
         <v>171</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>172</v>
       </c>
       <c r="D72" s="15" t="s">
         <v>25</v>
@@ -5200,13 +5197,13 @@
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C73" s="19" t="s">
         <v>173</v>
-      </c>
-      <c r="B73" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C73" s="19" t="s">
-        <v>174</v>
       </c>
       <c r="D73" s="20" t="s">
         <v>25</v>
@@ -5226,13 +5223,13 @@
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C74" s="14" t="s">
         <v>175</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>176</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>25</v>
@@ -5252,13 +5249,13 @@
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" s="19" t="s">
         <v>177</v>
-      </c>
-      <c r="B75" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>178</v>
       </c>
       <c r="D75" s="20" t="s">
         <v>25</v>
@@ -5278,13 +5275,13 @@
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C76" s="14" t="s">
         <v>179</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>180</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>25</v>
@@ -5304,13 +5301,13 @@
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C77" s="19" t="s">
         <v>181</v>
-      </c>
-      <c r="B77" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C77" s="19" t="s">
-        <v>182</v>
       </c>
       <c r="D77" s="20" t="s">
         <v>25</v>
@@ -5330,13 +5327,13 @@
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C78" s="14" t="s">
         <v>183</v>
-      </c>
-      <c r="B78" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>184</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>25</v>
@@ -5356,13 +5353,13 @@
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C79" s="19" t="s">
         <v>185</v>
-      </c>
-      <c r="B79" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C79" s="19" t="s">
-        <v>186</v>
       </c>
       <c r="D79" s="20" t="s">
         <v>25</v>
@@ -5382,13 +5379,13 @@
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C80" s="14" t="s">
         <v>187</v>
-      </c>
-      <c r="B80" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>188</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>25</v>
@@ -5408,13 +5405,13 @@
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" s="19" t="s">
         <v>189</v>
-      </c>
-      <c r="B81" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>190</v>
       </c>
       <c r="D81" s="20" t="s">
         <v>25</v>
@@ -5434,13 +5431,13 @@
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B82" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="C82" s="14" t="s">
         <v>192</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>193</v>
       </c>
       <c r="D82" s="15" t="s">
         <v>25</v>
@@ -5460,13 +5457,13 @@
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C83" s="19" t="s">
         <v>194</v>
-      </c>
-      <c r="B83" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>195</v>
       </c>
       <c r="D83" s="20" t="s">
         <v>25</v>
@@ -5486,13 +5483,13 @@
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C84" s="14" t="s">
         <v>196</v>
-      </c>
-      <c r="B84" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="C84" s="14" t="s">
-        <v>197</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>25</v>
@@ -5512,13 +5509,13 @@
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C85" s="19" t="s">
         <v>198</v>
-      </c>
-      <c r="B85" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>199</v>
       </c>
       <c r="D85" s="20" t="s">
         <v>25</v>
@@ -5538,13 +5535,13 @@
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C86" s="14" t="s">
         <v>200</v>
-      </c>
-      <c r="B86" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>201</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>25</v>
@@ -5564,13 +5561,13 @@
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
+        <v>201</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C87" s="19" t="s">
         <v>202</v>
-      </c>
-      <c r="B87" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C87" s="19" t="s">
-        <v>203</v>
       </c>
       <c r="D87" s="20" t="s">
         <v>25</v>
@@ -5590,13 +5587,13 @@
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="B88" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C88" s="14" t="s">
         <v>204</v>
-      </c>
-      <c r="B88" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>205</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>25</v>
@@ -5616,13 +5613,13 @@
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C89" s="19" t="s">
         <v>206</v>
-      </c>
-      <c r="B89" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C89" s="19" t="s">
-        <v>207</v>
       </c>
       <c r="D89" s="20" t="s">
         <v>25</v>
@@ -5642,13 +5639,13 @@
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B90" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" s="14" t="s">
         <v>208</v>
-      </c>
-      <c r="B90" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="C90" s="14" t="s">
-        <v>209</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>25</v>
@@ -5668,13 +5665,13 @@
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C91" s="19" t="s">
         <v>210</v>
-      </c>
-      <c r="B91" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="C91" s="19" t="s">
-        <v>211</v>
       </c>
       <c r="D91" s="20" t="s">
         <v>25</v>
@@ -5694,13 +5691,13 @@
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B92" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="C92" s="14" t="s">
         <v>213</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>214</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>25</v>
@@ -5720,13 +5717,13 @@
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C93" s="19" t="s">
         <v>215</v>
-      </c>
-      <c r="B93" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C93" s="19" t="s">
-        <v>216</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>25</v>
@@ -5746,13 +5743,13 @@
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B94" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C94" s="14" t="s">
         <v>217</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C94" s="14" t="s">
-        <v>218</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>25</v>
@@ -5772,13 +5769,13 @@
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C95" s="19" t="s">
         <v>219</v>
-      </c>
-      <c r="B95" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>220</v>
       </c>
       <c r="D95" s="20" t="s">
         <v>25</v>
@@ -5798,13 +5795,13 @@
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B96" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C96" s="14" t="s">
         <v>221</v>
-      </c>
-      <c r="B96" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C96" s="14" t="s">
-        <v>222</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>25</v>
@@ -5824,13 +5821,13 @@
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C97" s="19" t="s">
         <v>223</v>
-      </c>
-      <c r="B97" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C97" s="19" t="s">
-        <v>224</v>
       </c>
       <c r="D97" s="20" t="s">
         <v>25</v>
@@ -5850,13 +5847,13 @@
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B98" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C98" s="14" t="s">
         <v>225</v>
-      </c>
-      <c r="B98" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C98" s="14" t="s">
-        <v>226</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>25</v>
@@ -5876,13 +5873,13 @@
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B99" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C99" s="19" t="s">
         <v>227</v>
-      </c>
-      <c r="B99" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C99" s="19" t="s">
-        <v>228</v>
       </c>
       <c r="D99" s="20" t="s">
         <v>25</v>
@@ -5902,13 +5899,13 @@
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B100" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C100" s="14" t="s">
         <v>229</v>
-      </c>
-      <c r="B100" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C100" s="14" t="s">
-        <v>230</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>25</v>
@@ -5928,13 +5925,13 @@
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="B101" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C101" s="19" t="s">
         <v>231</v>
-      </c>
-      <c r="B101" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>232</v>
       </c>
       <c r="D101" s="20" t="s">
         <v>25</v>
@@ -5954,13 +5951,13 @@
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B102" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="C102" s="14" t="s">
         <v>234</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>235</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>25</v>
@@ -5980,13 +5977,13 @@
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C103" s="19" t="s">
         <v>236</v>
-      </c>
-      <c r="B103" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>237</v>
       </c>
       <c r="D103" s="20" t="s">
         <v>25</v>
@@ -6006,13 +6003,13 @@
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C104" s="14" t="s">
         <v>238</v>
-      </c>
-      <c r="B104" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="C104" s="14" t="s">
-        <v>239</v>
       </c>
       <c r="D104" s="15" t="s">
         <v>25</v>
@@ -6032,13 +6029,13 @@
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C105" s="19" t="s">
         <v>240</v>
-      </c>
-      <c r="B105" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C105" s="19" t="s">
-        <v>241</v>
       </c>
       <c r="D105" s="20" t="s">
         <v>25</v>
@@ -6058,13 +6055,13 @@
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B106" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C106" s="14" t="s">
         <v>242</v>
-      </c>
-      <c r="B106" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="C106" s="14" t="s">
-        <v>243</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>25</v>
@@ -6084,13 +6081,13 @@
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="B107" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C107" s="19" t="s">
         <v>244</v>
-      </c>
-      <c r="B107" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>245</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>25</v>
@@ -6110,13 +6107,13 @@
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="B108" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C108" s="14" t="s">
         <v>246</v>
-      </c>
-      <c r="B108" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="C108" s="14" t="s">
-        <v>247</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>25</v>
@@ -6136,13 +6133,13 @@
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B109" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C109" s="19" t="s">
         <v>248</v>
-      </c>
-      <c r="B109" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C109" s="19" t="s">
-        <v>249</v>
       </c>
       <c r="D109" s="20" t="s">
         <v>25</v>
@@ -6162,13 +6159,13 @@
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C110" s="14" t="s">
         <v>250</v>
-      </c>
-      <c r="B110" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="C110" s="14" t="s">
-        <v>251</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>25</v>
@@ -6188,13 +6185,13 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C111" s="19" t="s">
         <v>252</v>
-      </c>
-      <c r="B111" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="C111" s="19" t="s">
-        <v>253</v>
       </c>
       <c r="D111" s="20" t="s">
         <v>25</v>
@@ -6214,13 +6211,13 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B112" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="C112" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>256</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>25</v>
@@ -6240,13 +6237,13 @@
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C113" s="19" t="s">
         <v>257</v>
-      </c>
-      <c r="B113" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C113" s="19" t="s">
-        <v>258</v>
       </c>
       <c r="D113" s="20" t="s">
         <v>25</v>
@@ -6266,13 +6263,13 @@
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="B114" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" s="14" t="s">
         <v>259</v>
-      </c>
-      <c r="B114" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C114" s="14" t="s">
-        <v>260</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>25</v>
@@ -6292,13 +6289,13 @@
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="B115" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C115" s="19" t="s">
         <v>261</v>
-      </c>
-      <c r="B115" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C115" s="19" t="s">
-        <v>262</v>
       </c>
       <c r="D115" s="20" t="s">
         <v>25</v>
@@ -6318,13 +6315,13 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C116" s="14" t="s">
         <v>263</v>
-      </c>
-      <c r="B116" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C116" s="14" t="s">
-        <v>264</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>25</v>
@@ -6344,13 +6341,13 @@
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="B117" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C117" s="19" t="s">
         <v>265</v>
-      </c>
-      <c r="B117" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C117" s="19" t="s">
-        <v>266</v>
       </c>
       <c r="D117" s="20" t="s">
         <v>25</v>
@@ -6370,13 +6367,13 @@
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="B118" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C118" s="14" t="s">
         <v>267</v>
-      </c>
-      <c r="B118" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C118" s="14" t="s">
-        <v>268</v>
       </c>
       <c r="D118" s="15" t="s">
         <v>25</v>
@@ -6396,13 +6393,13 @@
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="B119" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C119" s="19" t="s">
         <v>269</v>
-      </c>
-      <c r="B119" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C119" s="19" t="s">
-        <v>270</v>
       </c>
       <c r="D119" s="20" t="s">
         <v>25</v>
@@ -6422,13 +6419,13 @@
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="B120" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C120" s="14" t="s">
         <v>271</v>
-      </c>
-      <c r="B120" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C120" s="14" t="s">
-        <v>272</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>25</v>
@@ -6448,13 +6445,13 @@
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="B121" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C121" s="19" t="s">
         <v>273</v>
-      </c>
-      <c r="B121" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C121" s="19" t="s">
-        <v>274</v>
       </c>
       <c r="D121" s="20" t="s">
         <v>25</v>
@@ -6474,13 +6471,13 @@
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B122" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="C122" s="14" t="s">
         <v>276</v>
-      </c>
-      <c r="C122" s="14" t="s">
-        <v>277</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>25</v>
@@ -6500,13 +6497,13 @@
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="B123" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C123" s="19" t="s">
         <v>278</v>
-      </c>
-      <c r="B123" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C123" s="19" t="s">
-        <v>279</v>
       </c>
       <c r="D123" s="20" t="s">
         <v>25</v>
@@ -6526,13 +6523,13 @@
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C124" s="14" t="s">
         <v>280</v>
-      </c>
-      <c r="B124" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C124" s="14" t="s">
-        <v>281</v>
       </c>
       <c r="D124" s="15" t="s">
         <v>25</v>
@@ -6552,13 +6549,13 @@
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="B125" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C125" s="19" t="s">
         <v>282</v>
-      </c>
-      <c r="B125" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C125" s="19" t="s">
-        <v>283</v>
       </c>
       <c r="D125" s="20" t="s">
         <v>25</v>
@@ -6578,13 +6575,13 @@
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="B126" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C126" s="14" t="s">
         <v>284</v>
-      </c>
-      <c r="B126" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C126" s="14" t="s">
-        <v>285</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>25</v>
@@ -6604,13 +6601,13 @@
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="B127" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C127" s="19" t="s">
         <v>286</v>
-      </c>
-      <c r="B127" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C127" s="19" t="s">
-        <v>287</v>
       </c>
       <c r="D127" s="20" t="s">
         <v>25</v>
@@ -6630,13 +6627,13 @@
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="B128" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C128" s="14" t="s">
         <v>288</v>
-      </c>
-      <c r="B128" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C128" s="14" t="s">
-        <v>289</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>25</v>
@@ -6656,13 +6653,13 @@
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="B129" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C129" s="19" t="s">
         <v>290</v>
-      </c>
-      <c r="B129" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C129" s="19" t="s">
-        <v>291</v>
       </c>
       <c r="D129" s="20" t="s">
         <v>25</v>
@@ -6682,13 +6679,13 @@
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B130" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C130" s="14" t="s">
         <v>292</v>
-      </c>
-      <c r="B130" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C130" s="14" t="s">
-        <v>293</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>25</v>
@@ -6708,13 +6705,13 @@
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="B131" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="C131" s="19" t="s">
         <v>294</v>
-      </c>
-      <c r="B131" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C131" s="19" t="s">
-        <v>295</v>
       </c>
       <c r="D131" s="20" t="s">
         <v>25</v>
@@ -6734,13 +6731,13 @@
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B132" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="C132" s="14" t="s">
         <v>297</v>
-      </c>
-      <c r="C132" s="14" t="s">
-        <v>298</v>
       </c>
       <c r="D132" s="15" t="s">
         <v>25</v>
@@ -6760,13 +6757,13 @@
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B133" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C133" s="19" t="s">
         <v>299</v>
-      </c>
-      <c r="B133" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C133" s="19" t="s">
-        <v>300</v>
       </c>
       <c r="D133" s="20" t="s">
         <v>25</v>
@@ -6786,13 +6783,13 @@
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="B134" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C134" s="14" t="s">
         <v>301</v>
-      </c>
-      <c r="B134" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C134" s="14" t="s">
-        <v>302</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>25</v>
@@ -6812,13 +6809,13 @@
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="B135" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C135" s="19" t="s">
         <v>303</v>
-      </c>
-      <c r="B135" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C135" s="19" t="s">
-        <v>304</v>
       </c>
       <c r="D135" s="20" t="s">
         <v>25</v>
@@ -6838,13 +6835,13 @@
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B136" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C136" s="14" t="s">
         <v>305</v>
-      </c>
-      <c r="B136" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C136" s="14" t="s">
-        <v>306</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>25</v>
@@ -6864,13 +6861,13 @@
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="B137" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C137" s="19" t="s">
         <v>307</v>
-      </c>
-      <c r="B137" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C137" s="19" t="s">
-        <v>308</v>
       </c>
       <c r="D137" s="20" t="s">
         <v>25</v>
@@ -6890,13 +6887,13 @@
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B138" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C138" s="14" t="s">
         <v>309</v>
-      </c>
-      <c r="B138" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C138" s="14" t="s">
-        <v>310</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>25</v>
@@ -6916,13 +6913,13 @@
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B139" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C139" s="19" t="s">
         <v>311</v>
-      </c>
-      <c r="B139" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C139" s="19" t="s">
-        <v>312</v>
       </c>
       <c r="D139" s="20" t="s">
         <v>25</v>
@@ -6942,13 +6939,13 @@
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B140" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C140" s="14" t="s">
         <v>313</v>
-      </c>
-      <c r="B140" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C140" s="14" t="s">
-        <v>314</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>25</v>
@@ -6968,13 +6965,13 @@
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="B141" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C141" s="19" t="s">
         <v>315</v>
-      </c>
-      <c r="B141" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="C141" s="19" t="s">
-        <v>316</v>
       </c>
       <c r="D141" s="20" t="s">
         <v>25</v>
@@ -6994,13 +6991,13 @@
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B142" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="B142" s="13" t="s">
+      <c r="C142" s="14" t="s">
         <v>318</v>
-      </c>
-      <c r="C142" s="14" t="s">
-        <v>319</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>25</v>
@@ -7020,13 +7017,13 @@
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="B143" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C143" s="19" t="s">
         <v>320</v>
-      </c>
-      <c r="B143" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C143" s="19" t="s">
-        <v>321</v>
       </c>
       <c r="D143" s="20" t="s">
         <v>25</v>
@@ -7046,13 +7043,13 @@
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C144" s="14" t="s">
         <v>322</v>
-      </c>
-      <c r="B144" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="C144" s="14" t="s">
-        <v>323</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>25</v>
@@ -7072,13 +7069,13 @@
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="B145" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C145" s="19" t="s">
         <v>324</v>
-      </c>
-      <c r="B145" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C145" s="19" t="s">
-        <v>325</v>
       </c>
       <c r="D145" s="20" t="s">
         <v>25</v>
@@ -7098,13 +7095,13 @@
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="B146" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C146" s="14" t="s">
         <v>326</v>
-      </c>
-      <c r="B146" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="C146" s="14" t="s">
-        <v>327</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>25</v>
@@ -7124,13 +7121,13 @@
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="B147" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C147" s="19" t="s">
         <v>328</v>
-      </c>
-      <c r="B147" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C147" s="19" t="s">
-        <v>329</v>
       </c>
       <c r="D147" s="20" t="s">
         <v>25</v>
@@ -7150,13 +7147,13 @@
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="B148" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C148" s="14" t="s">
         <v>330</v>
-      </c>
-      <c r="B148" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="C148" s="14" t="s">
-        <v>331</v>
       </c>
       <c r="D148" s="15" t="s">
         <v>25</v>
@@ -7176,13 +7173,13 @@
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B149" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C149" s="19" t="s">
         <v>332</v>
-      </c>
-      <c r="B149" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C149" s="19" t="s">
-        <v>333</v>
       </c>
       <c r="D149" s="20" t="s">
         <v>25</v>
@@ -7202,13 +7199,13 @@
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="B150" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C150" s="14" t="s">
         <v>334</v>
-      </c>
-      <c r="B150" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="C150" s="14" t="s">
-        <v>335</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>25</v>
@@ -7228,13 +7225,13 @@
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="B151" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="C151" s="19" t="s">
         <v>336</v>
-      </c>
-      <c r="B151" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C151" s="19" t="s">
-        <v>337</v>
       </c>
       <c r="D151" s="20" t="s">
         <v>25</v>
@@ -7254,13 +7251,13 @@
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B152" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="B152" s="13" t="s">
+      <c r="C152" s="14" t="s">
         <v>339</v>
-      </c>
-      <c r="C152" s="14" t="s">
-        <v>340</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>25</v>
@@ -7280,13 +7277,13 @@
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="B153" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C153" s="19" t="s">
         <v>341</v>
-      </c>
-      <c r="B153" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C153" s="19" t="s">
-        <v>342</v>
       </c>
       <c r="D153" s="20" t="s">
         <v>25</v>
@@ -7306,13 +7303,13 @@
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="B154" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C154" s="14" t="s">
         <v>343</v>
-      </c>
-      <c r="B154" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C154" s="14" t="s">
-        <v>344</v>
       </c>
       <c r="D154" s="15" t="s">
         <v>25</v>
@@ -7332,13 +7329,13 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="B155" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C155" s="19" t="s">
         <v>345</v>
-      </c>
-      <c r="B155" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C155" s="19" t="s">
-        <v>346</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>25</v>
@@ -7358,13 +7355,13 @@
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="B156" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C156" s="14" t="s">
         <v>347</v>
-      </c>
-      <c r="B156" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C156" s="14" t="s">
-        <v>348</v>
       </c>
       <c r="D156" s="15" t="s">
         <v>25</v>
@@ -7384,13 +7381,13 @@
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
+        <v>348</v>
+      </c>
+      <c r="B157" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C157" s="19" t="s">
         <v>349</v>
-      </c>
-      <c r="B157" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C157" s="19" t="s">
-        <v>350</v>
       </c>
       <c r="D157" s="20" t="s">
         <v>25</v>
@@ -7410,13 +7407,13 @@
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C158" s="14" t="s">
         <v>351</v>
-      </c>
-      <c r="B158" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C158" s="14" t="s">
-        <v>352</v>
       </c>
       <c r="D158" s="15" t="s">
         <v>25</v>
@@ -7436,13 +7433,13 @@
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="B159" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="C159" s="19" t="s">
         <v>353</v>
-      </c>
-      <c r="B159" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C159" s="19" t="s">
-        <v>354</v>
       </c>
       <c r="D159" s="20" t="s">
         <v>25</v>
@@ -7462,13 +7459,13 @@
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="B160" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C160" s="14" t="s">
         <v>355</v>
-      </c>
-      <c r="B160" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C160" s="14" t="s">
-        <v>356</v>
       </c>
       <c r="D160" s="15" t="s">
         <v>25</v>
@@ -7488,13 +7485,13 @@
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="B161" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="B161" s="18" t="s">
-        <v>339</v>
-      </c>
       <c r="C161" s="19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D161" s="20" t="s">
         <v>25</v>
@@ -7514,13 +7511,13 @@
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B162" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="C162" s="14" t="s">
         <v>358</v>
-      </c>
-      <c r="C162" s="14" t="s">
-        <v>359</v>
       </c>
       <c r="D162" s="15" t="s">
         <v>25</v>
@@ -7540,13 +7537,13 @@
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B163" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C163" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D163" s="20" t="s">
         <v>25</v>
@@ -7566,13 +7563,13 @@
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D164" s="15" t="s">
         <v>25</v>
@@ -7592,13 +7589,13 @@
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B165" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D165" s="20" t="s">
         <v>25</v>
@@ -7618,13 +7615,13 @@
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D166" s="15" t="s">
         <v>25</v>
@@ -7644,13 +7641,13 @@
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>25</v>
@@ -7670,13 +7667,13 @@
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="B168" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="C168" s="14" t="s">
         <v>365</v>
-      </c>
-      <c r="B168" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="C168" s="14" t="s">
-        <v>366</v>
       </c>
       <c r="D168" s="15" t="s">
         <v>25</v>
@@ -7696,13 +7693,13 @@
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="17" t="s">
+        <v>366</v>
+      </c>
+      <c r="B169" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="C169" s="19" t="s">
         <v>367</v>
-      </c>
-      <c r="B169" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="C169" s="19" t="s">
-        <v>368</v>
       </c>
       <c r="D169" s="20" t="s">
         <v>25</v>
@@ -7722,13 +7719,13 @@
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B170" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="C170" s="14" t="s">
         <v>369</v>
-      </c>
-      <c r="B170" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="C170" s="14" t="s">
-        <v>370</v>
       </c>
       <c r="D170" s="15" t="s">
         <v>25</v>
@@ -7748,13 +7745,13 @@
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C171" s="19" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D171" s="20" t="s">
         <v>25</v>
@@ -7774,13 +7771,13 @@
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B172" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C172" s="14" t="s">
         <v>372</v>
-      </c>
-      <c r="C172" s="14" t="s">
-        <v>373</v>
       </c>
       <c r="D172" s="15" t="s">
         <v>25</v>
@@ -7800,13 +7797,13 @@
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C173" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D173" s="20" t="s">
         <v>25</v>
@@ -7826,13 +7823,13 @@
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D174" s="15" t="s">
         <v>25</v>
@@ -7852,13 +7849,13 @@
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D175" s="20" t="s">
         <v>25</v>
@@ -7878,13 +7875,13 @@
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>25</v>
@@ -7904,13 +7901,13 @@
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B177" s="18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D177" s="20" t="s">
         <v>25</v>
@@ -7930,13 +7927,13 @@
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
+        <v>378</v>
+      </c>
+      <c r="B178" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C178" s="14" t="s">
         <v>379</v>
-      </c>
-      <c r="B178" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="C178" s="14" t="s">
-        <v>380</v>
       </c>
       <c r="D178" s="15" t="s">
         <v>25</v>
@@ -7956,13 +7953,13 @@
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
+        <v>380</v>
+      </c>
+      <c r="B179" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C179" s="19" t="s">
         <v>381</v>
-      </c>
-      <c r="B179" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="C179" s="19" t="s">
-        <v>382</v>
       </c>
       <c r="D179" s="20" t="s">
         <v>25</v>
@@ -7982,13 +7979,13 @@
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B180" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C180" s="14" t="s">
         <v>383</v>
-      </c>
-      <c r="B180" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="C180" s="14" t="s">
-        <v>384</v>
       </c>
       <c r="D180" s="15" t="s">
         <v>25</v>
@@ -8008,13 +8005,13 @@
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D181" s="20" t="s">
         <v>25</v>
@@ -8034,13 +8031,13 @@
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="B182" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="B182" s="13" t="s">
+      <c r="C182" s="14" t="s">
         <v>387</v>
-      </c>
-      <c r="C182" s="14" t="s">
-        <v>388</v>
       </c>
       <c r="D182" s="15" t="s">
         <v>25</v>
@@ -8060,13 +8057,13 @@
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="B183" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C183" s="19" t="s">
         <v>389</v>
-      </c>
-      <c r="B183" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C183" s="19" t="s">
-        <v>390</v>
       </c>
       <c r="D183" s="20" t="s">
         <v>25</v>
@@ -8086,13 +8083,13 @@
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="B184" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C184" s="14" t="s">
         <v>391</v>
-      </c>
-      <c r="B184" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C184" s="14" t="s">
-        <v>392</v>
       </c>
       <c r="D184" s="15" t="s">
         <v>25</v>
@@ -8112,13 +8109,13 @@
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="B185" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C185" s="19" t="s">
         <v>393</v>
-      </c>
-      <c r="B185" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C185" s="19" t="s">
-        <v>394</v>
       </c>
       <c r="D185" s="20" t="s">
         <v>25</v>
@@ -8138,13 +8135,13 @@
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="B186" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C186" s="14" t="s">
         <v>395</v>
-      </c>
-      <c r="B186" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C186" s="14" t="s">
-        <v>396</v>
       </c>
       <c r="D186" s="15" t="s">
         <v>25</v>
@@ -8164,13 +8161,13 @@
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="B187" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C187" s="19" t="s">
         <v>397</v>
-      </c>
-      <c r="B187" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C187" s="19" t="s">
-        <v>398</v>
       </c>
       <c r="D187" s="20" t="s">
         <v>25</v>
@@ -8190,13 +8187,13 @@
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="B188" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C188" s="14" t="s">
         <v>399</v>
-      </c>
-      <c r="B188" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C188" s="14" t="s">
-        <v>400</v>
       </c>
       <c r="D188" s="15" t="s">
         <v>25</v>
@@ -8216,13 +8213,13 @@
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="B189" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C189" s="19" t="s">
         <v>401</v>
-      </c>
-      <c r="B189" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C189" s="19" t="s">
-        <v>402</v>
       </c>
       <c r="D189" s="20" t="s">
         <v>25</v>
@@ -8242,13 +8239,13 @@
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="B190" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C190" s="14" t="s">
         <v>403</v>
-      </c>
-      <c r="B190" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C190" s="14" t="s">
-        <v>404</v>
       </c>
       <c r="D190" s="15" t="s">
         <v>25</v>
@@ -8268,13 +8265,13 @@
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="B191" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C191" s="19" t="s">
         <v>405</v>
-      </c>
-      <c r="B191" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="C191" s="19" t="s">
-        <v>406</v>
       </c>
       <c r="D191" s="20" t="s">
         <v>25</v>
@@ -8294,13 +8291,13 @@
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="B192" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="B192" s="13" t="s">
+      <c r="C192" s="14" t="s">
         <v>408</v>
-      </c>
-      <c r="C192" s="14" t="s">
-        <v>409</v>
       </c>
       <c r="D192" s="15" t="s">
         <v>25</v>
@@ -8320,13 +8317,13 @@
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B193" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C193" s="19" t="s">
         <v>410</v>
-      </c>
-      <c r="B193" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C193" s="19" t="s">
-        <v>411</v>
       </c>
       <c r="D193" s="20" t="s">
         <v>25</v>
@@ -8346,13 +8343,13 @@
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="B194" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="C194" s="14" t="s">
         <v>412</v>
-      </c>
-      <c r="B194" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="C194" s="14" t="s">
-        <v>413</v>
       </c>
       <c r="D194" s="15" t="s">
         <v>25</v>
@@ -8372,13 +8369,13 @@
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="B195" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C195" s="19" t="s">
         <v>414</v>
-      </c>
-      <c r="B195" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C195" s="19" t="s">
-        <v>415</v>
       </c>
       <c r="D195" s="20" t="s">
         <v>25</v>
@@ -8398,13 +8395,13 @@
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="B196" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="C196" s="14" t="s">
         <v>416</v>
-      </c>
-      <c r="B196" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="C196" s="14" t="s">
-        <v>417</v>
       </c>
       <c r="D196" s="15" t="s">
         <v>25</v>
@@ -8424,13 +8421,13 @@
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="B197" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C197" s="19" t="s">
         <v>418</v>
-      </c>
-      <c r="B197" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C197" s="19" t="s">
-        <v>419</v>
       </c>
       <c r="D197" s="20" t="s">
         <v>25</v>
@@ -8450,13 +8447,13 @@
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="B198" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="C198" s="14" t="s">
         <v>420</v>
-      </c>
-      <c r="B198" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="C198" s="14" t="s">
-        <v>421</v>
       </c>
       <c r="D198" s="15" t="s">
         <v>25</v>
@@ -8476,13 +8473,13 @@
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
+        <v>421</v>
+      </c>
+      <c r="B199" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C199" s="19" t="s">
         <v>422</v>
-      </c>
-      <c r="B199" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C199" s="19" t="s">
-        <v>423</v>
       </c>
       <c r="D199" s="20" t="s">
         <v>25</v>
@@ -8502,13 +8499,13 @@
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="B200" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="C200" s="14" t="s">
         <v>424</v>
-      </c>
-      <c r="B200" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="C200" s="14" t="s">
-        <v>425</v>
       </c>
       <c r="D200" s="15" t="s">
         <v>25</v>
@@ -8528,13 +8525,13 @@
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="B201" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="C201" s="19" t="s">
         <v>426</v>
-      </c>
-      <c r="B201" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="C201" s="19" t="s">
-        <v>427</v>
       </c>
       <c r="D201" s="20" t="s">
         <v>25</v>
@@ -8554,13 +8551,13 @@
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="B202" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="B202" s="13" t="s">
+      <c r="C202" s="14" t="s">
         <v>429</v>
-      </c>
-      <c r="C202" s="14" t="s">
-        <v>430</v>
       </c>
       <c r="D202" s="15" t="s">
         <v>25</v>
@@ -8580,13 +8577,13 @@
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="17" t="s">
+        <v>430</v>
+      </c>
+      <c r="B203" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C203" s="19" t="s">
         <v>431</v>
-      </c>
-      <c r="B203" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="C203" s="19" t="s">
-        <v>432</v>
       </c>
       <c r="D203" s="20" t="s">
         <v>25</v>
@@ -8606,13 +8603,13 @@
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="B204" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="C204" s="14" t="s">
         <v>433</v>
-      </c>
-      <c r="B204" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="C204" s="14" t="s">
-        <v>434</v>
       </c>
       <c r="D204" s="15" t="s">
         <v>25</v>
@@ -8632,13 +8629,13 @@
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="B205" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C205" s="19" t="s">
         <v>435</v>
-      </c>
-      <c r="B205" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="C205" s="19" t="s">
-        <v>436</v>
       </c>
       <c r="D205" s="20" t="s">
         <v>25</v>
@@ -8658,13 +8655,13 @@
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="B206" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="C206" s="14" t="s">
         <v>437</v>
-      </c>
-      <c r="B206" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="C206" s="14" t="s">
-        <v>438</v>
       </c>
       <c r="D206" s="15" t="s">
         <v>25</v>
@@ -8684,13 +8681,13 @@
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="17" t="s">
+        <v>438</v>
+      </c>
+      <c r="B207" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C207" s="19" t="s">
         <v>439</v>
-      </c>
-      <c r="B207" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="C207" s="19" t="s">
-        <v>440</v>
       </c>
       <c r="D207" s="20" t="s">
         <v>25</v>
@@ -8710,13 +8707,13 @@
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="B208" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="C208" s="14" t="s">
         <v>441</v>
-      </c>
-      <c r="B208" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="C208" s="14" t="s">
-        <v>442</v>
       </c>
       <c r="D208" s="15" t="s">
         <v>25</v>
@@ -8736,13 +8733,13 @@
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="B209" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C209" s="19" t="s">
         <v>443</v>
-      </c>
-      <c r="B209" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="C209" s="19" t="s">
-        <v>444</v>
       </c>
       <c r="D209" s="20" t="s">
         <v>25</v>
@@ -8762,13 +8759,13 @@
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="B210" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="C210" s="14" t="s">
         <v>445</v>
-      </c>
-      <c r="B210" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="C210" s="14" t="s">
-        <v>446</v>
       </c>
       <c r="D210" s="15" t="s">
         <v>25</v>
@@ -8788,13 +8785,13 @@
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="B211" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C211" s="19" t="s">
         <v>447</v>
-      </c>
-      <c r="B211" s="18" t="s">
-        <v>429</v>
-      </c>
-      <c r="C211" s="19" t="s">
-        <v>448</v>
       </c>
       <c r="D211" s="20" t="s">
         <v>25</v>
@@ -8814,13 +8811,13 @@
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="B212" s="13" t="s">
         <v>449</v>
       </c>
-      <c r="B212" s="13" t="s">
+      <c r="C212" s="14" t="s">
         <v>450</v>
-      </c>
-      <c r="C212" s="14" t="s">
-        <v>451</v>
       </c>
       <c r="D212" s="15" t="s">
         <v>25</v>
@@ -8840,13 +8837,13 @@
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="17" t="s">
+        <v>451</v>
+      </c>
+      <c r="B213" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="C213" s="19" t="s">
         <v>452</v>
-      </c>
-      <c r="B213" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="C213" s="19" t="s">
-        <v>453</v>
       </c>
       <c r="D213" s="20" t="s">
         <v>25</v>
@@ -8866,13 +8863,13 @@
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="B214" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="C214" s="14" t="s">
         <v>454</v>
-      </c>
-      <c r="B214" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="C214" s="14" t="s">
-        <v>455</v>
       </c>
       <c r="D214" s="15" t="s">
         <v>25</v>
@@ -8892,13 +8889,13 @@
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="B215" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="C215" s="19" t="s">
         <v>456</v>
-      </c>
-      <c r="B215" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="C215" s="19" t="s">
-        <v>457</v>
       </c>
       <c r="D215" s="20" t="s">
         <v>25</v>
@@ -8918,13 +8915,13 @@
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="B216" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="C216" s="14" t="s">
         <v>458</v>
-      </c>
-      <c r="B216" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="C216" s="14" t="s">
-        <v>459</v>
       </c>
       <c r="D216" s="15" t="s">
         <v>25</v>
@@ -8944,13 +8941,13 @@
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="17" t="s">
+        <v>459</v>
+      </c>
+      <c r="B217" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="C217" s="19" t="s">
         <v>460</v>
-      </c>
-      <c r="B217" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="C217" s="19" t="s">
-        <v>461</v>
       </c>
       <c r="D217" s="20" t="s">
         <v>25</v>
@@ -8970,13 +8967,13 @@
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="B218" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="C218" s="14" t="s">
         <v>462</v>
-      </c>
-      <c r="B218" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="C218" s="14" t="s">
-        <v>463</v>
       </c>
       <c r="D218" s="15" t="s">
         <v>25</v>
@@ -8996,13 +8993,13 @@
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="17" t="s">
+        <v>463</v>
+      </c>
+      <c r="B219" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="C219" s="19" t="s">
         <v>464</v>
-      </c>
-      <c r="B219" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="C219" s="19" t="s">
-        <v>465</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>25</v>
@@ -9022,13 +9019,13 @@
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="B220" s="13" t="s">
+        <v>449</v>
+      </c>
+      <c r="C220" s="14" t="s">
         <v>466</v>
-      </c>
-      <c r="B220" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="C220" s="14" t="s">
-        <v>467</v>
       </c>
       <c r="D220" s="15" t="s">
         <v>25</v>
@@ -9048,13 +9045,13 @@
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="B221" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="C221" s="19" t="s">
         <v>468</v>
-      </c>
-      <c r="B221" s="18" t="s">
-        <v>450</v>
-      </c>
-      <c r="C221" s="19" t="s">
-        <v>469</v>
       </c>
       <c r="D221" s="20" t="s">
         <v>25</v>
@@ -9074,13 +9071,13 @@
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="B222" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="B222" s="13" t="s">
+      <c r="C222" s="14" t="s">
         <v>471</v>
-      </c>
-      <c r="C222" s="14" t="s">
-        <v>472</v>
       </c>
       <c r="D222" s="15" t="s">
         <v>25</v>
@@ -9100,13 +9097,13 @@
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="B223" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="C223" s="19" t="s">
         <v>473</v>
-      </c>
-      <c r="B223" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="C223" s="19" t="s">
-        <v>474</v>
       </c>
       <c r="D223" s="20" t="s">
         <v>25</v>
@@ -9126,13 +9123,13 @@
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="B224" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="C224" s="14" t="s">
         <v>475</v>
-      </c>
-      <c r="B224" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="C224" s="14" t="s">
-        <v>476</v>
       </c>
       <c r="D224" s="15" t="s">
         <v>25</v>
@@ -9152,13 +9149,13 @@
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="B225" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="C225" s="19" t="s">
         <v>477</v>
-      </c>
-      <c r="B225" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="C225" s="19" t="s">
-        <v>478</v>
       </c>
       <c r="D225" s="20" t="s">
         <v>25</v>
@@ -9178,13 +9175,13 @@
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="B226" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="C226" s="14" t="s">
         <v>479</v>
-      </c>
-      <c r="B226" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="C226" s="14" t="s">
-        <v>480</v>
       </c>
       <c r="D226" s="15" t="s">
         <v>25</v>
@@ -9204,13 +9201,13 @@
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="B227" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="C227" s="19" t="s">
         <v>481</v>
-      </c>
-      <c r="B227" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="C227" s="19" t="s">
-        <v>482</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>25</v>
@@ -9230,13 +9227,13 @@
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="B228" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="C228" s="14" t="s">
         <v>483</v>
-      </c>
-      <c r="B228" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="C228" s="14" t="s">
-        <v>484</v>
       </c>
       <c r="D228" s="15" t="s">
         <v>25</v>
@@ -9256,13 +9253,13 @@
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B229" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="C229" s="19" t="s">
         <v>485</v>
-      </c>
-      <c r="B229" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="C229" s="19" t="s">
-        <v>486</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>25</v>
@@ -9282,13 +9279,13 @@
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="B230" s="13" t="s">
+        <v>470</v>
+      </c>
+      <c r="C230" s="14" t="s">
         <v>487</v>
-      </c>
-      <c r="B230" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="C230" s="14" t="s">
-        <v>488</v>
       </c>
       <c r="D230" s="15" t="s">
         <v>25</v>
@@ -9308,13 +9305,13 @@
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="B231" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="C231" s="19" t="s">
         <v>489</v>
-      </c>
-      <c r="B231" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="C231" s="19" t="s">
-        <v>490</v>
       </c>
       <c r="D231" s="20" t="s">
         <v>25</v>
@@ -9334,13 +9331,13 @@
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="B232" s="13" t="s">
         <v>491</v>
       </c>
-      <c r="B232" s="13" t="s">
+      <c r="C232" s="14" t="s">
         <v>492</v>
-      </c>
-      <c r="C232" s="14" t="s">
-        <v>493</v>
       </c>
       <c r="D232" s="15" t="s">
         <v>25</v>
@@ -9360,13 +9357,13 @@
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="B233" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="C233" s="19" t="s">
         <v>494</v>
-      </c>
-      <c r="B233" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="C233" s="19" t="s">
-        <v>495</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>25</v>
@@ -9386,13 +9383,13 @@
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="B234" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="C234" s="14" t="s">
         <v>496</v>
-      </c>
-      <c r="B234" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="C234" s="14" t="s">
-        <v>497</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>25</v>
@@ -9412,13 +9409,13 @@
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="B235" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="C235" s="19" t="s">
         <v>498</v>
-      </c>
-      <c r="B235" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="C235" s="19" t="s">
-        <v>499</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>25</v>
@@ -9438,13 +9435,13 @@
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="B236" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="C236" s="14" t="s">
         <v>500</v>
-      </c>
-      <c r="B236" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="C236" s="14" t="s">
-        <v>501</v>
       </c>
       <c r="D236" s="15" t="s">
         <v>25</v>
@@ -9464,13 +9461,13 @@
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="B237" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="C237" s="19" t="s">
         <v>502</v>
-      </c>
-      <c r="B237" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="C237" s="19" t="s">
-        <v>503</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>25</v>
@@ -9490,13 +9487,13 @@
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
+        <v>503</v>
+      </c>
+      <c r="B238" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="C238" s="14" t="s">
         <v>504</v>
-      </c>
-      <c r="B238" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="C238" s="14" t="s">
-        <v>505</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>25</v>
@@ -9516,13 +9513,13 @@
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="B239" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="C239" s="19" t="s">
         <v>506</v>
-      </c>
-      <c r="B239" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="C239" s="19" t="s">
-        <v>507</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>25</v>
@@ -9542,13 +9539,13 @@
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="B240" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="C240" s="14" t="s">
         <v>508</v>
-      </c>
-      <c r="B240" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="C240" s="14" t="s">
-        <v>509</v>
       </c>
       <c r="D240" s="15" t="s">
         <v>25</v>
@@ -9568,13 +9565,13 @@
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="B241" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="C241" s="19" t="s">
         <v>510</v>
-      </c>
-      <c r="B241" s="18" t="s">
-        <v>492</v>
-      </c>
-      <c r="C241" s="19" t="s">
-        <v>511</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>25</v>
@@ -9594,13 +9591,13 @@
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
+        <v>511</v>
+      </c>
+      <c r="B242" s="13" t="s">
         <v>512</v>
       </c>
-      <c r="B242" s="13" t="s">
+      <c r="C242" s="14" t="s">
         <v>513</v>
-      </c>
-      <c r="C242" s="14" t="s">
-        <v>514</v>
       </c>
       <c r="D242" s="15" t="s">
         <v>25</v>
@@ -9620,13 +9617,13 @@
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="B243" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="C243" s="19" t="s">
         <v>515</v>
-      </c>
-      <c r="B243" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="C243" s="19" t="s">
-        <v>516</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>25</v>
@@ -9646,13 +9643,13 @@
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="B244" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="C244" s="14" t="s">
         <v>517</v>
-      </c>
-      <c r="B244" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="C244" s="14" t="s">
-        <v>518</v>
       </c>
       <c r="D244" s="15" t="s">
         <v>25</v>
@@ -9672,13 +9669,13 @@
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="B245" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="C245" s="19" t="s">
         <v>519</v>
-      </c>
-      <c r="B245" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="C245" s="19" t="s">
-        <v>520</v>
       </c>
       <c r="D245" s="20" t="s">
         <v>25</v>
@@ -9698,13 +9695,13 @@
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
+        <v>520</v>
+      </c>
+      <c r="B246" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="C246" s="14" t="s">
         <v>521</v>
-      </c>
-      <c r="B246" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="C246" s="14" t="s">
-        <v>522</v>
       </c>
       <c r="D246" s="15" t="s">
         <v>25</v>
@@ -9724,13 +9721,13 @@
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="17" t="s">
+        <v>522</v>
+      </c>
+      <c r="B247" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="C247" s="19" t="s">
         <v>523</v>
-      </c>
-      <c r="B247" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="C247" s="19" t="s">
-        <v>524</v>
       </c>
       <c r="D247" s="20" t="s">
         <v>25</v>
@@ -9750,13 +9747,13 @@
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
+        <v>524</v>
+      </c>
+      <c r="B248" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="C248" s="14" t="s">
         <v>525</v>
-      </c>
-      <c r="B248" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="C248" s="14" t="s">
-        <v>526</v>
       </c>
       <c r="D248" s="15" t="s">
         <v>25</v>
@@ -9776,13 +9773,13 @@
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="B249" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="C249" s="19" t="s">
         <v>527</v>
-      </c>
-      <c r="B249" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="C249" s="19" t="s">
-        <v>528</v>
       </c>
       <c r="D249" s="20" t="s">
         <v>25</v>
@@ -9802,13 +9799,13 @@
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
+        <v>528</v>
+      </c>
+      <c r="B250" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="C250" s="14" t="s">
         <v>529</v>
-      </c>
-      <c r="B250" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="C250" s="14" t="s">
-        <v>530</v>
       </c>
       <c r="D250" s="15" t="s">
         <v>25</v>
@@ -9828,13 +9825,13 @@
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="B251" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="C251" s="19" t="s">
         <v>531</v>
-      </c>
-      <c r="B251" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="C251" s="19" t="s">
-        <v>532</v>
       </c>
       <c r="D251" s="20" t="s">
         <v>25</v>
@@ -9854,13 +9851,13 @@
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="B252" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="B252" s="13" t="s">
+      <c r="C252" s="14" t="s">
         <v>534</v>
-      </c>
-      <c r="C252" s="14" t="s">
-        <v>535</v>
       </c>
       <c r="D252" s="15" t="s">
         <v>25</v>
@@ -9880,13 +9877,13 @@
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="B253" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="C253" s="19" t="s">
         <v>536</v>
-      </c>
-      <c r="B253" s="18" t="s">
-        <v>534</v>
-      </c>
-      <c r="C253" s="19" t="s">
-        <v>537</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>25</v>
@@ -9906,13 +9903,13 @@
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="B254" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="C254" s="14" t="s">
         <v>538</v>
-      </c>
-      <c r="B254" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="C254" s="14" t="s">
-        <v>539</v>
       </c>
       <c r="D254" s="15" t="s">
         <v>25</v>
@@ -9932,13 +9929,13 @@
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="B255" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="C255" s="19" t="s">
         <v>540</v>
-      </c>
-      <c r="B255" s="18" t="s">
-        <v>534</v>
-      </c>
-      <c r="C255" s="19" t="s">
-        <v>541</v>
       </c>
       <c r="D255" s="20" t="s">
         <v>25</v>
@@ -9958,13 +9955,13 @@
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="B256" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="C256" s="14" t="s">
         <v>542</v>
-      </c>
-      <c r="B256" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="C256" s="14" t="s">
-        <v>543</v>
       </c>
       <c r="D256" s="15" t="s">
         <v>25</v>
@@ -9984,13 +9981,13 @@
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="B257" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="C257" s="19" t="s">
         <v>544</v>
-      </c>
-      <c r="B257" s="18" t="s">
-        <v>534</v>
-      </c>
-      <c r="C257" s="19" t="s">
-        <v>545</v>
       </c>
       <c r="D257" s="20" t="s">
         <v>25</v>
@@ -10010,13 +10007,13 @@
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="B258" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="C258" s="14" t="s">
         <v>546</v>
-      </c>
-      <c r="B258" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="C258" s="14" t="s">
-        <v>547</v>
       </c>
       <c r="D258" s="15" t="s">
         <v>25</v>
@@ -10036,13 +10033,13 @@
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="17" t="s">
+        <v>547</v>
+      </c>
+      <c r="B259" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="C259" s="19" t="s">
         <v>548</v>
-      </c>
-      <c r="B259" s="18" t="s">
-        <v>534</v>
-      </c>
-      <c r="C259" s="19" t="s">
-        <v>549</v>
       </c>
       <c r="D259" s="20" t="s">
         <v>25</v>
@@ -10062,13 +10059,13 @@
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="B260" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="C260" s="14" t="s">
         <v>550</v>
-      </c>
-      <c r="B260" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="C260" s="14" t="s">
-        <v>551</v>
       </c>
       <c r="D260" s="15" t="s">
         <v>25</v>
@@ -10088,13 +10085,13 @@
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="B261" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="C261" s="19" t="s">
         <v>552</v>
-      </c>
-      <c r="B261" s="18" t="s">
-        <v>534</v>
-      </c>
-      <c r="C261" s="19" t="s">
-        <v>553</v>
       </c>
       <c r="D261" s="20" t="s">
         <v>25</v>
@@ -10114,13 +10111,13 @@
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="B262" s="13" t="s">
         <v>554</v>
       </c>
-      <c r="B262" s="13" t="s">
+      <c r="C262" s="14" t="s">
         <v>555</v>
-      </c>
-      <c r="C262" s="14" t="s">
-        <v>556</v>
       </c>
       <c r="D262" s="15" t="s">
         <v>25</v>
@@ -10140,13 +10137,13 @@
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="B263" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="C263" s="19" t="s">
         <v>557</v>
-      </c>
-      <c r="B263" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="C263" s="19" t="s">
-        <v>558</v>
       </c>
       <c r="D263" s="20" t="s">
         <v>25</v>
@@ -10166,13 +10163,13 @@
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="B264" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="C264" s="14" t="s">
         <v>559</v>
-      </c>
-      <c r="B264" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="C264" s="14" t="s">
-        <v>560</v>
       </c>
       <c r="D264" s="15" t="s">
         <v>25</v>
@@ -10192,13 +10189,13 @@
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="B265" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="C265" s="19" t="s">
         <v>561</v>
-      </c>
-      <c r="B265" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="C265" s="19" t="s">
-        <v>562</v>
       </c>
       <c r="D265" s="20" t="s">
         <v>25</v>
@@ -10218,13 +10215,13 @@
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="B266" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="C266" s="14" t="s">
         <v>563</v>
-      </c>
-      <c r="B266" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="C266" s="14" t="s">
-        <v>564</v>
       </c>
       <c r="D266" s="15" t="s">
         <v>25</v>
@@ -10244,13 +10241,13 @@
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="B267" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="C267" s="19" t="s">
         <v>565</v>
-      </c>
-      <c r="B267" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="C267" s="19" t="s">
-        <v>566</v>
       </c>
       <c r="D267" s="20" t="s">
         <v>25</v>
@@ -10270,13 +10267,13 @@
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="B268" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="C268" s="14" t="s">
         <v>567</v>
-      </c>
-      <c r="B268" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="C268" s="14" t="s">
-        <v>568</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>25</v>
@@ -10296,13 +10293,13 @@
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="B269" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="C269" s="19" t="s">
         <v>569</v>
-      </c>
-      <c r="B269" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="C269" s="19" t="s">
-        <v>570</v>
       </c>
       <c r="D269" s="20" t="s">
         <v>25</v>
@@ -10322,13 +10319,13 @@
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12" t="s">
+        <v>570</v>
+      </c>
+      <c r="B270" s="13" t="s">
+        <v>554</v>
+      </c>
+      <c r="C270" s="14" t="s">
         <v>571</v>
-      </c>
-      <c r="B270" s="13" t="s">
-        <v>555</v>
-      </c>
-      <c r="C270" s="14" t="s">
-        <v>572</v>
       </c>
       <c r="D270" s="15" t="s">
         <v>25</v>
@@ -10348,13 +10345,13 @@
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="B271" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="C271" s="19" t="s">
         <v>573</v>
-      </c>
-      <c r="B271" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="C271" s="19" t="s">
-        <v>574</v>
       </c>
       <c r="D271" s="20" t="s">
         <v>25</v>
@@ -10374,13 +10371,13 @@
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
+        <v>574</v>
+      </c>
+      <c r="B272" s="13" t="s">
         <v>575</v>
       </c>
-      <c r="B272" s="13" t="s">
+      <c r="C272" s="14" t="s">
         <v>576</v>
-      </c>
-      <c r="C272" s="14" t="s">
-        <v>577</v>
       </c>
       <c r="D272" s="15" t="s">
         <v>25</v>
@@ -10400,13 +10397,13 @@
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
+        <v>577</v>
+      </c>
+      <c r="B273" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="C273" s="19" t="s">
         <v>578</v>
-      </c>
-      <c r="B273" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="C273" s="19" t="s">
-        <v>579</v>
       </c>
       <c r="D273" s="20" t="s">
         <v>25</v>
@@ -10426,13 +10423,13 @@
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
+        <v>579</v>
+      </c>
+      <c r="B274" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="C274" s="14" t="s">
         <v>580</v>
-      </c>
-      <c r="B274" s="13" t="s">
-        <v>576</v>
-      </c>
-      <c r="C274" s="14" t="s">
-        <v>581</v>
       </c>
       <c r="D274" s="15" t="s">
         <v>25</v>
@@ -10452,13 +10449,13 @@
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="B275" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="C275" s="19" t="s">
         <v>582</v>
-      </c>
-      <c r="B275" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="C275" s="19" t="s">
-        <v>583</v>
       </c>
       <c r="D275" s="20" t="s">
         <v>25</v>
@@ -10478,13 +10475,13 @@
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="B276" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="C276" s="14" t="s">
         <v>584</v>
-      </c>
-      <c r="B276" s="13" t="s">
-        <v>576</v>
-      </c>
-      <c r="C276" s="14" t="s">
-        <v>585</v>
       </c>
       <c r="D276" s="15" t="s">
         <v>25</v>
@@ -10504,13 +10501,13 @@
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="17" t="s">
+        <v>585</v>
+      </c>
+      <c r="B277" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="C277" s="19" t="s">
         <v>586</v>
-      </c>
-      <c r="B277" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="C277" s="19" t="s">
-        <v>587</v>
       </c>
       <c r="D277" s="20" t="s">
         <v>25</v>
@@ -10530,13 +10527,13 @@
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="B278" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="C278" s="14" t="s">
         <v>588</v>
-      </c>
-      <c r="B278" s="13" t="s">
-        <v>576</v>
-      </c>
-      <c r="C278" s="14" t="s">
-        <v>589</v>
       </c>
       <c r="D278" s="15" t="s">
         <v>25</v>
@@ -10556,13 +10553,13 @@
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="B279" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="C279" s="19" t="s">
         <v>590</v>
-      </c>
-      <c r="B279" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="C279" s="19" t="s">
-        <v>591</v>
       </c>
       <c r="D279" s="20" t="s">
         <v>25</v>
@@ -10582,13 +10579,13 @@
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="B280" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="C280" s="14" t="s">
         <v>592</v>
-      </c>
-      <c r="B280" s="13" t="s">
-        <v>576</v>
-      </c>
-      <c r="C280" s="14" t="s">
-        <v>593</v>
       </c>
       <c r="D280" s="15" t="s">
         <v>25</v>
@@ -10608,13 +10605,13 @@
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="B281" s="18" t="s">
+        <v>575</v>
+      </c>
+      <c r="C281" s="19" t="s">
         <v>594</v>
-      </c>
-      <c r="B281" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="C281" s="19" t="s">
-        <v>595</v>
       </c>
       <c r="D281" s="20" t="s">
         <v>25</v>
@@ -10634,13 +10631,13 @@
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="B282" s="13" t="s">
         <v>596</v>
       </c>
-      <c r="B282" s="13" t="s">
+      <c r="C282" s="14" t="s">
         <v>597</v>
-      </c>
-      <c r="C282" s="14" t="s">
-        <v>598</v>
       </c>
       <c r="D282" s="15" t="s">
         <v>25</v>
@@ -10660,13 +10657,13 @@
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
+        <v>598</v>
+      </c>
+      <c r="B283" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="C283" s="19" t="s">
         <v>599</v>
-      </c>
-      <c r="B283" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="C283" s="19" t="s">
-        <v>600</v>
       </c>
       <c r="D283" s="20" t="s">
         <v>25</v>
@@ -10686,13 +10683,13 @@
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="B284" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="C284" s="14" t="s">
         <v>601</v>
-      </c>
-      <c r="B284" s="13" t="s">
-        <v>597</v>
-      </c>
-      <c r="C284" s="14" t="s">
-        <v>602</v>
       </c>
       <c r="D284" s="15" t="s">
         <v>25</v>
@@ -10712,13 +10709,13 @@
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="B285" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="C285" s="19" t="s">
         <v>603</v>
-      </c>
-      <c r="B285" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="C285" s="19" t="s">
-        <v>604</v>
       </c>
       <c r="D285" s="20" t="s">
         <v>25</v>
@@ -10738,13 +10735,13 @@
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="B286" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="C286" s="14" t="s">
         <v>605</v>
-      </c>
-      <c r="B286" s="13" t="s">
-        <v>597</v>
-      </c>
-      <c r="C286" s="14" t="s">
-        <v>606</v>
       </c>
       <c r="D286" s="15" t="s">
         <v>25</v>
@@ -10764,13 +10761,13 @@
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="17" t="s">
+        <v>606</v>
+      </c>
+      <c r="B287" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="C287" s="19" t="s">
         <v>607</v>
-      </c>
-      <c r="B287" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="C287" s="19" t="s">
-        <v>608</v>
       </c>
       <c r="D287" s="20" t="s">
         <v>25</v>
@@ -10790,13 +10787,13 @@
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="B288" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="C288" s="14" t="s">
         <v>609</v>
-      </c>
-      <c r="B288" s="13" t="s">
-        <v>597</v>
-      </c>
-      <c r="C288" s="14" t="s">
-        <v>610</v>
       </c>
       <c r="D288" s="15" t="s">
         <v>25</v>
@@ -10816,13 +10813,13 @@
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="17" t="s">
+        <v>610</v>
+      </c>
+      <c r="B289" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="C289" s="19" t="s">
         <v>611</v>
-      </c>
-      <c r="B289" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="C289" s="19" t="s">
-        <v>612</v>
       </c>
       <c r="D289" s="20" t="s">
         <v>25</v>
@@ -10842,13 +10839,13 @@
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="B290" s="13" t="s">
+        <v>596</v>
+      </c>
+      <c r="C290" s="14" t="s">
         <v>613</v>
-      </c>
-      <c r="B290" s="13" t="s">
-        <v>597</v>
-      </c>
-      <c r="C290" s="14" t="s">
-        <v>614</v>
       </c>
       <c r="D290" s="15" t="s">
         <v>25</v>
@@ -10868,13 +10865,13 @@
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="17" t="s">
+        <v>614</v>
+      </c>
+      <c r="B291" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="C291" s="19" t="s">
         <v>615</v>
-      </c>
-      <c r="B291" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="C291" s="19" t="s">
-        <v>616</v>
       </c>
       <c r="D291" s="20" t="s">
         <v>25</v>
@@ -10894,13 +10891,13 @@
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="B292" s="13" t="s">
         <v>617</v>
       </c>
-      <c r="B292" s="13" t="s">
+      <c r="C292" s="14" t="s">
         <v>618</v>
-      </c>
-      <c r="C292" s="14" t="s">
-        <v>619</v>
       </c>
       <c r="D292" s="15" t="s">
         <v>25</v>
@@ -10920,13 +10917,13 @@
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="17" t="s">
+        <v>619</v>
+      </c>
+      <c r="B293" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="C293" s="19" t="s">
         <v>620</v>
-      </c>
-      <c r="B293" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="C293" s="19" t="s">
-        <v>621</v>
       </c>
       <c r="D293" s="20" t="s">
         <v>25</v>
@@ -10946,13 +10943,13 @@
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="B294" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="C294" s="14" t="s">
         <v>622</v>
-      </c>
-      <c r="B294" s="13" t="s">
-        <v>618</v>
-      </c>
-      <c r="C294" s="14" t="s">
-        <v>623</v>
       </c>
       <c r="D294" s="15" t="s">
         <v>25</v>
@@ -10972,13 +10969,13 @@
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="B295" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="C295" s="19" t="s">
         <v>624</v>
-      </c>
-      <c r="B295" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="C295" s="19" t="s">
-        <v>625</v>
       </c>
       <c r="D295" s="20" t="s">
         <v>25</v>
@@ -10998,13 +10995,13 @@
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="B296" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="C296" s="14" t="s">
         <v>626</v>
-      </c>
-      <c r="B296" s="13" t="s">
-        <v>618</v>
-      </c>
-      <c r="C296" s="14" t="s">
-        <v>627</v>
       </c>
       <c r="D296" s="15" t="s">
         <v>25</v>
@@ -11024,13 +11021,13 @@
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="B297" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="C297" s="19" t="s">
         <v>628</v>
-      </c>
-      <c r="B297" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="C297" s="19" t="s">
-        <v>629</v>
       </c>
       <c r="D297" s="20" t="s">
         <v>25</v>
@@ -11050,13 +11047,13 @@
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="C298" s="14" t="s">
         <v>630</v>
-      </c>
-      <c r="B298" s="13" t="s">
-        <v>618</v>
-      </c>
-      <c r="C298" s="14" t="s">
-        <v>631</v>
       </c>
       <c r="D298" s="15" t="s">
         <v>25</v>
@@ -11076,13 +11073,13 @@
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
+        <v>631</v>
+      </c>
+      <c r="B299" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="C299" s="19" t="s">
         <v>632</v>
-      </c>
-      <c r="B299" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="C299" s="19" t="s">
-        <v>633</v>
       </c>
       <c r="D299" s="20" t="s">
         <v>25</v>
@@ -11102,13 +11099,13 @@
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="B300" s="13" t="s">
+        <v>617</v>
+      </c>
+      <c r="C300" s="14" t="s">
         <v>634</v>
-      </c>
-      <c r="B300" s="13" t="s">
-        <v>618</v>
-      </c>
-      <c r="C300" s="14" t="s">
-        <v>635</v>
       </c>
       <c r="D300" s="15" t="s">
         <v>25</v>
@@ -11128,13 +11125,13 @@
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="17" t="s">
+        <v>635</v>
+      </c>
+      <c r="B301" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="C301" s="19" t="s">
         <v>636</v>
-      </c>
-      <c r="B301" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="C301" s="19" t="s">
-        <v>637</v>
       </c>
       <c r="D301" s="20" t="s">
         <v>25</v>
@@ -11175,33 +11172,33 @@
         <v>16</v>
       </c>
       <c r="B1" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>638</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>639</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
+        <v>640</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>641</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="C2" s="22" t="s">
         <v>642</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="D2" s="22" t="s">
         <v>643</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="E2" s="22" t="s">
         <v>644</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -11224,19 +11221,19 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="23" t="s">
+        <v>646</v>
+      </c>
+      <c r="D1" s="23" t="s">
         <v>647</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="E1" s="23" t="s">
         <v>648</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11244,16 +11241,16 @@
         <v>27</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>649</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>650</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="D2" s="25" t="s">
         <v>651</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="E2" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11261,16 +11258,16 @@
         <v>27</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>653</v>
+      </c>
+      <c r="C3" s="26" t="s">
         <v>654</v>
       </c>
-      <c r="C3" s="26" t="s">
-        <v>655</v>
-      </c>
       <c r="D3" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E3" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11278,16 +11275,16 @@
         <v>27</v>
       </c>
       <c r="B4" s="24" t="s">
+        <v>655</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>656</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>657</v>
-      </c>
       <c r="D4" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E4" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11295,16 +11292,16 @@
         <v>27</v>
       </c>
       <c r="B5" s="26" t="s">
+        <v>657</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>658</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>659</v>
-      </c>
       <c r="D5" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11312,16 +11309,16 @@
         <v>27</v>
       </c>
       <c r="B6" s="24" t="s">
+        <v>659</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>660</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>661</v>
-      </c>
       <c r="D6" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11329,16 +11326,16 @@
         <v>27</v>
       </c>
       <c r="B7" s="26" t="s">
+        <v>661</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>662</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>663</v>
-      </c>
       <c r="D7" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E7" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11346,16 +11343,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="24" t="s">
+        <v>663</v>
+      </c>
+      <c r="C8" s="24" t="s">
         <v>664</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>665</v>
-      </c>
       <c r="D8" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11363,16 +11360,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="26" t="s">
+        <v>665</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>666</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>667</v>
-      </c>
       <c r="D9" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E9" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11380,16 +11377,16 @@
         <v>27</v>
       </c>
       <c r="B10" s="24" t="s">
+        <v>667</v>
+      </c>
+      <c r="C10" s="24" t="s">
         <v>668</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>669</v>
-      </c>
       <c r="D10" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E10" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11397,16 +11394,16 @@
         <v>27</v>
       </c>
       <c r="B11" s="26" t="s">
+        <v>669</v>
+      </c>
+      <c r="C11" s="26" t="s">
         <v>670</v>
       </c>
-      <c r="C11" s="26" t="s">
-        <v>671</v>
-      </c>
       <c r="D11" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11414,16 +11411,16 @@
         <v>27</v>
       </c>
       <c r="B12" s="24" t="s">
+        <v>671</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>672</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>673</v>
-      </c>
       <c r="D12" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E12" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11431,16 +11428,16 @@
         <v>27</v>
       </c>
       <c r="B13" s="26" t="s">
+        <v>673</v>
+      </c>
+      <c r="C13" s="26" t="s">
         <v>674</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>675</v>
-      </c>
       <c r="D13" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11448,16 +11445,16 @@
         <v>27</v>
       </c>
       <c r="B14" s="24" t="s">
+        <v>675</v>
+      </c>
+      <c r="C14" s="24" t="s">
         <v>676</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>677</v>
-      </c>
       <c r="D14" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11465,16 +11462,16 @@
         <v>27</v>
       </c>
       <c r="B15" s="26" t="s">
+        <v>677</v>
+      </c>
+      <c r="C15" s="26" t="s">
         <v>678</v>
       </c>
-      <c r="C15" s="26" t="s">
-        <v>679</v>
-      </c>
       <c r="D15" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11482,16 +11479,16 @@
         <v>27</v>
       </c>
       <c r="B16" s="24" t="s">
+        <v>679</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>680</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>681</v>
-      </c>
       <c r="D16" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E16" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11499,16 +11496,16 @@
         <v>27</v>
       </c>
       <c r="B17" s="26" t="s">
+        <v>681</v>
+      </c>
+      <c r="C17" s="26" t="s">
         <v>682</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>683</v>
-      </c>
       <c r="D17" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E17" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11516,16 +11513,16 @@
         <v>27</v>
       </c>
       <c r="B18" s="24" t="s">
+        <v>683</v>
+      </c>
+      <c r="C18" s="24" t="s">
         <v>684</v>
       </c>
-      <c r="C18" s="24" t="s">
-        <v>685</v>
-      </c>
       <c r="D18" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E18" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11533,16 +11530,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="26" t="s">
+        <v>685</v>
+      </c>
+      <c r="C19" s="26" t="s">
         <v>686</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>687</v>
-      </c>
       <c r="D19" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E19" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11550,16 +11547,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="24" t="s">
+        <v>687</v>
+      </c>
+      <c r="C20" s="24" t="s">
         <v>688</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>689</v>
-      </c>
       <c r="D20" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E20" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11567,16 +11564,16 @@
         <v>27</v>
       </c>
       <c r="B21" s="26" t="s">
+        <v>689</v>
+      </c>
+      <c r="C21" s="26" t="s">
         <v>690</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>691</v>
-      </c>
       <c r="D21" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E21" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11584,16 +11581,16 @@
         <v>27</v>
       </c>
       <c r="B22" s="24" t="s">
+        <v>691</v>
+      </c>
+      <c r="C22" s="24" t="s">
         <v>692</v>
       </c>
-      <c r="C22" s="24" t="s">
-        <v>693</v>
-      </c>
       <c r="D22" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E22" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11601,16 +11598,16 @@
         <v>27</v>
       </c>
       <c r="B23" s="26" t="s">
+        <v>693</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>694</v>
       </c>
-      <c r="C23" s="26" t="s">
-        <v>695</v>
-      </c>
       <c r="D23" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E23" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11618,16 +11615,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="24" t="s">
+        <v>695</v>
+      </c>
+      <c r="C24" s="24" t="s">
         <v>696</v>
       </c>
-      <c r="C24" s="24" t="s">
-        <v>697</v>
-      </c>
       <c r="D24" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E24" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11635,16 +11632,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="26" t="s">
+        <v>697</v>
+      </c>
+      <c r="C25" s="26" t="s">
         <v>698</v>
       </c>
-      <c r="C25" s="26" t="s">
-        <v>699</v>
-      </c>
       <c r="D25" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E25" s="26" t="s">
         <v>652</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11652,16 +11649,16 @@
         <v>27</v>
       </c>
       <c r="B26" s="24" t="s">
+        <v>699</v>
+      </c>
+      <c r="C26" s="24" t="s">
         <v>700</v>
       </c>
-      <c r="C26" s="24" t="s">
-        <v>701</v>
-      </c>
       <c r="D26" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E26" s="24" t="s">
         <v>652</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11669,16 +11666,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="26" t="s">
+        <v>701</v>
+      </c>
+      <c r="C27" s="26" t="s">
         <v>702</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="D27" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E27" s="26" t="s">
         <v>703</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>652</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11686,16 +11683,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="24" t="s">
+        <v>704</v>
+      </c>
+      <c r="C28" s="24" t="s">
         <v>705</v>
       </c>
-      <c r="C28" s="24" t="s">
-        <v>706</v>
-      </c>
       <c r="D28" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11703,16 +11700,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="26" t="s">
+        <v>706</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>707</v>
       </c>
-      <c r="C29" s="26" t="s">
-        <v>708</v>
-      </c>
       <c r="D29" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11720,16 +11717,16 @@
         <v>27</v>
       </c>
       <c r="B30" s="24" t="s">
+        <v>708</v>
+      </c>
+      <c r="C30" s="24" t="s">
         <v>709</v>
       </c>
-      <c r="C30" s="24" t="s">
-        <v>710</v>
-      </c>
       <c r="D30" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11737,16 +11734,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="26" t="s">
+        <v>710</v>
+      </c>
+      <c r="C31" s="26" t="s">
         <v>711</v>
       </c>
-      <c r="C31" s="26" t="s">
-        <v>712</v>
-      </c>
       <c r="D31" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11754,16 +11751,16 @@
         <v>27</v>
       </c>
       <c r="B32" s="24" t="s">
+        <v>712</v>
+      </c>
+      <c r="C32" s="24" t="s">
         <v>713</v>
       </c>
-      <c r="C32" s="24" t="s">
-        <v>714</v>
-      </c>
       <c r="D32" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11771,16 +11768,16 @@
         <v>27</v>
       </c>
       <c r="B33" s="26" t="s">
+        <v>714</v>
+      </c>
+      <c r="C33" s="26" t="s">
         <v>715</v>
       </c>
-      <c r="C33" s="26" t="s">
-        <v>716</v>
-      </c>
       <c r="D33" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11788,16 +11785,16 @@
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
+        <v>716</v>
+      </c>
+      <c r="C34" s="24" t="s">
         <v>717</v>
       </c>
-      <c r="C34" s="24" t="s">
-        <v>718</v>
-      </c>
       <c r="D34" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11805,16 +11802,16 @@
         <v>27</v>
       </c>
       <c r="B35" s="26" t="s">
+        <v>718</v>
+      </c>
+      <c r="C35" s="26" t="s">
         <v>719</v>
       </c>
-      <c r="C35" s="26" t="s">
-        <v>720</v>
-      </c>
       <c r="D35" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11822,16 +11819,16 @@
         <v>27</v>
       </c>
       <c r="B36" s="24" t="s">
+        <v>720</v>
+      </c>
+      <c r="C36" s="24" t="s">
         <v>721</v>
       </c>
-      <c r="C36" s="24" t="s">
-        <v>722</v>
-      </c>
       <c r="D36" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11839,16 +11836,16 @@
         <v>27</v>
       </c>
       <c r="B37" s="26" t="s">
+        <v>722</v>
+      </c>
+      <c r="C37" s="26" t="s">
         <v>723</v>
       </c>
-      <c r="C37" s="26" t="s">
-        <v>724</v>
-      </c>
       <c r="D37" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11856,16 +11853,16 @@
         <v>27</v>
       </c>
       <c r="B38" s="24" t="s">
+        <v>724</v>
+      </c>
+      <c r="C38" s="24" t="s">
         <v>725</v>
       </c>
-      <c r="C38" s="24" t="s">
-        <v>726</v>
-      </c>
       <c r="D38" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11873,16 +11870,16 @@
         <v>27</v>
       </c>
       <c r="B39" s="26" t="s">
+        <v>726</v>
+      </c>
+      <c r="C39" s="26" t="s">
         <v>727</v>
       </c>
-      <c r="C39" s="26" t="s">
-        <v>728</v>
-      </c>
       <c r="D39" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11890,16 +11887,16 @@
         <v>27</v>
       </c>
       <c r="B40" s="24" t="s">
+        <v>728</v>
+      </c>
+      <c r="C40" s="24" t="s">
         <v>729</v>
       </c>
-      <c r="C40" s="24" t="s">
-        <v>730</v>
-      </c>
       <c r="D40" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11907,16 +11904,16 @@
         <v>27</v>
       </c>
       <c r="B41" s="26" t="s">
+        <v>730</v>
+      </c>
+      <c r="C41" s="26" t="s">
         <v>731</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>732</v>
-      </c>
       <c r="D41" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11924,16 +11921,16 @@
         <v>27</v>
       </c>
       <c r="B42" s="24" t="s">
+        <v>732</v>
+      </c>
+      <c r="C42" s="24" t="s">
         <v>733</v>
       </c>
-      <c r="C42" s="24" t="s">
-        <v>734</v>
-      </c>
       <c r="D42" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11941,16 +11938,16 @@
         <v>27</v>
       </c>
       <c r="B43" s="26" t="s">
+        <v>734</v>
+      </c>
+      <c r="C43" s="26" t="s">
         <v>735</v>
       </c>
-      <c r="C43" s="26" t="s">
-        <v>736</v>
-      </c>
       <c r="D43" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11958,16 +11955,16 @@
         <v>27</v>
       </c>
       <c r="B44" s="24" t="s">
+        <v>736</v>
+      </c>
+      <c r="C44" s="24" t="s">
         <v>737</v>
       </c>
-      <c r="C44" s="24" t="s">
-        <v>738</v>
-      </c>
       <c r="D44" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11975,16 +11972,16 @@
         <v>27</v>
       </c>
       <c r="B45" s="26" t="s">
+        <v>738</v>
+      </c>
+      <c r="C45" s="26" t="s">
         <v>739</v>
       </c>
-      <c r="C45" s="26" t="s">
-        <v>740</v>
-      </c>
       <c r="D45" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11992,16 +11989,16 @@
         <v>27</v>
       </c>
       <c r="B46" s="24" t="s">
+        <v>740</v>
+      </c>
+      <c r="C46" s="24" t="s">
         <v>741</v>
       </c>
-      <c r="C46" s="24" t="s">
-        <v>742</v>
-      </c>
       <c r="D46" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12009,16 +12006,16 @@
         <v>27</v>
       </c>
       <c r="B47" s="26" t="s">
+        <v>742</v>
+      </c>
+      <c r="C47" s="26" t="s">
         <v>743</v>
       </c>
-      <c r="C47" s="26" t="s">
-        <v>744</v>
-      </c>
       <c r="D47" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12026,16 +12023,16 @@
         <v>27</v>
       </c>
       <c r="B48" s="24" t="s">
+        <v>744</v>
+      </c>
+      <c r="C48" s="24" t="s">
         <v>745</v>
       </c>
-      <c r="C48" s="24" t="s">
-        <v>746</v>
-      </c>
       <c r="D48" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12043,16 +12040,16 @@
         <v>27</v>
       </c>
       <c r="B49" s="26" t="s">
+        <v>746</v>
+      </c>
+      <c r="C49" s="26" t="s">
         <v>747</v>
       </c>
-      <c r="C49" s="26" t="s">
-        <v>748</v>
-      </c>
       <c r="D49" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12060,16 +12057,16 @@
         <v>27</v>
       </c>
       <c r="B50" s="24" t="s">
+        <v>748</v>
+      </c>
+      <c r="C50" s="24" t="s">
         <v>749</v>
       </c>
-      <c r="C50" s="24" t="s">
-        <v>750</v>
-      </c>
       <c r="D50" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12077,16 +12074,16 @@
         <v>27</v>
       </c>
       <c r="B51" s="26" t="s">
+        <v>750</v>
+      </c>
+      <c r="C51" s="26" t="s">
         <v>751</v>
       </c>
-      <c r="C51" s="26" t="s">
-        <v>752</v>
-      </c>
       <c r="D51" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12094,16 +12091,16 @@
         <v>27</v>
       </c>
       <c r="B52" s="24" t="s">
+        <v>752</v>
+      </c>
+      <c r="C52" s="24" t="s">
         <v>753</v>
       </c>
-      <c r="C52" s="24" t="s">
+      <c r="D52" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E52" s="24" t="s">
         <v>754</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>652</v>
-      </c>
-      <c r="E52" s="24" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12111,16 +12108,16 @@
         <v>27</v>
       </c>
       <c r="B53" s="26" t="s">
+        <v>755</v>
+      </c>
+      <c r="C53" s="26" t="s">
         <v>756</v>
       </c>
-      <c r="C53" s="26" t="s">
-        <v>757</v>
-      </c>
       <c r="D53" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12128,16 +12125,16 @@
         <v>27</v>
       </c>
       <c r="B54" s="24" t="s">
+        <v>757</v>
+      </c>
+      <c r="C54" s="24" t="s">
         <v>758</v>
       </c>
-      <c r="C54" s="24" t="s">
-        <v>759</v>
-      </c>
       <c r="D54" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12145,16 +12142,16 @@
         <v>27</v>
       </c>
       <c r="B55" s="26" t="s">
+        <v>759</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>760</v>
       </c>
-      <c r="C55" s="26" t="s">
-        <v>761</v>
-      </c>
       <c r="D55" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12162,16 +12159,16 @@
         <v>27</v>
       </c>
       <c r="B56" s="24" t="s">
+        <v>761</v>
+      </c>
+      <c r="C56" s="24" t="s">
         <v>762</v>
       </c>
-      <c r="C56" s="24" t="s">
-        <v>763</v>
-      </c>
       <c r="D56" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12179,16 +12176,16 @@
         <v>27</v>
       </c>
       <c r="B57" s="26" t="s">
+        <v>763</v>
+      </c>
+      <c r="C57" s="26" t="s">
         <v>764</v>
       </c>
-      <c r="C57" s="26" t="s">
-        <v>765</v>
-      </c>
       <c r="D57" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12196,16 +12193,16 @@
         <v>27</v>
       </c>
       <c r="B58" s="24" t="s">
+        <v>765</v>
+      </c>
+      <c r="C58" s="24" t="s">
         <v>766</v>
       </c>
-      <c r="C58" s="24" t="s">
-        <v>767</v>
-      </c>
       <c r="D58" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12213,16 +12210,16 @@
         <v>27</v>
       </c>
       <c r="B59" s="26" t="s">
+        <v>767</v>
+      </c>
+      <c r="C59" s="26" t="s">
         <v>768</v>
       </c>
-      <c r="C59" s="26" t="s">
-        <v>769</v>
-      </c>
       <c r="D59" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12230,16 +12227,16 @@
         <v>27</v>
       </c>
       <c r="B60" s="24" t="s">
+        <v>769</v>
+      </c>
+      <c r="C60" s="24" t="s">
         <v>770</v>
       </c>
-      <c r="C60" s="24" t="s">
-        <v>771</v>
-      </c>
       <c r="D60" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12247,16 +12244,16 @@
         <v>27</v>
       </c>
       <c r="B61" s="26" t="s">
+        <v>771</v>
+      </c>
+      <c r="C61" s="26" t="s">
         <v>772</v>
       </c>
-      <c r="C61" s="26" t="s">
-        <v>773</v>
-      </c>
       <c r="D61" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12264,16 +12261,16 @@
         <v>27</v>
       </c>
       <c r="B62" s="24" t="s">
+        <v>773</v>
+      </c>
+      <c r="C62" s="24" t="s">
         <v>774</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="D62" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E62" s="24" t="s">
         <v>775</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>652</v>
-      </c>
-      <c r="E62" s="24" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12281,16 +12278,16 @@
         <v>27</v>
       </c>
       <c r="B63" s="26" t="s">
+        <v>776</v>
+      </c>
+      <c r="C63" s="26" t="s">
         <v>777</v>
       </c>
-      <c r="C63" s="26" t="s">
-        <v>778</v>
-      </c>
       <c r="D63" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12298,16 +12295,16 @@
         <v>27</v>
       </c>
       <c r="B64" s="24" t="s">
+        <v>778</v>
+      </c>
+      <c r="C64" s="24" t="s">
         <v>779</v>
       </c>
-      <c r="C64" s="24" t="s">
-        <v>780</v>
-      </c>
       <c r="D64" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12315,16 +12312,16 @@
         <v>27</v>
       </c>
       <c r="B65" s="26" t="s">
+        <v>780</v>
+      </c>
+      <c r="C65" s="26" t="s">
         <v>781</v>
       </c>
-      <c r="C65" s="26" t="s">
-        <v>782</v>
-      </c>
       <c r="D65" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12332,16 +12329,16 @@
         <v>27</v>
       </c>
       <c r="B66" s="24" t="s">
+        <v>782</v>
+      </c>
+      <c r="C66" s="24" t="s">
         <v>783</v>
       </c>
-      <c r="C66" s="24" t="s">
-        <v>784</v>
-      </c>
       <c r="D66" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12349,16 +12346,16 @@
         <v>27</v>
       </c>
       <c r="B67" s="26" t="s">
+        <v>784</v>
+      </c>
+      <c r="C67" s="26" t="s">
         <v>785</v>
       </c>
-      <c r="C67" s="26" t="s">
-        <v>786</v>
-      </c>
       <c r="D67" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12366,16 +12363,16 @@
         <v>27</v>
       </c>
       <c r="B68" s="24" t="s">
+        <v>786</v>
+      </c>
+      <c r="C68" s="24" t="s">
         <v>787</v>
       </c>
-      <c r="C68" s="24" t="s">
-        <v>788</v>
-      </c>
       <c r="D68" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12383,16 +12380,16 @@
         <v>27</v>
       </c>
       <c r="B69" s="26" t="s">
+        <v>788</v>
+      </c>
+      <c r="C69" s="26" t="s">
         <v>789</v>
       </c>
-      <c r="C69" s="26" t="s">
-        <v>790</v>
-      </c>
       <c r="D69" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12400,16 +12397,16 @@
         <v>27</v>
       </c>
       <c r="B70" s="24" t="s">
+        <v>790</v>
+      </c>
+      <c r="C70" s="24" t="s">
         <v>791</v>
       </c>
-      <c r="C70" s="24" t="s">
-        <v>792</v>
-      </c>
       <c r="D70" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12417,16 +12414,16 @@
         <v>27</v>
       </c>
       <c r="B71" s="26" t="s">
+        <v>792</v>
+      </c>
+      <c r="C71" s="26" t="s">
         <v>793</v>
       </c>
-      <c r="C71" s="26" t="s">
-        <v>794</v>
-      </c>
       <c r="D71" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12434,16 +12431,16 @@
         <v>27</v>
       </c>
       <c r="B72" s="24" t="s">
+        <v>794</v>
+      </c>
+      <c r="C72" s="24" t="s">
         <v>795</v>
       </c>
-      <c r="C72" s="24" t="s">
+      <c r="D72" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E72" s="24" t="s">
         <v>796</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>652</v>
-      </c>
-      <c r="E72" s="24" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12451,16 +12448,16 @@
         <v>27</v>
       </c>
       <c r="B73" s="26" t="s">
+        <v>797</v>
+      </c>
+      <c r="C73" s="26" t="s">
         <v>798</v>
       </c>
-      <c r="C73" s="26" t="s">
-        <v>799</v>
-      </c>
       <c r="D73" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12468,16 +12465,16 @@
         <v>27</v>
       </c>
       <c r="B74" s="24" t="s">
+        <v>799</v>
+      </c>
+      <c r="C74" s="24" t="s">
         <v>800</v>
       </c>
-      <c r="C74" s="24" t="s">
-        <v>801</v>
-      </c>
       <c r="D74" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12485,16 +12482,16 @@
         <v>27</v>
       </c>
       <c r="B75" s="26" t="s">
+        <v>801</v>
+      </c>
+      <c r="C75" s="26" t="s">
         <v>802</v>
       </c>
-      <c r="C75" s="26" t="s">
-        <v>803</v>
-      </c>
       <c r="D75" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12502,16 +12499,16 @@
         <v>27</v>
       </c>
       <c r="B76" s="24" t="s">
+        <v>803</v>
+      </c>
+      <c r="C76" s="24" t="s">
         <v>804</v>
       </c>
-      <c r="C76" s="24" t="s">
-        <v>805</v>
-      </c>
       <c r="D76" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12519,16 +12516,16 @@
         <v>27</v>
       </c>
       <c r="B77" s="26" t="s">
+        <v>805</v>
+      </c>
+      <c r="C77" s="26" t="s">
         <v>806</v>
       </c>
-      <c r="C77" s="26" t="s">
-        <v>807</v>
-      </c>
       <c r="D77" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12536,16 +12533,16 @@
         <v>27</v>
       </c>
       <c r="B78" s="24" t="s">
+        <v>807</v>
+      </c>
+      <c r="C78" s="24" t="s">
         <v>808</v>
       </c>
-      <c r="C78" s="24" t="s">
-        <v>809</v>
-      </c>
       <c r="D78" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12553,16 +12550,16 @@
         <v>27</v>
       </c>
       <c r="B79" s="26" t="s">
+        <v>809</v>
+      </c>
+      <c r="C79" s="26" t="s">
         <v>810</v>
       </c>
-      <c r="C79" s="26" t="s">
-        <v>811</v>
-      </c>
       <c r="D79" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12570,16 +12567,16 @@
         <v>27</v>
       </c>
       <c r="B80" s="24" t="s">
+        <v>811</v>
+      </c>
+      <c r="C80" s="24" t="s">
         <v>812</v>
       </c>
-      <c r="C80" s="24" t="s">
-        <v>813</v>
-      </c>
       <c r="D80" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12587,16 +12584,16 @@
         <v>27</v>
       </c>
       <c r="B81" s="26" t="s">
+        <v>813</v>
+      </c>
+      <c r="C81" s="26" t="s">
         <v>814</v>
       </c>
-      <c r="C81" s="26" t="s">
-        <v>815</v>
-      </c>
       <c r="D81" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12604,16 +12601,16 @@
         <v>27</v>
       </c>
       <c r="B82" s="24" t="s">
+        <v>815</v>
+      </c>
+      <c r="C82" s="24" t="s">
         <v>816</v>
       </c>
-      <c r="C82" s="24" t="s">
+      <c r="D82" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E82" s="24" t="s">
         <v>817</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>652</v>
-      </c>
-      <c r="E82" s="24" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12621,16 +12618,16 @@
         <v>27</v>
       </c>
       <c r="B83" s="26" t="s">
+        <v>818</v>
+      </c>
+      <c r="C83" s="26" t="s">
         <v>819</v>
       </c>
-      <c r="C83" s="26" t="s">
-        <v>820</v>
-      </c>
       <c r="D83" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12638,16 +12635,16 @@
         <v>27</v>
       </c>
       <c r="B84" s="24" t="s">
+        <v>820</v>
+      </c>
+      <c r="C84" s="24" t="s">
         <v>821</v>
       </c>
-      <c r="C84" s="24" t="s">
-        <v>822</v>
-      </c>
       <c r="D84" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E84" s="24" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12655,16 +12652,16 @@
         <v>27</v>
       </c>
       <c r="B85" s="26" t="s">
+        <v>822</v>
+      </c>
+      <c r="C85" s="26" t="s">
         <v>823</v>
       </c>
-      <c r="C85" s="26" t="s">
-        <v>824</v>
-      </c>
       <c r="D85" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12672,16 +12669,16 @@
         <v>27</v>
       </c>
       <c r="B86" s="24" t="s">
+        <v>824</v>
+      </c>
+      <c r="C86" s="24" t="s">
         <v>825</v>
       </c>
-      <c r="C86" s="24" t="s">
-        <v>826</v>
-      </c>
       <c r="D86" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12689,16 +12686,16 @@
         <v>27</v>
       </c>
       <c r="B87" s="26" t="s">
+        <v>826</v>
+      </c>
+      <c r="C87" s="26" t="s">
         <v>827</v>
       </c>
-      <c r="C87" s="26" t="s">
-        <v>828</v>
-      </c>
       <c r="D87" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12706,16 +12703,16 @@
         <v>27</v>
       </c>
       <c r="B88" s="24" t="s">
+        <v>828</v>
+      </c>
+      <c r="C88" s="24" t="s">
         <v>829</v>
       </c>
-      <c r="C88" s="24" t="s">
-        <v>830</v>
-      </c>
       <c r="D88" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12723,16 +12720,16 @@
         <v>27</v>
       </c>
       <c r="B89" s="26" t="s">
+        <v>830</v>
+      </c>
+      <c r="C89" s="26" t="s">
         <v>831</v>
       </c>
-      <c r="C89" s="26" t="s">
-        <v>832</v>
-      </c>
       <c r="D89" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12740,16 +12737,16 @@
         <v>27</v>
       </c>
       <c r="B90" s="24" t="s">
+        <v>832</v>
+      </c>
+      <c r="C90" s="24" t="s">
         <v>833</v>
       </c>
-      <c r="C90" s="24" t="s">
-        <v>834</v>
-      </c>
       <c r="D90" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12757,16 +12754,16 @@
         <v>27</v>
       </c>
       <c r="B91" s="26" t="s">
+        <v>834</v>
+      </c>
+      <c r="C91" s="26" t="s">
         <v>835</v>
       </c>
-      <c r="C91" s="26" t="s">
-        <v>836</v>
-      </c>
       <c r="D91" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12774,16 +12771,16 @@
         <v>27</v>
       </c>
       <c r="B92" s="24" t="s">
+        <v>836</v>
+      </c>
+      <c r="C92" s="24" t="s">
         <v>837</v>
       </c>
-      <c r="C92" s="24" t="s">
+      <c r="D92" s="25" t="s">
+        <v>651</v>
+      </c>
+      <c r="E92" s="24" t="s">
         <v>838</v>
-      </c>
-      <c r="D92" s="25" t="s">
-        <v>652</v>
-      </c>
-      <c r="E92" s="24" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12791,16 +12788,16 @@
         <v>27</v>
       </c>
       <c r="B93" s="26" t="s">
+        <v>839</v>
+      </c>
+      <c r="C93" s="26" t="s">
         <v>840</v>
       </c>
-      <c r="C93" s="26" t="s">
-        <v>841</v>
-      </c>
       <c r="D93" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12808,16 +12805,16 @@
         <v>27</v>
       </c>
       <c r="B94" s="24" t="s">
+        <v>841</v>
+      </c>
+      <c r="C94" s="24" t="s">
         <v>842</v>
       </c>
-      <c r="C94" s="24" t="s">
-        <v>843</v>
-      </c>
       <c r="D94" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E94" s="24" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12825,16 +12822,16 @@
         <v>27</v>
       </c>
       <c r="B95" s="26" t="s">
+        <v>843</v>
+      </c>
+      <c r="C95" s="26" t="s">
         <v>844</v>
       </c>
-      <c r="C95" s="26" t="s">
-        <v>845</v>
-      </c>
       <c r="D95" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12842,16 +12839,16 @@
         <v>27</v>
       </c>
       <c r="B96" s="24" t="s">
+        <v>845</v>
+      </c>
+      <c r="C96" s="24" t="s">
         <v>846</v>
       </c>
-      <c r="C96" s="24" t="s">
-        <v>847</v>
-      </c>
       <c r="D96" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E96" s="24" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12859,16 +12856,16 @@
         <v>27</v>
       </c>
       <c r="B97" s="26" t="s">
+        <v>847</v>
+      </c>
+      <c r="C97" s="26" t="s">
         <v>848</v>
       </c>
-      <c r="C97" s="26" t="s">
-        <v>849</v>
-      </c>
       <c r="D97" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12876,16 +12873,16 @@
         <v>27</v>
       </c>
       <c r="B98" s="24" t="s">
+        <v>849</v>
+      </c>
+      <c r="C98" s="24" t="s">
         <v>850</v>
       </c>
-      <c r="C98" s="24" t="s">
-        <v>851</v>
-      </c>
       <c r="D98" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E98" s="24" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12893,16 +12890,16 @@
         <v>27</v>
       </c>
       <c r="B99" s="26" t="s">
+        <v>851</v>
+      </c>
+      <c r="C99" s="26" t="s">
         <v>852</v>
       </c>
-      <c r="C99" s="26" t="s">
-        <v>853</v>
-      </c>
       <c r="D99" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12910,16 +12907,16 @@
         <v>27</v>
       </c>
       <c r="B100" s="24" t="s">
+        <v>853</v>
+      </c>
+      <c r="C100" s="24" t="s">
         <v>854</v>
       </c>
-      <c r="C100" s="24" t="s">
-        <v>855</v>
-      </c>
       <c r="D100" s="25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E100" s="24" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12927,16 +12924,16 @@
         <v>27</v>
       </c>
       <c r="B101" s="26" t="s">
+        <v>855</v>
+      </c>
+      <c r="C101" s="26" t="s">
         <v>856</v>
       </c>
-      <c r="C101" s="26" t="s">
-        <v>857</v>
-      </c>
       <c r="D101" s="27" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
